--- a/2025-06-15 New Run/Base de dados/PIM_Forecast_OutputFile.xlsx
+++ b/2025-06-15 New Run/Base de dados/PIM_Forecast_OutputFile.xlsx
@@ -356,10 +356,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -370,1968 +370,2241 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>lPIM_0pc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>lPIM_2pc</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>lPIM_4pc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lPIM_6pc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>lPIM_8pc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>4.34639945703073</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>42736</v>
       </c>
       <c r="C2">
-        <v>4.34639945703073</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="D2">
-        <v>4.34639945703073</v>
+        <v>4.354475565586591</v>
       </c>
       <c r="E2">
-        <v>4.34639945703073</v>
-      </c>
-      <c r="F2" s="2">
-        <v>42705</v>
+        <v>4.373893651443693</v>
+      </c>
+      <c r="F2">
+        <v>4.392941846414387</v>
+      </c>
+      <c r="G2">
+        <v>4.411633979426539</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>4.348049675972079</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>42767</v>
       </c>
       <c r="C3">
-        <v>4.349667849793504</v>
+        <v>4.328098292648326</v>
       </c>
       <c r="D3">
-        <v>4.351255199374395</v>
+        <v>4.347900919944506</v>
       </c>
       <c r="E3">
-        <v>4.352812877125408</v>
-      </c>
-      <c r="F3" s="2">
-        <v>42736</v>
+        <v>4.367319005801607</v>
+      </c>
+      <c r="F3">
+        <v>4.386367200772302</v>
+      </c>
+      <c r="G3">
+        <v>4.405059333784454</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>4.349699894913427</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>42795</v>
       </c>
       <c r="C4">
-        <v>4.352936242556277</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="D4">
-        <v>4.35611094171806</v>
+        <v>4.445846147386836</v>
       </c>
       <c r="E4">
-        <v>4.359226297220085</v>
-      </c>
-      <c r="F4" s="2">
-        <v>42767</v>
+        <v>4.465264233243937</v>
+      </c>
+      <c r="F4">
+        <v>4.484312428214632</v>
+      </c>
+      <c r="G4">
+        <v>4.503004561226784</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>4.351350113854775</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>42826</v>
       </c>
       <c r="C5">
-        <v>4.356204635319051</v>
+        <v>4.417635062141249</v>
       </c>
       <c r="D5">
-        <v>4.360966684061724</v>
+        <v>4.437437689437429</v>
       </c>
       <c r="E5">
-        <v>4.365639717314763</v>
-      </c>
-      <c r="F5" s="2">
-        <v>42795</v>
+        <v>4.456855775294531</v>
+      </c>
+      <c r="F5">
+        <v>4.475903970265225</v>
+      </c>
+      <c r="G5">
+        <v>4.494596103277377</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>4.353000332796124</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>42856</v>
       </c>
       <c r="C6">
-        <v>4.359473028081824</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="D6">
-        <v>4.365822426405389</v>
+        <v>4.476472804965828</v>
       </c>
       <c r="E6">
-        <v>4.37205313740944</v>
-      </c>
-      <c r="F6" s="2">
-        <v>42826</v>
+        <v>4.495890890822929</v>
+      </c>
+      <c r="F6">
+        <v>4.514939085793624</v>
+      </c>
+      <c r="G6">
+        <v>4.533631218805776</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>4.354650551737472</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>42887</v>
       </c>
       <c r="C7">
-        <v>4.362741420844598</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="D7">
-        <v>4.370678168749054</v>
+        <v>4.490297909957669</v>
       </c>
       <c r="E7">
-        <v>4.378466557504117</v>
-      </c>
-      <c r="F7" s="2">
-        <v>42856</v>
+        <v>4.509715995814771</v>
+      </c>
+      <c r="F7">
+        <v>4.528764190785465</v>
+      </c>
+      <c r="G7">
+        <v>4.547456323797618</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>4.35630077067882</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>42917</v>
       </c>
       <c r="C8">
-        <v>4.366009813607371</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="D8">
-        <v>4.375533911092718</v>
+        <v>4.514041252576989</v>
       </c>
       <c r="E8">
-        <v>4.384879977598795</v>
-      </c>
-      <c r="F8" s="2">
-        <v>42887</v>
+        <v>4.533459338434091</v>
+      </c>
+      <c r="F8">
+        <v>4.552507533404786</v>
+      </c>
+      <c r="G8">
+        <v>4.571199666416938</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>4.357950989620169</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>42948</v>
       </c>
       <c r="C9">
-        <v>4.369278206370145</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="D9">
-        <v>4.380389653436383</v>
+        <v>4.550249267088335</v>
       </c>
       <c r="E9">
-        <v>4.391293397693472</v>
-      </c>
-      <c r="F9" s="2">
-        <v>42917</v>
+        <v>4.569667352945436</v>
+      </c>
+      <c r="F9">
+        <v>4.588715547916131</v>
+      </c>
+      <c r="G9">
+        <v>4.607407680928283</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>4.359601208561517</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>42979</v>
       </c>
       <c r="C10">
-        <v>4.372546599132918</v>
+        <v>4.499809670330265</v>
       </c>
       <c r="D10">
-        <v>4.385245395780048</v>
+        <v>4.519612297626445</v>
       </c>
       <c r="E10">
-        <v>4.39770681778815</v>
-      </c>
-      <c r="F10" s="2">
-        <v>42948</v>
+        <v>4.539030383483547</v>
+      </c>
+      <c r="F10">
+        <v>4.558078578454241</v>
+      </c>
+      <c r="G10">
+        <v>4.576770711466393</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>4.361251427502865</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>43009</v>
       </c>
       <c r="C11">
-        <v>4.375814991895692</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="D11">
-        <v>4.390101138123712</v>
+        <v>4.521832054364758</v>
       </c>
       <c r="E11">
-        <v>4.404120237882827</v>
-      </c>
-      <c r="F11" s="2">
-        <v>42979</v>
+        <v>4.54125014022186</v>
+      </c>
+      <c r="F11">
+        <v>4.560298335192554</v>
+      </c>
+      <c r="G11">
+        <v>4.578990468204706</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>4.362901646444214</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>43040</v>
       </c>
       <c r="C12">
-        <v>4.379083384658465</v>
+        <v>4.460144413937834</v>
       </c>
       <c r="D12">
-        <v>4.394956880467377</v>
+        <v>4.479947041234014</v>
       </c>
       <c r="E12">
-        <v>4.410533657977505</v>
-      </c>
-      <c r="F12" s="2">
-        <v>43009</v>
+        <v>4.499365127091115</v>
+      </c>
+      <c r="F12">
+        <v>4.51841332206181</v>
+      </c>
+      <c r="G12">
+        <v>4.537105455073962</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>4.364551865385562</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>43070</v>
       </c>
       <c r="C13">
-        <v>4.382351777421238</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="D13">
-        <v>4.399812622811042</v>
+        <v>4.36620208432691</v>
       </c>
       <c r="E13">
-        <v>4.416947078072181</v>
-      </c>
-      <c r="F13" s="2">
-        <v>43040</v>
+        <v>4.385620170184012</v>
+      </c>
+      <c r="F13">
+        <v>4.404668365154706</v>
+      </c>
+      <c r="G13">
+        <v>4.423360498166859</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>4.36620208432691</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>43101</v>
       </c>
       <c r="C14">
-        <v>4.385620170184012</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="D14">
-        <v>4.404668365154706</v>
+        <v>4.374278192882771</v>
       </c>
       <c r="E14">
-        <v>4.423360498166859</v>
-      </c>
-      <c r="F14" s="2">
-        <v>43070</v>
+        <v>4.413114364596974</v>
+      </c>
+      <c r="F14">
+        <v>4.451210754538363</v>
+      </c>
+      <c r="G14">
+        <v>4.488595020562667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>4.367852303268259</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>43132</v>
       </c>
       <c r="C15">
-        <v>4.388888562946785</v>
+        <v>4.328098292648326</v>
       </c>
       <c r="D15">
-        <v>4.409524107498371</v>
+        <v>4.367703547240685</v>
       </c>
       <c r="E15">
-        <v>4.429773918261536</v>
-      </c>
-      <c r="F15" s="2">
-        <v>43101</v>
+        <v>4.406539718954889</v>
+      </c>
+      <c r="F15">
+        <v>4.444636108896278</v>
+      </c>
+      <c r="G15">
+        <v>4.482020374920582</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>4.369502522209607</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>43160</v>
       </c>
       <c r="C16">
-        <v>4.392156955709559</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="D16">
-        <v>4.414379849842035</v>
+        <v>4.465648774683015</v>
       </c>
       <c r="E16">
-        <v>4.436187338356214</v>
-      </c>
-      <c r="F16" s="2">
-        <v>43132</v>
+        <v>4.504484946397219</v>
+      </c>
+      <c r="F16">
+        <v>4.542581336338608</v>
+      </c>
+      <c r="G16">
+        <v>4.579965602362912</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>4.371152741150955</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>43191</v>
       </c>
       <c r="C17">
-        <v>4.395425348472332</v>
+        <v>4.417635062141249</v>
       </c>
       <c r="D17">
-        <v>4.4192355921857</v>
+        <v>4.457240316733609</v>
       </c>
       <c r="E17">
-        <v>4.442600758450891</v>
-      </c>
-      <c r="F17" s="2">
-        <v>43160</v>
+        <v>4.496076488447812</v>
+      </c>
+      <c r="F17">
+        <v>4.534172878389201</v>
+      </c>
+      <c r="G17">
+        <v>4.571557144413505</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>4.372802960092304</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>43221</v>
       </c>
       <c r="C18">
-        <v>4.398693741235106</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="D18">
-        <v>4.424091334529365</v>
+        <v>4.496275432262007</v>
       </c>
       <c r="E18">
-        <v>4.449014178545569</v>
-      </c>
-      <c r="F18" s="2">
-        <v>43191</v>
+        <v>4.535111603976211</v>
+      </c>
+      <c r="F18">
+        <v>4.5732079939176</v>
+      </c>
+      <c r="G18">
+        <v>4.610592259941904</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>4.374453179033652</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>43252</v>
       </c>
       <c r="C19">
-        <v>4.401962133997879</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="D19">
-        <v>4.42894707687303</v>
+        <v>4.510100537253849</v>
       </c>
       <c r="E19">
-        <v>4.455427598640246</v>
-      </c>
-      <c r="F19" s="2">
-        <v>43221</v>
+        <v>4.548936708968053</v>
+      </c>
+      <c r="F19">
+        <v>4.587033098909441</v>
+      </c>
+      <c r="G19">
+        <v>4.624417364933746</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>4.376103397975</v>
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>43282</v>
       </c>
       <c r="C20">
-        <v>4.405230526760652</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="D20">
-        <v>4.433802819216695</v>
+        <v>4.533843879873169</v>
       </c>
       <c r="E20">
-        <v>4.461841018734923</v>
-      </c>
-      <c r="F20" s="2">
-        <v>43252</v>
+        <v>4.572680051587373</v>
+      </c>
+      <c r="F20">
+        <v>4.610776441528762</v>
+      </c>
+      <c r="G20">
+        <v>4.648160707553066</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>4.377753616916348</v>
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>43313</v>
       </c>
       <c r="C21">
-        <v>4.408498919523426</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="D21">
-        <v>4.438658561560359</v>
+        <v>4.570051894384514</v>
       </c>
       <c r="E21">
-        <v>4.4682544388296</v>
-      </c>
-      <c r="F21" s="2">
-        <v>43282</v>
+        <v>4.608888066098718</v>
+      </c>
+      <c r="F21">
+        <v>4.646984456040107</v>
+      </c>
+      <c r="G21">
+        <v>4.684368722064411</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>4.379403835857697</v>
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>43344</v>
       </c>
       <c r="C22">
-        <v>4.4117673122862</v>
+        <v>4.499809670330265</v>
       </c>
       <c r="D22">
-        <v>4.443514303904023</v>
+        <v>4.539414924922625</v>
       </c>
       <c r="E22">
-        <v>4.474667858924278</v>
-      </c>
-      <c r="F22" s="2">
-        <v>43313</v>
+        <v>4.578251096636828</v>
+      </c>
+      <c r="F22">
+        <v>4.616347486578217</v>
+      </c>
+      <c r="G22">
+        <v>4.653731752602521</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>4.381054054799045</v>
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>43374</v>
       </c>
       <c r="C23">
-        <v>4.415035705048973</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="D23">
-        <v>4.448370046247688</v>
+        <v>4.541634681660938</v>
       </c>
       <c r="E23">
-        <v>4.481081279018955</v>
-      </c>
-      <c r="F23" s="2">
-        <v>43344</v>
+        <v>4.580470853375141</v>
+      </c>
+      <c r="F23">
+        <v>4.61856724331653</v>
+      </c>
+      <c r="G23">
+        <v>4.655951509340834</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>4.382704273740393</v>
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>43405</v>
       </c>
       <c r="C24">
-        <v>4.418304097811746</v>
+        <v>4.460144413937834</v>
       </c>
       <c r="D24">
-        <v>4.453225788591353</v>
+        <v>4.499749668530193</v>
       </c>
       <c r="E24">
-        <v>4.487494699113633</v>
-      </c>
-      <c r="F24" s="2">
-        <v>43374</v>
+        <v>4.538585840244397</v>
+      </c>
+      <c r="F24">
+        <v>4.576682230185786</v>
+      </c>
+      <c r="G24">
+        <v>4.61406649621009</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>4.384354492681742</v>
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>43435</v>
       </c>
       <c r="C25">
-        <v>4.42157249057452</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="D25">
-        <v>4.458081530935018</v>
+        <v>4.38600471162309</v>
       </c>
       <c r="E25">
-        <v>4.49390811920831</v>
-      </c>
-      <c r="F25" s="2">
-        <v>43405</v>
+        <v>4.424840883337294</v>
+      </c>
+      <c r="F25">
+        <v>4.462937273278683</v>
+      </c>
+      <c r="G25">
+        <v>4.500321539302987</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>4.38600471162309</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>43466</v>
       </c>
       <c r="C26">
-        <v>4.424840883337293</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="D26">
-        <v>4.462937273278683</v>
+        <v>4.39408082017895</v>
       </c>
       <c r="E26">
-        <v>4.500321539302988</v>
-      </c>
-      <c r="F26" s="2">
-        <v>43435</v>
+        <v>4.452335077750256</v>
+      </c>
+      <c r="F26">
+        <v>4.509479662662339</v>
+      </c>
+      <c r="G26">
+        <v>4.565556061698795</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27">
-        <v>4.387654930564438</v>
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>43497</v>
       </c>
       <c r="C27">
-        <v>4.428109276100066</v>
+        <v>4.328098292648326</v>
       </c>
       <c r="D27">
-        <v>4.467793015622346</v>
+        <v>4.387506174536865</v>
       </c>
       <c r="E27">
-        <v>4.506734959397665</v>
-      </c>
-      <c r="F27" s="2">
-        <v>43466</v>
+        <v>4.445760432108171</v>
+      </c>
+      <c r="F27">
+        <v>4.502905017020254</v>
+      </c>
+      <c r="G27">
+        <v>4.55898141605671</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>4.389305149505787</v>
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>43525</v>
       </c>
       <c r="C28">
-        <v>4.43137766886284</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="D28">
-        <v>4.472648757966011</v>
+        <v>4.485451401979195</v>
       </c>
       <c r="E28">
-        <v>4.513148379492342</v>
-      </c>
-      <c r="F28" s="2">
-        <v>43497</v>
+        <v>4.543705659550501</v>
+      </c>
+      <c r="F28">
+        <v>4.600850244462584</v>
+      </c>
+      <c r="G28">
+        <v>4.65692664349904</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29">
-        <v>4.390955368447135</v>
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>43556</v>
       </c>
       <c r="C29">
-        <v>4.434646061625614</v>
+        <v>4.417635062141249</v>
       </c>
       <c r="D29">
-        <v>4.477504500309676</v>
+        <v>4.477042944029789</v>
       </c>
       <c r="E29">
-        <v>4.519561799587019</v>
-      </c>
-      <c r="F29" s="2">
-        <v>43525</v>
+        <v>4.535297201601094</v>
+      </c>
+      <c r="F29">
+        <v>4.592441786513177</v>
+      </c>
+      <c r="G29">
+        <v>4.648518185549634</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30">
-        <v>4.392605587388483</v>
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>43586</v>
       </c>
       <c r="C30">
-        <v>4.437914454388387</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="D30">
-        <v>4.482360242653341</v>
+        <v>4.516078059558187</v>
       </c>
       <c r="E30">
-        <v>4.525975219681697</v>
-      </c>
-      <c r="F30" s="2">
-        <v>43556</v>
+        <v>4.574332317129493</v>
+      </c>
+      <c r="F30">
+        <v>4.631476902041576</v>
+      </c>
+      <c r="G30">
+        <v>4.687553301078032</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31">
-        <v>4.394255806329832</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>43617</v>
       </c>
       <c r="C31">
-        <v>4.44118284715116</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="D31">
-        <v>4.487215984997006</v>
+        <v>4.529903164550029</v>
       </c>
       <c r="E31">
-        <v>4.532388639776374</v>
-      </c>
-      <c r="F31" s="2">
-        <v>43586</v>
+        <v>4.588157422121334</v>
+      </c>
+      <c r="F31">
+        <v>4.645302007033417</v>
+      </c>
+      <c r="G31">
+        <v>4.701378406069874</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32">
-        <v>4.39590602527118</v>
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>43647</v>
       </c>
       <c r="C32">
-        <v>4.444451239913934</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="D32">
-        <v>4.492071727340671</v>
+        <v>4.553646507169349</v>
       </c>
       <c r="E32">
-        <v>4.538802059871052</v>
-      </c>
-      <c r="F32" s="2">
-        <v>43617</v>
+        <v>4.611900764740654</v>
+      </c>
+      <c r="F32">
+        <v>4.669045349652738</v>
+      </c>
+      <c r="G32">
+        <v>4.725121748689194</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33">
-        <v>4.397556244212528</v>
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>43678</v>
       </c>
       <c r="C33">
-        <v>4.447719632676708</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="D33">
-        <v>4.496927469684334</v>
+        <v>4.589854521680694</v>
       </c>
       <c r="E33">
-        <v>4.545215479965729</v>
-      </c>
-      <c r="F33" s="2">
-        <v>43647</v>
+        <v>4.648108779252</v>
+      </c>
+      <c r="F33">
+        <v>4.705253364164083</v>
+      </c>
+      <c r="G33">
+        <v>4.761329763200539</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34">
-        <v>4.399206463153877</v>
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>43709</v>
       </c>
       <c r="C34">
-        <v>4.45098802543948</v>
+        <v>4.499809670330265</v>
       </c>
       <c r="D34">
-        <v>4.501783212027999</v>
+        <v>4.559217552218804</v>
       </c>
       <c r="E34">
-        <v>4.551628900060406</v>
-      </c>
-      <c r="F34" s="2">
-        <v>43678</v>
+        <v>4.61747180979011</v>
+      </c>
+      <c r="F34">
+        <v>4.674616394702193</v>
+      </c>
+      <c r="G34">
+        <v>4.730692793738649</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35">
-        <v>4.400856682095225</v>
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>43739</v>
       </c>
       <c r="C35">
-        <v>4.454256418202254</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="D35">
-        <v>4.506638954371664</v>
+        <v>4.561437308957117</v>
       </c>
       <c r="E35">
-        <v>4.558042320155083</v>
-      </c>
-      <c r="F35" s="2">
-        <v>43709</v>
+        <v>4.619691566528423</v>
+      </c>
+      <c r="F35">
+        <v>4.676836151440506</v>
+      </c>
+      <c r="G35">
+        <v>4.732912550476962</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36">
-        <v>4.402506901036573</v>
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>43770</v>
       </c>
       <c r="C36">
-        <v>4.457524810965028</v>
+        <v>4.460144413937834</v>
       </c>
       <c r="D36">
-        <v>4.511494696715329</v>
+        <v>4.519552295826373</v>
       </c>
       <c r="E36">
-        <v>4.564455740249761</v>
-      </c>
-      <c r="F36" s="2">
-        <v>43739</v>
+        <v>4.577806553397679</v>
+      </c>
+      <c r="F36">
+        <v>4.634951138309762</v>
+      </c>
+      <c r="G36">
+        <v>4.691027537346218</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37">
-        <v>4.404157119977921</v>
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>43800</v>
       </c>
       <c r="C37">
-        <v>4.460793203727801</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="D37">
-        <v>4.516350439058994</v>
+        <v>4.40580733891927</v>
       </c>
       <c r="E37">
-        <v>4.570869160344438</v>
-      </c>
-      <c r="F37" s="2">
-        <v>43770</v>
+        <v>4.464061596490575</v>
+      </c>
+      <c r="F37">
+        <v>4.521206181402659</v>
+      </c>
+      <c r="G37">
+        <v>4.577282580439115</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38">
-        <v>4.40580733891927</v>
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>43831</v>
       </c>
       <c r="C38">
-        <v>4.464061596490574</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="D38">
-        <v>4.521206181402658</v>
+        <v>4.41388344747513</v>
       </c>
       <c r="E38">
-        <v>4.577282580439116</v>
-      </c>
-      <c r="F38" s="2">
-        <v>43800</v>
+        <v>4.491555790903537</v>
+      </c>
+      <c r="F38">
+        <v>4.567748570786315</v>
+      </c>
+      <c r="G38">
+        <v>4.642517102834923</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39">
-        <v>4.407457557860618</v>
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>43862</v>
       </c>
       <c r="C39">
-        <v>4.467329989253348</v>
+        <v>4.328098292648326</v>
       </c>
       <c r="D39">
-        <v>4.526061923746322</v>
+        <v>4.407308801833045</v>
       </c>
       <c r="E39">
-        <v>4.583696000533793</v>
-      </c>
-      <c r="F39" s="2">
-        <v>43831</v>
+        <v>4.484981145261452</v>
+      </c>
+      <c r="F39">
+        <v>4.56117392514423</v>
+      </c>
+      <c r="G39">
+        <v>4.635942457192838</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40">
-        <v>4.409107776801966</v>
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>43891</v>
       </c>
       <c r="C40">
-        <v>4.470598382016122</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="D40">
-        <v>4.530917666089987</v>
+        <v>4.505254029275375</v>
       </c>
       <c r="E40">
-        <v>4.590109420628471</v>
-      </c>
-      <c r="F40" s="2">
-        <v>43862</v>
+        <v>4.582926372703782</v>
+      </c>
+      <c r="F40">
+        <v>4.65911915258656</v>
+      </c>
+      <c r="G40">
+        <v>4.733887684635168</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41">
-        <v>4.410757995743315</v>
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>43922</v>
       </c>
       <c r="C41">
-        <v>4.473866774778894</v>
+        <v>4.417635062141249</v>
       </c>
       <c r="D41">
-        <v>4.535773408433652</v>
+        <v>4.496845571325968</v>
       </c>
       <c r="E41">
-        <v>4.596522840723148</v>
-      </c>
-      <c r="F41" s="2">
-        <v>43891</v>
+        <v>4.574517914754376</v>
+      </c>
+      <c r="F41">
+        <v>4.650710694637153</v>
+      </c>
+      <c r="G41">
+        <v>4.725479226685762</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42">
-        <v>4.412408214684663</v>
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>43952</v>
       </c>
       <c r="C42">
-        <v>4.477135167541668</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="D42">
-        <v>4.540629150777317</v>
+        <v>4.535880686854367</v>
       </c>
       <c r="E42">
-        <v>4.602936260817825</v>
-      </c>
-      <c r="F42" s="2">
-        <v>43922</v>
+        <v>4.613553030282774</v>
+      </c>
+      <c r="F42">
+        <v>4.689745810165552</v>
+      </c>
+      <c r="G42">
+        <v>4.76451434221416</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43">
-        <v>4.414058433626011</v>
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>43983</v>
       </c>
       <c r="C43">
-        <v>4.480403560304442</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="D43">
-        <v>4.545484893120981</v>
+        <v>4.549705791846208</v>
       </c>
       <c r="E43">
-        <v>4.609349680912502</v>
-      </c>
-      <c r="F43" s="2">
-        <v>43952</v>
+        <v>4.627378135274616</v>
+      </c>
+      <c r="F43">
+        <v>4.703570915157393</v>
+      </c>
+      <c r="G43">
+        <v>4.778339447206002</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="B44">
-        <v>4.41570865256736</v>
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>44013</v>
       </c>
       <c r="C44">
-        <v>4.483671953067216</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="D44">
-        <v>4.550340635464646</v>
+        <v>4.573449134465529</v>
       </c>
       <c r="E44">
-        <v>4.61576310100718</v>
-      </c>
-      <c r="F44" s="2">
-        <v>43983</v>
+        <v>4.651121477893936</v>
+      </c>
+      <c r="F44">
+        <v>4.727314257776714</v>
+      </c>
+      <c r="G44">
+        <v>4.802082789825322</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="B45">
-        <v>4.417358871508708</v>
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>44044</v>
       </c>
       <c r="C45">
-        <v>4.486940345829988</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="D45">
-        <v>4.55519637780831</v>
+        <v>4.609657148976874</v>
       </c>
       <c r="E45">
-        <v>4.622176521101857</v>
-      </c>
-      <c r="F45" s="2">
-        <v>44013</v>
+        <v>4.687329492405281</v>
+      </c>
+      <c r="F45">
+        <v>4.763522272288059</v>
+      </c>
+      <c r="G45">
+        <v>4.838290804336667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="B46">
-        <v>4.419009090450056</v>
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>44075</v>
       </c>
       <c r="C46">
-        <v>4.490208738592762</v>
+        <v>4.499809670330265</v>
       </c>
       <c r="D46">
-        <v>4.560052120151975</v>
+        <v>4.579020179514984</v>
       </c>
       <c r="E46">
-        <v>4.628589941196535</v>
-      </c>
-      <c r="F46" s="2">
-        <v>44044</v>
+        <v>4.656692522943391</v>
+      </c>
+      <c r="F46">
+        <v>4.732885302826169</v>
+      </c>
+      <c r="G46">
+        <v>4.807653834874777</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>45</v>
-      </c>
-      <c r="B47">
-        <v>4.420659309391405</v>
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>44105</v>
       </c>
       <c r="C47">
-        <v>4.493477131355536</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="D47">
-        <v>4.56490786249564</v>
+        <v>4.581239936253297</v>
       </c>
       <c r="E47">
-        <v>4.635003361291212</v>
-      </c>
-      <c r="F47" s="2">
-        <v>44075</v>
+        <v>4.658912279681704</v>
+      </c>
+      <c r="F47">
+        <v>4.735105059564482</v>
+      </c>
+      <c r="G47">
+        <v>4.809873591613091</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="B48">
-        <v>4.422309528332753</v>
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>44136</v>
       </c>
       <c r="C48">
-        <v>4.496745524118309</v>
+        <v>4.460144413937834</v>
       </c>
       <c r="D48">
-        <v>4.569763604839305</v>
+        <v>4.539354923122553</v>
       </c>
       <c r="E48">
-        <v>4.641416781385889</v>
-      </c>
-      <c r="F48" s="2">
-        <v>44105</v>
+        <v>4.61702726655096</v>
+      </c>
+      <c r="F48">
+        <v>4.693220046433738</v>
+      </c>
+      <c r="G48">
+        <v>4.767988578482346</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="B49">
-        <v>4.423959747274101</v>
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>44166</v>
       </c>
       <c r="C49">
-        <v>4.500013916881082</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="D49">
-        <v>4.574619347182969</v>
+        <v>4.42560996621545</v>
       </c>
       <c r="E49">
-        <v>4.647830201480566</v>
-      </c>
-      <c r="F49" s="2">
-        <v>44136</v>
+        <v>4.503282309643857</v>
+      </c>
+      <c r="F49">
+        <v>4.579475089526635</v>
+      </c>
+      <c r="G49">
+        <v>4.654243621575243</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="B50">
-        <v>4.42560996621545</v>
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>44197</v>
       </c>
       <c r="C50">
-        <v>4.503282309643856</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="D50">
-        <v>4.579475089526634</v>
+        <v>4.43368607477131</v>
       </c>
       <c r="E50">
-        <v>4.654243621575244</v>
-      </c>
-      <c r="F50" s="2">
-        <v>44166</v>
+        <v>4.530776504056819</v>
+      </c>
+      <c r="F50">
+        <v>4.626017478910291</v>
+      </c>
+      <c r="G50">
+        <v>4.719478143971052</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="B51">
-        <v>4.427260185156798</v>
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>44228</v>
       </c>
       <c r="C51">
-        <v>4.50655070240663</v>
+        <v>4.328098292648326</v>
       </c>
       <c r="D51">
-        <v>4.584330831870298</v>
+        <v>4.427111429129225</v>
       </c>
       <c r="E51">
-        <v>4.660657041669921</v>
-      </c>
-      <c r="F51" s="2">
-        <v>44197</v>
+        <v>4.524201858414734</v>
+      </c>
+      <c r="F51">
+        <v>4.619442833268206</v>
+      </c>
+      <c r="G51">
+        <v>4.712903498328966</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="B52">
-        <v>4.428910404098146</v>
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>44256</v>
       </c>
       <c r="C52">
-        <v>4.509819095169402</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="D52">
-        <v>4.589186574213963</v>
+        <v>4.525056656571555</v>
       </c>
       <c r="E52">
-        <v>4.667070461764599</v>
-      </c>
-      <c r="F52" s="2">
-        <v>44228</v>
+        <v>4.622147085857064</v>
+      </c>
+      <c r="F52">
+        <v>4.717388060710536</v>
+      </c>
+      <c r="G52">
+        <v>4.810848725771296</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="B53">
-        <v>4.430560623039494</v>
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>44287</v>
       </c>
       <c r="C53">
-        <v>4.513087487932176</v>
+        <v>4.417635062141249</v>
       </c>
       <c r="D53">
-        <v>4.594042316557628</v>
+        <v>4.516648198622148</v>
       </c>
       <c r="E53">
-        <v>4.673483881859276</v>
-      </c>
-      <c r="F53" s="2">
-        <v>44256</v>
+        <v>4.613738627907657</v>
+      </c>
+      <c r="F53">
+        <v>4.708979602761129</v>
+      </c>
+      <c r="G53">
+        <v>4.80244026782189</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54">
-        <v>4.432210841980843</v>
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>44317</v>
       </c>
       <c r="C54">
-        <v>4.51635588069495</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="D54">
-        <v>4.598898058901292</v>
+        <v>4.555683314150547</v>
       </c>
       <c r="E54">
-        <v>4.679897301953954</v>
-      </c>
-      <c r="F54" s="2">
-        <v>44287</v>
+        <v>4.652773743436056</v>
+      </c>
+      <c r="F54">
+        <v>4.748014718289528</v>
+      </c>
+      <c r="G54">
+        <v>4.841475383350288</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="B55">
-        <v>4.433861060922191</v>
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>44348</v>
       </c>
       <c r="C55">
-        <v>4.519624273457723</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="D55">
-        <v>4.603753801244957</v>
+        <v>4.569508419142388</v>
       </c>
       <c r="E55">
-        <v>4.686310722048631</v>
-      </c>
-      <c r="F55" s="2">
-        <v>44317</v>
+        <v>4.666598848427897</v>
+      </c>
+      <c r="F55">
+        <v>4.761839823281369</v>
+      </c>
+      <c r="G55">
+        <v>4.85530048834213</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56">
-        <v>4.435511279863539</v>
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>44378</v>
       </c>
       <c r="C56">
-        <v>4.522892666220496</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="D56">
-        <v>4.608609543588622</v>
+        <v>4.593251761761708</v>
       </c>
       <c r="E56">
-        <v>4.692724142143308</v>
-      </c>
-      <c r="F56" s="2">
-        <v>44348</v>
+        <v>4.690342191047217</v>
+      </c>
+      <c r="F56">
+        <v>4.78558316590069</v>
+      </c>
+      <c r="G56">
+        <v>4.87904383096145</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="B57">
-        <v>4.437161498804888</v>
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>44409</v>
       </c>
       <c r="C57">
-        <v>4.52616105898327</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="D57">
-        <v>4.613465285932286</v>
+        <v>4.629459776273054</v>
       </c>
       <c r="E57">
-        <v>4.699137562237985</v>
-      </c>
-      <c r="F57" s="2">
-        <v>44378</v>
+        <v>4.726550205558563</v>
+      </c>
+      <c r="F57">
+        <v>4.821791180412035</v>
+      </c>
+      <c r="G57">
+        <v>4.915251845472795</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="B58">
-        <v>4.438811717746236</v>
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>44440</v>
       </c>
       <c r="C58">
-        <v>4.529429451746044</v>
+        <v>4.499809670330265</v>
       </c>
       <c r="D58">
-        <v>4.618321028275951</v>
+        <v>4.598822806811164</v>
       </c>
       <c r="E58">
-        <v>4.705550982332663</v>
-      </c>
-      <c r="F58" s="2">
-        <v>44409</v>
+        <v>4.695913236096673</v>
+      </c>
+      <c r="F58">
+        <v>4.791154210950145</v>
+      </c>
+      <c r="G58">
+        <v>4.884614876010906</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="B59">
-        <v>4.440461936687584</v>
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>44470</v>
       </c>
       <c r="C59">
-        <v>4.532697844508816</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="D59">
-        <v>4.623176770619616</v>
+        <v>4.601042563549477</v>
       </c>
       <c r="E59">
-        <v>4.71196440242734</v>
-      </c>
-      <c r="F59" s="2">
-        <v>44440</v>
+        <v>4.698132992834986</v>
+      </c>
+      <c r="F59">
+        <v>4.793373967688458</v>
+      </c>
+      <c r="G59">
+        <v>4.886834632749219</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="B60">
-        <v>4.442112155628933</v>
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>44501</v>
       </c>
       <c r="C60">
-        <v>4.53596623727159</v>
+        <v>4.460144413937834</v>
       </c>
       <c r="D60">
-        <v>4.62803251296328</v>
+        <v>4.559157550418733</v>
       </c>
       <c r="E60">
-        <v>4.718377822522018</v>
-      </c>
-      <c r="F60" s="2">
-        <v>44470</v>
+        <v>4.656247979704242</v>
+      </c>
+      <c r="F60">
+        <v>4.751488954557714</v>
+      </c>
+      <c r="G60">
+        <v>4.844949619618474</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="B61">
-        <v>4.443762374570281</v>
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>44531</v>
       </c>
       <c r="C61">
-        <v>4.539234630034364</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="D61">
-        <v>4.632888255306945</v>
+        <v>4.445412593511629</v>
       </c>
       <c r="E61">
-        <v>4.724791242616695</v>
-      </c>
-      <c r="F61" s="2">
-        <v>44501</v>
+        <v>4.542503022797138</v>
+      </c>
+      <c r="F61">
+        <v>4.637743997650611</v>
+      </c>
+      <c r="G61">
+        <v>4.731204662711371</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="B62">
-        <v>4.445412593511629</v>
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>44562</v>
       </c>
       <c r="C62">
-        <v>4.542503022797137</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="D62">
-        <v>4.63774399765061</v>
+        <v>4.45348870206749</v>
       </c>
       <c r="E62">
-        <v>4.731204662711373</v>
-      </c>
-      <c r="F62" s="2">
-        <v>44531</v>
+        <v>4.5699972172101</v>
+      </c>
+      <c r="F62">
+        <v>4.684286387034267</v>
+      </c>
+      <c r="G62">
+        <v>4.79643918510718</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>61</v>
-      </c>
-      <c r="B63">
-        <v>4.447062812452978</v>
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>44593</v>
       </c>
       <c r="C63">
-        <v>4.54577141555991</v>
+        <v>4.328098292648326</v>
       </c>
       <c r="D63">
-        <v>4.642599739994274</v>
+        <v>4.446914056425404</v>
       </c>
       <c r="E63">
-        <v>4.737618082806049</v>
-      </c>
-      <c r="F63" s="2">
-        <v>44562</v>
+        <v>4.563422571568015</v>
+      </c>
+      <c r="F63">
+        <v>4.677711741392182</v>
+      </c>
+      <c r="G63">
+        <v>4.789864539465094</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>62</v>
-      </c>
-      <c r="B64">
-        <v>4.448713031394326</v>
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>44621</v>
       </c>
       <c r="C64">
-        <v>4.549039808322684</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="D64">
-        <v>4.647455482337939</v>
+        <v>4.544859283867734</v>
       </c>
       <c r="E64">
-        <v>4.744031502900727</v>
-      </c>
-      <c r="F64" s="2">
-        <v>44593</v>
+        <v>4.661367799010345</v>
+      </c>
+      <c r="F64">
+        <v>4.775656968834512</v>
+      </c>
+      <c r="G64">
+        <v>4.887809766907425</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>63</v>
-      </c>
-      <c r="B65">
-        <v>4.450363250335674</v>
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>44652</v>
       </c>
       <c r="C65">
-        <v>4.552308201085458</v>
+        <v>4.417635062141249</v>
       </c>
       <c r="D65">
-        <v>4.652311224681603</v>
+        <v>4.536450825918328</v>
       </c>
       <c r="E65">
-        <v>4.750444922995404</v>
-      </c>
-      <c r="F65" s="2">
-        <v>44621</v>
+        <v>4.652959341060939</v>
+      </c>
+      <c r="F65">
+        <v>4.767248510885105</v>
+      </c>
+      <c r="G65">
+        <v>4.879401308958018</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>64</v>
-      </c>
-      <c r="B66">
-        <v>4.452013469277023</v>
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>44682</v>
       </c>
       <c r="C66">
-        <v>4.555576593848231</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="D66">
-        <v>4.657166967025268</v>
+        <v>4.575485941446726</v>
       </c>
       <c r="E66">
-        <v>4.756858343090082</v>
-      </c>
-      <c r="F66" s="2">
-        <v>44652</v>
+        <v>4.691994456589337</v>
+      </c>
+      <c r="F66">
+        <v>4.806283626413504</v>
+      </c>
+      <c r="G66">
+        <v>4.918436424486416</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>65</v>
-      </c>
-      <c r="B67">
-        <v>4.453663688218371</v>
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>44713</v>
       </c>
       <c r="C67">
-        <v>4.558844986611004</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="D67">
-        <v>4.662022709368933</v>
+        <v>4.589311046438568</v>
       </c>
       <c r="E67">
-        <v>4.763271763184759</v>
-      </c>
-      <c r="F67" s="2">
-        <v>44682</v>
+        <v>4.705819561581179</v>
+      </c>
+      <c r="F67">
+        <v>4.820108731405345</v>
+      </c>
+      <c r="G67">
+        <v>4.932261529478258</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>66</v>
-      </c>
-      <c r="B68">
-        <v>4.455313907159719</v>
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>44743</v>
       </c>
       <c r="C68">
-        <v>4.562113379373778</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="D68">
-        <v>4.666878451712598</v>
+        <v>4.613054389057888</v>
       </c>
       <c r="E68">
-        <v>4.769685183279437</v>
-      </c>
-      <c r="F68" s="2">
-        <v>44713</v>
+        <v>4.729562904200499</v>
+      </c>
+      <c r="F68">
+        <v>4.843852074024666</v>
+      </c>
+      <c r="G68">
+        <v>4.956004872097578</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>67</v>
-      </c>
-      <c r="B69">
-        <v>4.456964126101068</v>
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>44774</v>
       </c>
       <c r="C69">
-        <v>4.565381772136551</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="D69">
-        <v>4.671734194056262</v>
+        <v>4.649262403569233</v>
       </c>
       <c r="E69">
-        <v>4.776098603374114</v>
-      </c>
-      <c r="F69" s="2">
-        <v>44743</v>
+        <v>4.765770918711844</v>
+      </c>
+      <c r="F69">
+        <v>4.880060088536011</v>
+      </c>
+      <c r="G69">
+        <v>4.992212886608923</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>68</v>
-      </c>
-      <c r="B70">
-        <v>4.458614345042416</v>
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>44805</v>
       </c>
       <c r="C70">
-        <v>4.568650164899324</v>
+        <v>4.499809670330265</v>
       </c>
       <c r="D70">
-        <v>4.676589936399926</v>
+        <v>4.618625434107344</v>
       </c>
       <c r="E70">
-        <v>4.782512023468791</v>
-      </c>
-      <c r="F70" s="2">
-        <v>44774</v>
+        <v>4.735133949249954</v>
+      </c>
+      <c r="F70">
+        <v>4.849423119074121</v>
+      </c>
+      <c r="G70">
+        <v>4.961575917147034</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>69</v>
-      </c>
-      <c r="B71">
-        <v>4.460264563983764</v>
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>44835</v>
       </c>
       <c r="C71">
-        <v>4.571918557662098</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="D71">
-        <v>4.681445678743591</v>
+        <v>4.620845190845657</v>
       </c>
       <c r="E71">
-        <v>4.788925443563468</v>
-      </c>
-      <c r="F71" s="2">
-        <v>44805</v>
+        <v>4.737353705988268</v>
+      </c>
+      <c r="F71">
+        <v>4.851642875812434</v>
+      </c>
+      <c r="G71">
+        <v>4.963795673885347</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>70</v>
-      </c>
-      <c r="B72">
-        <v>4.461914782925112</v>
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>44866</v>
       </c>
       <c r="C72">
-        <v>4.575186950424872</v>
+        <v>4.460144413937834</v>
       </c>
       <c r="D72">
-        <v>4.686301421087256</v>
+        <v>4.578960177714912</v>
       </c>
       <c r="E72">
-        <v>4.795338863658146</v>
-      </c>
-      <c r="F72" s="2">
-        <v>44835</v>
+        <v>4.695468692857523</v>
+      </c>
+      <c r="F72">
+        <v>4.80975786268169</v>
+      </c>
+      <c r="G72">
+        <v>4.921910660754603</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>71</v>
-      </c>
-      <c r="B73">
-        <v>4.463565001866461</v>
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>44896</v>
       </c>
       <c r="C73">
-        <v>4.578455343187645</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="D73">
-        <v>4.691157163430921</v>
+        <v>4.465215220807809</v>
       </c>
       <c r="E73">
-        <v>4.801752283752823</v>
-      </c>
-      <c r="F73" s="2">
-        <v>44866</v>
+        <v>4.58172373595042</v>
+      </c>
+      <c r="F73">
+        <v>4.696012905774587</v>
+      </c>
+      <c r="G73">
+        <v>4.808165703847499</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>72</v>
-      </c>
-      <c r="B74">
-        <v>4.465215220807809</v>
+        <v>73</v>
+      </c>
+      <c r="B74" s="2">
+        <v>44927</v>
       </c>
       <c r="C74">
-        <v>4.581723735950418</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="D74">
-        <v>4.696012905774586</v>
+        <v>4.473291329363669</v>
       </c>
       <c r="E74">
-        <v>4.808165703847501</v>
-      </c>
-      <c r="F74" s="2">
-        <v>44896</v>
+        <v>4.609217930363382</v>
+      </c>
+      <c r="F74">
+        <v>4.742555295158243</v>
+      </c>
+      <c r="G74">
+        <v>4.873400226243308</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>73</v>
-      </c>
-      <c r="B75">
-        <v>4.466865439749157</v>
+        <v>74</v>
+      </c>
+      <c r="B75" s="2">
+        <v>44958</v>
       </c>
       <c r="C75">
-        <v>4.584992128713192</v>
+        <v>4.328098292648326</v>
       </c>
       <c r="D75">
-        <v>4.70086864811825</v>
+        <v>4.466716683721584</v>
       </c>
       <c r="E75">
-        <v>4.814579123942178</v>
-      </c>
-      <c r="F75" s="2">
-        <v>44927</v>
+        <v>4.602643284721297</v>
+      </c>
+      <c r="F75">
+        <v>4.735980649516158</v>
+      </c>
+      <c r="G75">
+        <v>4.866825580601223</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>74</v>
-      </c>
-      <c r="B76">
-        <v>4.468515658690506</v>
+        <v>75</v>
+      </c>
+      <c r="B76" s="2">
+        <v>44986</v>
       </c>
       <c r="C76">
-        <v>4.588260521475966</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="D76">
-        <v>4.705724390461914</v>
+        <v>4.564661911163914</v>
       </c>
       <c r="E76">
-        <v>4.820992544036856</v>
-      </c>
-      <c r="F76" s="2">
-        <v>44958</v>
+        <v>4.700588512163627</v>
+      </c>
+      <c r="F76">
+        <v>4.833925876958488</v>
+      </c>
+      <c r="G76">
+        <v>4.964770808043553</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>75</v>
-      </c>
-      <c r="B77">
-        <v>4.470165877631854</v>
+        <v>76</v>
+      </c>
+      <c r="B77" s="2">
+        <v>45017</v>
       </c>
       <c r="C77">
-        <v>4.591528914238739</v>
+        <v>4.417635062141249</v>
       </c>
       <c r="D77">
-        <v>4.710580132805579</v>
+        <v>4.556253453214508</v>
       </c>
       <c r="E77">
-        <v>4.827405964131533</v>
-      </c>
-      <c r="F77" s="2">
-        <v>44986</v>
+        <v>4.69218005421422</v>
+      </c>
+      <c r="F77">
+        <v>4.825517419009081</v>
+      </c>
+      <c r="G77">
+        <v>4.956362350094146</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>76</v>
-      </c>
-      <c r="B78">
-        <v>4.471816096573202</v>
+        <v>77</v>
+      </c>
+      <c r="B78" s="2">
+        <v>45047</v>
       </c>
       <c r="C78">
-        <v>4.594797307001512</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="D78">
-        <v>4.715435875149244</v>
+        <v>4.595288568742906</v>
       </c>
       <c r="E78">
-        <v>4.83381938422621</v>
-      </c>
-      <c r="F78" s="2">
-        <v>45017</v>
+        <v>4.731215169742619</v>
+      </c>
+      <c r="F78">
+        <v>4.86455253453748</v>
+      </c>
+      <c r="G78">
+        <v>4.995397465622545</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>77</v>
-      </c>
-      <c r="B79">
-        <v>4.473466315514551</v>
+        <v>78</v>
+      </c>
+      <c r="B79" s="2">
+        <v>45078</v>
       </c>
       <c r="C79">
-        <v>4.598065699764286</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="D79">
-        <v>4.720291617492909</v>
+        <v>4.609113673734748</v>
       </c>
       <c r="E79">
-        <v>4.840232804320888</v>
-      </c>
-      <c r="F79" s="2">
-        <v>45047</v>
+        <v>4.74504027473446</v>
+      </c>
+      <c r="F79">
+        <v>4.878377639529321</v>
+      </c>
+      <c r="G79">
+        <v>5.009222570614386</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>78</v>
-      </c>
-      <c r="B80">
-        <v>4.475116534455899</v>
+        <v>79</v>
+      </c>
+      <c r="B80" s="2">
+        <v>45108</v>
       </c>
       <c r="C80">
-        <v>4.601334092527059</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="D80">
-        <v>4.725147359836574</v>
+        <v>4.632857016354068</v>
       </c>
       <c r="E80">
-        <v>4.846646224415565</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45078</v>
+        <v>4.768783617353781</v>
+      </c>
+      <c r="F80">
+        <v>4.902120982148642</v>
+      </c>
+      <c r="G80">
+        <v>5.032965913233706</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>79</v>
-      </c>
-      <c r="B81">
-        <v>4.476766753397247</v>
+        <v>80</v>
+      </c>
+      <c r="B81" s="2">
+        <v>45139</v>
       </c>
       <c r="C81">
-        <v>4.604602485289832</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="D81">
-        <v>4.730003102180238</v>
+        <v>4.669065030865413</v>
       </c>
       <c r="E81">
-        <v>4.853059644510243</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45108</v>
+        <v>4.804991631865126</v>
+      </c>
+      <c r="F81">
+        <v>4.938328996659987</v>
+      </c>
+      <c r="G81">
+        <v>5.069173927745052</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>80</v>
-      </c>
-      <c r="B82">
-        <v>4.478416972338596</v>
+        <v>81</v>
+      </c>
+      <c r="B82" s="2">
+        <v>45170</v>
       </c>
       <c r="C82">
-        <v>4.607870878052606</v>
+        <v>4.499809670330265</v>
       </c>
       <c r="D82">
-        <v>4.734858844523902</v>
+        <v>4.638428061403523</v>
       </c>
       <c r="E82">
-        <v>4.85947306460492</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45139</v>
+        <v>4.774354662403236</v>
+      </c>
+      <c r="F82">
+        <v>4.907692027198097</v>
+      </c>
+      <c r="G82">
+        <v>5.038536958283162</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>81</v>
-      </c>
-      <c r="B83">
-        <v>4.480067191279944</v>
+        <v>82</v>
+      </c>
+      <c r="B83" s="2">
+        <v>45200</v>
       </c>
       <c r="C83">
-        <v>4.61113927081538</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="D83">
-        <v>4.739714586867567</v>
+        <v>4.640647818141836</v>
       </c>
       <c r="E83">
-        <v>4.865886484699598</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45170</v>
+        <v>4.776574419141549</v>
+      </c>
+      <c r="F83">
+        <v>4.90991178393641</v>
+      </c>
+      <c r="G83">
+        <v>5.040756715021475</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>82</v>
-      </c>
-      <c r="B84">
-        <v>4.481717410221292</v>
+        <v>83</v>
+      </c>
+      <c r="B84" s="2">
+        <v>45231</v>
       </c>
       <c r="C84">
-        <v>4.614407663578153</v>
+        <v>4.460144413937834</v>
       </c>
       <c r="D84">
-        <v>4.744570329211232</v>
+        <v>4.598762805011092</v>
       </c>
       <c r="E84">
-        <v>4.872299904794275</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45200</v>
+        <v>4.734689406010805</v>
+      </c>
+      <c r="F84">
+        <v>4.868026770805666</v>
+      </c>
+      <c r="G84">
+        <v>4.998871701890731</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>83</v>
-      </c>
-      <c r="B85">
-        <v>4.483367629162641</v>
+        <v>84</v>
+      </c>
+      <c r="B85" s="2">
+        <v>45261</v>
       </c>
       <c r="C85">
-        <v>4.617676056340926</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="D85">
-        <v>4.749426071554897</v>
+        <v>4.485017848103989</v>
       </c>
       <c r="E85">
-        <v>4.878713324888952</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45231</v>
+        <v>4.620944449103702</v>
+      </c>
+      <c r="F85">
+        <v>4.754281813898563</v>
+      </c>
+      <c r="G85">
+        <v>4.885126744983627</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>84</v>
-      </c>
-      <c r="B86">
-        <v>4.485017848103989</v>
+        <v>85</v>
+      </c>
+      <c r="B86" s="2">
+        <v>45292</v>
       </c>
       <c r="C86">
-        <v>4.6209444491037</v>
+        <v>4.334672938290411</v>
       </c>
       <c r="D86">
-        <v>4.754281813898562</v>
+        <v>4.493093956659849</v>
       </c>
       <c r="E86">
-        <v>4.885126744983629</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45261</v>
+        <v>4.648438643516664</v>
+      </c>
+      <c r="F86">
+        <v>4.800824203282219</v>
+      </c>
+      <c r="G86">
+        <v>4.950361267379436</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>85</v>
-      </c>
-      <c r="B87">
-        <v>4.486668067045337</v>
+        <v>86</v>
+      </c>
+      <c r="B87" s="2">
+        <v>45323</v>
       </c>
       <c r="C87">
-        <v>4.624212841866473</v>
+        <v>4.328098292648326</v>
       </c>
       <c r="D87">
-        <v>4.759137556242226</v>
+        <v>4.486519311017764</v>
       </c>
       <c r="E87">
-        <v>4.891540165078307</v>
-      </c>
-      <c r="F87" s="2">
-        <v>45292</v>
+        <v>4.641863997874578</v>
+      </c>
+      <c r="F87">
+        <v>4.794249557640134</v>
+      </c>
+      <c r="G87">
+        <v>4.943786621737351</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>86</v>
-      </c>
-      <c r="B88">
-        <v>4.488318285986685</v>
+        <v>87</v>
+      </c>
+      <c r="B88" s="2">
+        <v>45352</v>
       </c>
       <c r="C88">
-        <v>4.627481234629247</v>
+        <v>4.426043520090656</v>
       </c>
       <c r="D88">
-        <v>4.76399329858589</v>
+        <v>4.584464538460094</v>
       </c>
       <c r="E88">
-        <v>4.897953585172984</v>
-      </c>
-      <c r="F88" s="2">
-        <v>45323</v>
+        <v>4.739809225316908</v>
+      </c>
+      <c r="F88">
+        <v>4.892194785082464</v>
+      </c>
+      <c r="G88">
+        <v>5.041731849179681</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>87</v>
-      </c>
-      <c r="B89">
-        <v>4.489968504928034</v>
+        <v>88</v>
+      </c>
+      <c r="B89" s="2">
+        <v>45383</v>
       </c>
       <c r="C89">
-        <v>4.63074962739202</v>
+        <v>4.417635062141249</v>
       </c>
       <c r="D89">
-        <v>4.768849040929555</v>
+        <v>4.576056080510687</v>
       </c>
       <c r="E89">
-        <v>4.904367005267662</v>
-      </c>
-      <c r="F89" s="2">
-        <v>45352</v>
+        <v>4.731400767367502</v>
+      </c>
+      <c r="F89">
+        <v>4.883786327133057</v>
+      </c>
+      <c r="G89">
+        <v>5.033323391230274</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>88</v>
-      </c>
-      <c r="B90">
-        <v>4.491618723869382</v>
+        <v>89</v>
+      </c>
+      <c r="B90" s="2">
+        <v>45413</v>
       </c>
       <c r="C90">
-        <v>4.634018020154794</v>
+        <v>4.456670177669648</v>
       </c>
       <c r="D90">
-        <v>4.77370478327322</v>
+        <v>4.615091196039086</v>
       </c>
       <c r="E90">
-        <v>4.910780425362339</v>
-      </c>
-      <c r="F90" s="2">
-        <v>45383</v>
+        <v>4.7704358828959</v>
+      </c>
+      <c r="F90">
+        <v>4.922821442661456</v>
+      </c>
+      <c r="G90">
+        <v>5.072358506758673</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>89</v>
-      </c>
-      <c r="B91">
-        <v>4.49326894281073</v>
+        <v>90</v>
+      </c>
+      <c r="B91" s="2">
+        <v>45444</v>
       </c>
       <c r="C91">
-        <v>4.637286412917567</v>
+        <v>4.470495282661489</v>
       </c>
       <c r="D91">
-        <v>4.778560525616885</v>
+        <v>4.628916301030928</v>
       </c>
       <c r="E91">
-        <v>4.917193845457016</v>
-      </c>
-      <c r="F91" s="2">
-        <v>45413</v>
+        <v>4.784260987887742</v>
+      </c>
+      <c r="F91">
+        <v>4.936646547653297</v>
+      </c>
+      <c r="G91">
+        <v>5.086183611750514</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>90</v>
-      </c>
-      <c r="B92">
-        <v>4.494919161752079</v>
+        <v>91</v>
+      </c>
+      <c r="B92" s="2">
+        <v>45474</v>
       </c>
       <c r="C92">
-        <v>4.64055480568034</v>
+        <v>4.49423862528081</v>
       </c>
       <c r="D92">
-        <v>4.783416267960549</v>
+        <v>4.652659643650248</v>
       </c>
       <c r="E92">
-        <v>4.923607265551693</v>
-      </c>
-      <c r="F92" s="2">
-        <v>45444</v>
+        <v>4.808004330507062</v>
+      </c>
+      <c r="F92">
+        <v>4.960389890272618</v>
+      </c>
+      <c r="G92">
+        <v>5.109926954369834</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>91</v>
-      </c>
-      <c r="B93">
-        <v>4.496569380693427</v>
+        <v>92</v>
+      </c>
+      <c r="B93" s="2">
+        <v>45505</v>
       </c>
       <c r="C93">
-        <v>4.643823198443114</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="D93">
-        <v>4.788272010304214</v>
+        <v>4.688867658161593</v>
       </c>
       <c r="E93">
-        <v>4.930020685646371</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45474</v>
+        <v>4.844212345018407</v>
+      </c>
+      <c r="F93">
+        <v>4.996597904783963</v>
+      </c>
+      <c r="G93">
+        <v>5.14613496888118</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>92</v>
-      </c>
-      <c r="B94">
-        <v>4.498219599634775</v>
+        <v>93</v>
+      </c>
+      <c r="B94" s="2">
+        <v>45536</v>
       </c>
       <c r="C94">
-        <v>4.647091591205887</v>
+        <v>4.499809670330265</v>
       </c>
       <c r="D94">
-        <v>4.793127752647878</v>
+        <v>4.658230688699703</v>
       </c>
       <c r="E94">
-        <v>4.936434105741048</v>
-      </c>
-      <c r="F94" s="2">
-        <v>45505</v>
+        <v>4.813575375556518</v>
+      </c>
+      <c r="F94">
+        <v>4.965960935322073</v>
+      </c>
+      <c r="G94">
+        <v>5.11549799941929</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>93</v>
-      </c>
-      <c r="B95">
-        <v>4.499869818576124</v>
+        <v>94</v>
+      </c>
+      <c r="B95" s="2">
+        <v>45566</v>
       </c>
       <c r="C95">
-        <v>4.650359983968661</v>
+        <v>4.502029427068578</v>
       </c>
       <c r="D95">
-        <v>4.797983494991543</v>
+        <v>4.660450445438016</v>
       </c>
       <c r="E95">
-        <v>4.942847525835726</v>
-      </c>
-      <c r="F95" s="2">
-        <v>45536</v>
+        <v>4.815795132294831</v>
+      </c>
+      <c r="F95">
+        <v>4.968180692060386</v>
+      </c>
+      <c r="G95">
+        <v>5.117717756157603</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>94</v>
-      </c>
-      <c r="B96">
-        <v>4.501520037517472</v>
+        <v>95</v>
+      </c>
+      <c r="B96" s="2">
+        <v>45597</v>
       </c>
       <c r="C96">
-        <v>4.653628376731434</v>
+        <v>4.460144413937834</v>
       </c>
       <c r="D96">
-        <v>4.802839237335208</v>
+        <v>4.618565432307272</v>
       </c>
       <c r="E96">
-        <v>4.949260945930403</v>
-      </c>
-      <c r="F96" s="2">
-        <v>45566</v>
+        <v>4.773910119164086</v>
+      </c>
+      <c r="F96">
+        <v>4.926295678929642</v>
+      </c>
+      <c r="G96">
+        <v>5.075832743026859</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>95</v>
-      </c>
-      <c r="B97">
-        <v>4.50317025645882</v>
+        <v>96</v>
+      </c>
+      <c r="B97" s="2">
+        <v>45627</v>
       </c>
       <c r="C97">
-        <v>4.656896769494208</v>
+        <v>4.34639945703073</v>
       </c>
       <c r="D97">
-        <v>4.807694979678873</v>
+        <v>4.504820475400169</v>
       </c>
       <c r="E97">
-        <v>4.955674366025081</v>
-      </c>
-      <c r="F97" s="2">
-        <v>45597</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98">
-        <v>96</v>
-      </c>
-      <c r="B98">
-        <v>4.504820475400169</v>
-      </c>
-      <c r="C98">
-        <v>4.660165162256981</v>
-      </c>
-      <c r="D98">
-        <v>4.812550722022537</v>
-      </c>
-      <c r="E98">
-        <v>4.962087786119758</v>
-      </c>
-      <c r="F98" s="2">
-        <v>45627</v>
+        <v>4.660165162256983</v>
+      </c>
+      <c r="F97">
+        <v>4.812550722022539</v>
+      </c>
+      <c r="G97">
+        <v>4.962087786119755</v>
       </c>
     </row>
   </sheetData>
@@ -2341,10 +2614,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2355,1968 +2628,2241 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>lPIM_0pc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>lPIM_2pc</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>lPIM_4pc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lPIM_6pc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>lPIM_8pc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>4.397133371551336</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45658</v>
       </c>
       <c r="C2">
-        <v>4.397133371551336</v>
+        <v>4.394582439711202</v>
       </c>
       <c r="D2">
-        <v>4.397133371551336</v>
+        <v>4.414385067007382</v>
       </c>
       <c r="E2">
-        <v>4.397133371551336</v>
-      </c>
-      <c r="F2" s="2">
-        <v>45627</v>
+        <v>4.433803152864484</v>
+      </c>
+      <c r="F2">
+        <v>4.452851347835178</v>
+      </c>
+      <c r="G2">
+        <v>4.47154348084733</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>4.398783590492684</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45689</v>
       </c>
       <c r="C3">
-        <v>4.400401764314109</v>
+        <v>4.379635103483346</v>
       </c>
       <c r="D3">
-        <v>4.401989113895</v>
+        <v>4.399437730779526</v>
       </c>
       <c r="E3">
-        <v>4.403546791646013</v>
-      </c>
-      <c r="F3" s="2">
-        <v>45658</v>
+        <v>4.418855816636627</v>
+      </c>
+      <c r="F3">
+        <v>4.437904011607322</v>
+      </c>
+      <c r="G3">
+        <v>4.456596144619474</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>4.400433809434032</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45717</v>
       </c>
       <c r="C4">
-        <v>4.403670157076882</v>
+        <v>4.423475692907757</v>
       </c>
       <c r="D4">
-        <v>4.406844856238665</v>
+        <v>4.443278320203937</v>
       </c>
       <c r="E4">
-        <v>4.409960211740691</v>
-      </c>
-      <c r="F4" s="2">
-        <v>45689</v>
+        <v>4.462696406061038</v>
+      </c>
+      <c r="F4">
+        <v>4.481744601031733</v>
+      </c>
+      <c r="G4">
+        <v>4.500436734043885</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>4.402084028375381</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45748</v>
       </c>
       <c r="C5">
-        <v>4.406938549839656</v>
+        <v>4.456325547226226</v>
       </c>
       <c r="D5">
-        <v>4.411700598582329</v>
+        <v>4.476128174522406</v>
       </c>
       <c r="E5">
-        <v>4.416373631835368</v>
-      </c>
-      <c r="F5" s="2">
-        <v>45717</v>
+        <v>4.495546260379507</v>
+      </c>
+      <c r="F5">
+        <v>4.514594455350202</v>
+      </c>
+      <c r="G5">
+        <v>4.533286588362354</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>4.403734247316729</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45778</v>
       </c>
       <c r="C6">
-        <v>4.41020694260243</v>
+        <v>4.493571007620964</v>
       </c>
       <c r="D6">
-        <v>4.416556340925994</v>
+        <v>4.513373634917143</v>
       </c>
       <c r="E6">
-        <v>4.422787051930045</v>
-      </c>
-      <c r="F6" s="2">
-        <v>45748</v>
+        <v>4.532791720774245</v>
+      </c>
+      <c r="F6">
+        <v>4.55183991574494</v>
+      </c>
+      <c r="G6">
+        <v>4.570532048757092</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>4.405384466258077</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45809</v>
       </c>
       <c r="C7">
-        <v>4.413475335365203</v>
+        <v>4.509723178832335</v>
       </c>
       <c r="D7">
-        <v>4.421412083269659</v>
+        <v>4.529525806128515</v>
       </c>
       <c r="E7">
-        <v>4.429200472024722</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45778</v>
+        <v>4.548943891985616</v>
+      </c>
+      <c r="F7">
+        <v>4.567992086956311</v>
+      </c>
+      <c r="G7">
+        <v>4.586684219968463</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>4.407034685199426</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45839</v>
       </c>
       <c r="C8">
-        <v>4.416743728127976</v>
+        <v>4.572202925484229</v>
       </c>
       <c r="D8">
-        <v>4.426267825613324</v>
+        <v>4.592005552780408</v>
       </c>
       <c r="E8">
-        <v>4.4356138921194</v>
-      </c>
-      <c r="F8" s="2">
-        <v>45809</v>
+        <v>4.61142363863751</v>
+      </c>
+      <c r="F8">
+        <v>4.630471833608205</v>
+      </c>
+      <c r="G8">
+        <v>4.649163966620357</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>4.408684904140774</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45870</v>
       </c>
       <c r="C9">
-        <v>4.42001212089075</v>
+        <v>4.588573097950166</v>
       </c>
       <c r="D9">
-        <v>4.431123567956988</v>
+        <v>4.608375725246345</v>
       </c>
       <c r="E9">
-        <v>4.442027312214077</v>
-      </c>
-      <c r="F9" s="2">
-        <v>45839</v>
+        <v>4.627793811103447</v>
+      </c>
+      <c r="F9">
+        <v>4.646842006074142</v>
+      </c>
+      <c r="G9">
+        <v>4.665534139086294</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>4.410335123082122</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45901</v>
       </c>
       <c r="C10">
-        <v>4.423280513653523</v>
+        <v>4.55298012388381</v>
       </c>
       <c r="D10">
-        <v>4.435979310300653</v>
+        <v>4.572782751179989</v>
       </c>
       <c r="E10">
-        <v>4.448440732308755</v>
-      </c>
-      <c r="F10" s="2">
-        <v>45870</v>
+        <v>4.592200837037091</v>
+      </c>
+      <c r="F10">
+        <v>4.611249032007786</v>
+      </c>
+      <c r="G10">
+        <v>4.629941165019938</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>4.41198534202347</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45931</v>
       </c>
       <c r="C11">
-        <v>4.426548906416297</v>
+        <v>4.58504129974513</v>
       </c>
       <c r="D11">
-        <v>4.440835052644317</v>
+        <v>4.604843927041309</v>
       </c>
       <c r="E11">
-        <v>4.454854152403432</v>
-      </c>
-      <c r="F11" s="2">
-        <v>45901</v>
+        <v>4.624262012898411</v>
+      </c>
+      <c r="F11">
+        <v>4.643310207869106</v>
+      </c>
+      <c r="G11">
+        <v>4.662002340881258</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>4.413635560964819</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45962</v>
       </c>
       <c r="C12">
-        <v>4.42981729917907</v>
+        <v>4.503068009197655</v>
       </c>
       <c r="D12">
-        <v>4.445690794987982</v>
+        <v>4.522870636493835</v>
       </c>
       <c r="E12">
-        <v>4.46126757249811</v>
-      </c>
-      <c r="F12" s="2">
-        <v>45931</v>
+        <v>4.542288722350937</v>
+      </c>
+      <c r="F12">
+        <v>4.561336917321631</v>
+      </c>
+      <c r="G12">
+        <v>4.580029050333783</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>4.415285779906167</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45992</v>
       </c>
       <c r="C13">
-        <v>4.433085691941844</v>
+        <v>4.397133371551336</v>
       </c>
       <c r="D13">
-        <v>4.450546537331647</v>
+        <v>4.416935998847515</v>
       </c>
       <c r="E13">
-        <v>4.467680992592786</v>
-      </c>
-      <c r="F13" s="2">
-        <v>45962</v>
+        <v>4.436354084704617</v>
+      </c>
+      <c r="F13">
+        <v>4.455402279675312</v>
+      </c>
+      <c r="G13">
+        <v>4.474094412687464</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>4.416935998847515</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46023</v>
       </c>
       <c r="C14">
-        <v>4.436354084704617</v>
+        <v>4.394582439711202</v>
       </c>
       <c r="D14">
-        <v>4.455402279675312</v>
+        <v>4.434187694303562</v>
       </c>
       <c r="E14">
-        <v>4.474094412687464</v>
-      </c>
-      <c r="F14" s="2">
-        <v>45992</v>
+        <v>4.473023866017765</v>
+      </c>
+      <c r="F14">
+        <v>4.511120255959154</v>
+      </c>
+      <c r="G14">
+        <v>4.548504521983459</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>4.418586217788864</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46054</v>
       </c>
       <c r="C15">
-        <v>4.43962247746739</v>
+        <v>4.379635103483346</v>
       </c>
       <c r="D15">
-        <v>4.460258022018976</v>
+        <v>4.419240358075705</v>
       </c>
       <c r="E15">
-        <v>4.480507832782141</v>
-      </c>
-      <c r="F15" s="2">
-        <v>46023</v>
+        <v>4.458076529789909</v>
+      </c>
+      <c r="F15">
+        <v>4.496172919731298</v>
+      </c>
+      <c r="G15">
+        <v>4.533557185755602</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>4.420236436730212</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46082</v>
       </c>
       <c r="C16">
-        <v>4.442890870230164</v>
+        <v>4.423475692907757</v>
       </c>
       <c r="D16">
-        <v>4.46511376436264</v>
+        <v>4.463080947500116</v>
       </c>
       <c r="E16">
-        <v>4.486921252876819</v>
-      </c>
-      <c r="F16" s="2">
-        <v>46054</v>
+        <v>4.50191711921432</v>
+      </c>
+      <c r="F16">
+        <v>4.540013509155709</v>
+      </c>
+      <c r="G16">
+        <v>4.577397775180013</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>4.42188665567156</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46113</v>
       </c>
       <c r="C17">
-        <v>4.446159262992937</v>
+        <v>4.456325547226226</v>
       </c>
       <c r="D17">
-        <v>4.469969506706305</v>
+        <v>4.495930801818585</v>
       </c>
       <c r="E17">
-        <v>4.493334672971496</v>
-      </c>
-      <c r="F17" s="2">
-        <v>46082</v>
+        <v>4.534766973532789</v>
+      </c>
+      <c r="F17">
+        <v>4.572863363474178</v>
+      </c>
+      <c r="G17">
+        <v>4.610247629498482</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>4.423536874612909</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46143</v>
       </c>
       <c r="C18">
-        <v>4.449427655755711</v>
+        <v>4.493571007620964</v>
       </c>
       <c r="D18">
-        <v>4.47482524904997</v>
+        <v>4.533176262213323</v>
       </c>
       <c r="E18">
-        <v>4.499748093066174</v>
-      </c>
-      <c r="F18" s="2">
-        <v>46113</v>
+        <v>4.572012433927527</v>
+      </c>
+      <c r="F18">
+        <v>4.610108823868916</v>
+      </c>
+      <c r="G18">
+        <v>4.64749308989322</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>4.425187093554257</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46174</v>
       </c>
       <c r="C19">
-        <v>4.452696048518484</v>
+        <v>4.509723178832335</v>
       </c>
       <c r="D19">
-        <v>4.479680991393635</v>
+        <v>4.549328433424694</v>
       </c>
       <c r="E19">
-        <v>4.506161513160851</v>
-      </c>
-      <c r="F19" s="2">
-        <v>46143</v>
+        <v>4.588164605138898</v>
+      </c>
+      <c r="F19">
+        <v>4.626260995080287</v>
+      </c>
+      <c r="G19">
+        <v>4.663645261104591</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>4.426837312495605</v>
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46204</v>
       </c>
       <c r="C20">
-        <v>4.455964441281258</v>
+        <v>4.572202925484229</v>
       </c>
       <c r="D20">
-        <v>4.4845367337373</v>
+        <v>4.611808180076588</v>
       </c>
       <c r="E20">
-        <v>4.512574933255528</v>
-      </c>
-      <c r="F20" s="2">
-        <v>46174</v>
+        <v>4.650644351790792</v>
+      </c>
+      <c r="F20">
+        <v>4.688740741732181</v>
+      </c>
+      <c r="G20">
+        <v>4.726125007756485</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>4.428487531436954</v>
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46235</v>
       </c>
       <c r="C21">
-        <v>4.459232834044031</v>
+        <v>4.588573097950166</v>
       </c>
       <c r="D21">
-        <v>4.489392476080964</v>
+        <v>4.628178352542525</v>
       </c>
       <c r="E21">
-        <v>4.518988353350205</v>
-      </c>
-      <c r="F21" s="2">
-        <v>46204</v>
+        <v>4.667014524256729</v>
+      </c>
+      <c r="F21">
+        <v>4.705110914198118</v>
+      </c>
+      <c r="G21">
+        <v>4.742495180222422</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>4.430137750378302</v>
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46266</v>
       </c>
       <c r="C22">
-        <v>4.462501226806805</v>
+        <v>4.55298012388381</v>
       </c>
       <c r="D22">
-        <v>4.494248218424628</v>
+        <v>4.592585378476169</v>
       </c>
       <c r="E22">
-        <v>4.525401773444883</v>
-      </c>
-      <c r="F22" s="2">
-        <v>46235</v>
+        <v>4.631421550190373</v>
+      </c>
+      <c r="F22">
+        <v>4.669517940131762</v>
+      </c>
+      <c r="G22">
+        <v>4.706902206156066</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>4.43178796931965</v>
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46296</v>
       </c>
       <c r="C23">
-        <v>4.465769619569578</v>
+        <v>4.58504129974513</v>
       </c>
       <c r="D23">
-        <v>4.499103960768293</v>
+        <v>4.624646554337489</v>
       </c>
       <c r="E23">
-        <v>4.53181519353956</v>
-      </c>
-      <c r="F23" s="2">
-        <v>46266</v>
+        <v>4.663482726051693</v>
+      </c>
+      <c r="F23">
+        <v>4.701579115993082</v>
+      </c>
+      <c r="G23">
+        <v>4.738963382017386</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>4.433438188260999</v>
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46327</v>
       </c>
       <c r="C24">
-        <v>4.469038012332351</v>
+        <v>4.503068009197655</v>
       </c>
       <c r="D24">
-        <v>4.503959703111958</v>
+        <v>4.542673263790014</v>
       </c>
       <c r="E24">
-        <v>4.538228613634238</v>
-      </c>
-      <c r="F24" s="2">
-        <v>46296</v>
+        <v>4.581509435504218</v>
+      </c>
+      <c r="F24">
+        <v>4.619605825445607</v>
+      </c>
+      <c r="G24">
+        <v>4.656990091469911</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>4.435088407202347</v>
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46357</v>
       </c>
       <c r="C25">
-        <v>4.472306405095125</v>
+        <v>4.397133371551336</v>
       </c>
       <c r="D25">
-        <v>4.508815445455623</v>
+        <v>4.436738626143695</v>
       </c>
       <c r="E25">
-        <v>4.544642033728915</v>
-      </c>
-      <c r="F25" s="2">
-        <v>46327</v>
+        <v>4.475574797857899</v>
+      </c>
+      <c r="F25">
+        <v>4.513671187799288</v>
+      </c>
+      <c r="G25">
+        <v>4.551055453823592</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>4.436738626143695</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46388</v>
       </c>
       <c r="C26">
-        <v>4.475574797857898</v>
+        <v>4.394582439711202</v>
       </c>
       <c r="D26">
-        <v>4.513671187799288</v>
+        <v>4.453990321599742</v>
       </c>
       <c r="E26">
-        <v>4.551055453823593</v>
-      </c>
-      <c r="F26" s="2">
-        <v>46357</v>
+        <v>4.512244579171047</v>
+      </c>
+      <c r="F26">
+        <v>4.56938916408313</v>
+      </c>
+      <c r="G26">
+        <v>4.625465563119587</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27">
-        <v>4.438388845085043</v>
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46419</v>
       </c>
       <c r="C27">
-        <v>4.478843190620672</v>
+        <v>4.379635103483346</v>
       </c>
       <c r="D27">
-        <v>4.518526930142952</v>
+        <v>4.439042985371885</v>
       </c>
       <c r="E27">
-        <v>4.557468873918269</v>
-      </c>
-      <c r="F27" s="2">
-        <v>46388</v>
+        <v>4.497297242943191</v>
+      </c>
+      <c r="F27">
+        <v>4.554441827855274</v>
+      </c>
+      <c r="G27">
+        <v>4.61051822689173</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>4.440039064026392</v>
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46447</v>
       </c>
       <c r="C28">
-        <v>4.482111583383445</v>
+        <v>4.423475692907757</v>
       </c>
       <c r="D28">
-        <v>4.523382672486616</v>
+        <v>4.482883574796296</v>
       </c>
       <c r="E28">
-        <v>4.563882294012947</v>
-      </c>
-      <c r="F28" s="2">
-        <v>46419</v>
+        <v>4.541137832367601</v>
+      </c>
+      <c r="F28">
+        <v>4.598282417279685</v>
+      </c>
+      <c r="G28">
+        <v>4.654358816316141</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29">
-        <v>4.44168928296774</v>
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46478</v>
       </c>
       <c r="C29">
-        <v>4.485379976146219</v>
+        <v>4.456325547226226</v>
       </c>
       <c r="D29">
-        <v>4.528238414830281</v>
+        <v>4.515733429114765</v>
       </c>
       <c r="E29">
-        <v>4.570295714107624</v>
-      </c>
-      <c r="F29" s="2">
-        <v>46447</v>
+        <v>4.57398768668607</v>
+      </c>
+      <c r="F29">
+        <v>4.631132271598154</v>
+      </c>
+      <c r="G29">
+        <v>4.68720867063461</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30">
-        <v>4.443339501909088</v>
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46508</v>
       </c>
       <c r="C30">
-        <v>4.488648368908992</v>
+        <v>4.493571007620964</v>
       </c>
       <c r="D30">
-        <v>4.533094157173946</v>
+        <v>4.552978889509503</v>
       </c>
       <c r="E30">
-        <v>4.576709134202302</v>
-      </c>
-      <c r="F30" s="2">
-        <v>46478</v>
+        <v>4.611233147080808</v>
+      </c>
+      <c r="F30">
+        <v>4.668377731992892</v>
+      </c>
+      <c r="G30">
+        <v>4.724454131029348</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31">
-        <v>4.444989720850437</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46539</v>
       </c>
       <c r="C31">
-        <v>4.491916761671765</v>
+        <v>4.509723178832335</v>
       </c>
       <c r="D31">
-        <v>4.537949899517611</v>
+        <v>4.569131060720874</v>
       </c>
       <c r="E31">
-        <v>4.583122554296979</v>
-      </c>
-      <c r="F31" s="2">
-        <v>46508</v>
+        <v>4.62738531829218</v>
+      </c>
+      <c r="F31">
+        <v>4.684529903204263</v>
+      </c>
+      <c r="G31">
+        <v>4.740606302240719</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32">
-        <v>4.446639939791785</v>
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46569</v>
       </c>
       <c r="C32">
-        <v>4.495185154434539</v>
+        <v>4.572202925484229</v>
       </c>
       <c r="D32">
-        <v>4.542805641861275</v>
+        <v>4.631610807372768</v>
       </c>
       <c r="E32">
-        <v>4.589535974391657</v>
-      </c>
-      <c r="F32" s="2">
-        <v>46539</v>
+        <v>4.689865064944073</v>
+      </c>
+      <c r="F32">
+        <v>4.747009649856157</v>
+      </c>
+      <c r="G32">
+        <v>4.803086048892613</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33">
-        <v>4.448290158733133</v>
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46600</v>
       </c>
       <c r="C33">
-        <v>4.498453547197313</v>
+        <v>4.588573097950166</v>
       </c>
       <c r="D33">
-        <v>4.54766138420494</v>
+        <v>4.647980979838705</v>
       </c>
       <c r="E33">
-        <v>4.595949394486334</v>
-      </c>
-      <c r="F33" s="2">
-        <v>46569</v>
+        <v>4.70623523741001</v>
+      </c>
+      <c r="F33">
+        <v>4.763379822322094</v>
+      </c>
+      <c r="G33">
+        <v>4.81945622135855</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34">
-        <v>4.449940377674482</v>
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46631</v>
       </c>
       <c r="C34">
-        <v>4.501721939960086</v>
+        <v>4.55298012388381</v>
       </c>
       <c r="D34">
-        <v>4.552517126548604</v>
+        <v>4.612388005772349</v>
       </c>
       <c r="E34">
-        <v>4.602362814581012</v>
-      </c>
-      <c r="F34" s="2">
-        <v>46600</v>
+        <v>4.670642263343654</v>
+      </c>
+      <c r="F34">
+        <v>4.727786848255738</v>
+      </c>
+      <c r="G34">
+        <v>4.783863247292194</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35">
-        <v>4.45159059661583</v>
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46661</v>
       </c>
       <c r="C35">
-        <v>4.504990332722859</v>
+        <v>4.58504129974513</v>
       </c>
       <c r="D35">
-        <v>4.557372868892269</v>
+        <v>4.644449181633669</v>
       </c>
       <c r="E35">
-        <v>4.608776234675688</v>
-      </c>
-      <c r="F35" s="2">
-        <v>46631</v>
+        <v>4.702703439204974</v>
+      </c>
+      <c r="F35">
+        <v>4.759848024117058</v>
+      </c>
+      <c r="G35">
+        <v>4.815924423153514</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36">
-        <v>4.453240815557178</v>
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46692</v>
       </c>
       <c r="C36">
-        <v>4.508258725485633</v>
+        <v>4.503068009197655</v>
       </c>
       <c r="D36">
-        <v>4.562228611235934</v>
+        <v>4.562475891086194</v>
       </c>
       <c r="E36">
-        <v>4.615189654770366</v>
-      </c>
-      <c r="F36" s="2">
-        <v>46661</v>
+        <v>4.6207301486575</v>
+      </c>
+      <c r="F36">
+        <v>4.677874733569583</v>
+      </c>
+      <c r="G36">
+        <v>4.733951132606039</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37">
-        <v>4.454891034498527</v>
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46722</v>
       </c>
       <c r="C37">
-        <v>4.511527118248406</v>
+        <v>4.397133371551336</v>
       </c>
       <c r="D37">
-        <v>4.567084353579599</v>
+        <v>4.456541253439875</v>
       </c>
       <c r="E37">
-        <v>4.621603074865043</v>
-      </c>
-      <c r="F37" s="2">
-        <v>46692</v>
+        <v>4.51479551101118</v>
+      </c>
+      <c r="F37">
+        <v>4.571940095923264</v>
+      </c>
+      <c r="G37">
+        <v>4.62801649495972</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38">
-        <v>4.456541253439875</v>
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46753</v>
       </c>
       <c r="C38">
-        <v>4.514795511011179</v>
+        <v>4.394582439711202</v>
       </c>
       <c r="D38">
-        <v>4.571940095923263</v>
+        <v>4.473792948895921</v>
       </c>
       <c r="E38">
-        <v>4.628016494959721</v>
-      </c>
-      <c r="F38" s="2">
-        <v>46722</v>
+        <v>4.551465292324329</v>
+      </c>
+      <c r="F38">
+        <v>4.627658072207106</v>
+      </c>
+      <c r="G38">
+        <v>4.702426604255715</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39">
-        <v>4.458191472381223</v>
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46784</v>
       </c>
       <c r="C39">
-        <v>4.518063903773953</v>
+        <v>4.379635103483346</v>
       </c>
       <c r="D39">
-        <v>4.576795838266928</v>
+        <v>4.458845612668065</v>
       </c>
       <c r="E39">
-        <v>4.634429915054398</v>
-      </c>
-      <c r="F39" s="2">
-        <v>46753</v>
+        <v>4.536517956096472</v>
+      </c>
+      <c r="F39">
+        <v>4.61271073597925</v>
+      </c>
+      <c r="G39">
+        <v>4.687479268027858</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40">
-        <v>4.459841691322572</v>
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46813</v>
       </c>
       <c r="C40">
-        <v>4.521332296536727</v>
+        <v>4.423475692907757</v>
       </c>
       <c r="D40">
-        <v>4.581651580610592</v>
+        <v>4.502686202092476</v>
       </c>
       <c r="E40">
-        <v>4.640843335149076</v>
-      </c>
-      <c r="F40" s="2">
-        <v>46784</v>
+        <v>4.580358545520883</v>
+      </c>
+      <c r="F40">
+        <v>4.656551325403661</v>
+      </c>
+      <c r="G40">
+        <v>4.731319857452269</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41">
-        <v>4.46149191026392</v>
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46844</v>
       </c>
       <c r="C41">
-        <v>4.5246006892995</v>
+        <v>4.456325547226226</v>
       </c>
       <c r="D41">
-        <v>4.586507322954257</v>
+        <v>4.535536056410945</v>
       </c>
       <c r="E41">
-        <v>4.647256755243752</v>
-      </c>
-      <c r="F41" s="2">
-        <v>46813</v>
+        <v>4.613208399839352</v>
+      </c>
+      <c r="F41">
+        <v>4.68940117972213</v>
+      </c>
+      <c r="G41">
+        <v>4.764169711770738</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42">
-        <v>4.463142129205268</v>
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46874</v>
       </c>
       <c r="C42">
-        <v>4.527869082062273</v>
+        <v>4.493571007620964</v>
       </c>
       <c r="D42">
-        <v>4.591363065297922</v>
+        <v>4.572781516805683</v>
       </c>
       <c r="E42">
-        <v>4.65367017533843</v>
-      </c>
-      <c r="F42" s="2">
-        <v>46844</v>
+        <v>4.65045386023409</v>
+      </c>
+      <c r="F42">
+        <v>4.726646640116868</v>
+      </c>
+      <c r="G42">
+        <v>4.801415172165476</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43">
-        <v>4.464792348146617</v>
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46905</v>
       </c>
       <c r="C43">
-        <v>4.531137474825047</v>
+        <v>4.509723178832335</v>
       </c>
       <c r="D43">
-        <v>4.596218807641586</v>
+        <v>4.588933688017054</v>
       </c>
       <c r="E43">
-        <v>4.660083595433107</v>
-      </c>
-      <c r="F43" s="2">
-        <v>46874</v>
+        <v>4.666606031445461</v>
+      </c>
+      <c r="F43">
+        <v>4.742798811328239</v>
+      </c>
+      <c r="G43">
+        <v>4.817567343376847</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="B44">
-        <v>4.466442567087965</v>
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46935</v>
       </c>
       <c r="C44">
-        <v>4.534405867587821</v>
+        <v>4.572202925484229</v>
       </c>
       <c r="D44">
-        <v>4.601074549985251</v>
+        <v>4.651413434668948</v>
       </c>
       <c r="E44">
-        <v>4.666497015527785</v>
-      </c>
-      <c r="F44" s="2">
-        <v>46905</v>
+        <v>4.729085778097355</v>
+      </c>
+      <c r="F44">
+        <v>4.805278557980133</v>
+      </c>
+      <c r="G44">
+        <v>4.880047090028741</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="B45">
-        <v>4.468092786029313</v>
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46966</v>
       </c>
       <c r="C45">
-        <v>4.537674260350594</v>
+        <v>4.588573097950166</v>
       </c>
       <c r="D45">
-        <v>4.605930292328916</v>
+        <v>4.667783607134885</v>
       </c>
       <c r="E45">
-        <v>4.672910435622462</v>
-      </c>
-      <c r="F45" s="2">
-        <v>46935</v>
+        <v>4.745455950563292</v>
+      </c>
+      <c r="F45">
+        <v>4.82164873044607</v>
+      </c>
+      <c r="G45">
+        <v>4.896417262494678</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="B46">
-        <v>4.469743004970661</v>
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46997</v>
       </c>
       <c r="C46">
-        <v>4.540942653113367</v>
+        <v>4.55298012388381</v>
       </c>
       <c r="D46">
-        <v>4.61078603467258</v>
+        <v>4.632190633068529</v>
       </c>
       <c r="E46">
-        <v>4.67932385571714</v>
-      </c>
-      <c r="F46" s="2">
-        <v>46966</v>
+        <v>4.709862976496936</v>
+      </c>
+      <c r="F46">
+        <v>4.786055756379714</v>
+      </c>
+      <c r="G46">
+        <v>4.860824288428322</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>45</v>
-      </c>
-      <c r="B47">
-        <v>4.47139322391201</v>
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>47027</v>
       </c>
       <c r="C47">
-        <v>4.544211045876141</v>
+        <v>4.58504129974513</v>
       </c>
       <c r="D47">
-        <v>4.615641777016245</v>
+        <v>4.664251808929849</v>
       </c>
       <c r="E47">
-        <v>4.685737275811817</v>
-      </c>
-      <c r="F47" s="2">
-        <v>46997</v>
+        <v>4.741924152358256</v>
+      </c>
+      <c r="F47">
+        <v>4.818116932241034</v>
+      </c>
+      <c r="G47">
+        <v>4.892885464289642</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="B48">
-        <v>4.473043442853358</v>
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>47058</v>
       </c>
       <c r="C48">
-        <v>4.547479438638914</v>
+        <v>4.503068009197655</v>
       </c>
       <c r="D48">
-        <v>4.62049751935991</v>
+        <v>4.582278518382374</v>
       </c>
       <c r="E48">
-        <v>4.692150695906495</v>
-      </c>
-      <c r="F48" s="2">
-        <v>47027</v>
+        <v>4.659950861810781</v>
+      </c>
+      <c r="F48">
+        <v>4.736143641693559</v>
+      </c>
+      <c r="G48">
+        <v>4.810912173742167</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="B49">
-        <v>4.474693661794706</v>
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>47088</v>
       </c>
       <c r="C49">
-        <v>4.550747831401687</v>
+        <v>4.397133371551336</v>
       </c>
       <c r="D49">
-        <v>4.625353261703574</v>
+        <v>4.476343880736055</v>
       </c>
       <c r="E49">
-        <v>4.698564116001172</v>
-      </c>
-      <c r="F49" s="2">
-        <v>47058</v>
+        <v>4.554016224164462</v>
+      </c>
+      <c r="F49">
+        <v>4.63020900404724</v>
+      </c>
+      <c r="G49">
+        <v>4.704977536095848</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="B50">
-        <v>4.476343880736055</v>
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>47119</v>
       </c>
       <c r="C50">
-        <v>4.554016224164461</v>
+        <v>4.394582439711202</v>
       </c>
       <c r="D50">
-        <v>4.630209004047239</v>
+        <v>4.493595576192101</v>
       </c>
       <c r="E50">
-        <v>4.704977536095849</v>
-      </c>
-      <c r="F50" s="2">
-        <v>47088</v>
+        <v>4.59068600547761</v>
+      </c>
+      <c r="F50">
+        <v>4.685926980331082</v>
+      </c>
+      <c r="G50">
+        <v>4.779387645391843</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="B51">
-        <v>4.477994099677403</v>
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>47150</v>
       </c>
       <c r="C51">
-        <v>4.557284616927235</v>
+        <v>4.379635103483346</v>
       </c>
       <c r="D51">
-        <v>4.635064746390904</v>
+        <v>4.478648239964245</v>
       </c>
       <c r="E51">
-        <v>4.711390956190527</v>
-      </c>
-      <c r="F51" s="2">
-        <v>47119</v>
+        <v>4.575738669249754</v>
+      </c>
+      <c r="F51">
+        <v>4.670979644103226</v>
+      </c>
+      <c r="G51">
+        <v>4.764440309163986</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="B52">
-        <v>4.479644318618751</v>
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>47178</v>
       </c>
       <c r="C52">
-        <v>4.560553009690008</v>
+        <v>4.423475692907757</v>
       </c>
       <c r="D52">
-        <v>4.639920488734568</v>
+        <v>4.522488829388656</v>
       </c>
       <c r="E52">
-        <v>4.717804376285204</v>
-      </c>
-      <c r="F52" s="2">
-        <v>47150</v>
+        <v>4.619579258674165</v>
+      </c>
+      <c r="F52">
+        <v>4.714820233527637</v>
+      </c>
+      <c r="G52">
+        <v>4.808280898588397</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="B53">
-        <v>4.4812945375601</v>
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>47209</v>
       </c>
       <c r="C53">
-        <v>4.563821402452781</v>
+        <v>4.456325547226226</v>
       </c>
       <c r="D53">
-        <v>4.644776231078233</v>
+        <v>4.555338683707125</v>
       </c>
       <c r="E53">
-        <v>4.724217796379881</v>
-      </c>
-      <c r="F53" s="2">
-        <v>47178</v>
+        <v>4.652429112992634</v>
+      </c>
+      <c r="F53">
+        <v>4.747670087846106</v>
+      </c>
+      <c r="G53">
+        <v>4.841130752906866</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54">
-        <v>4.482944756501448</v>
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>47239</v>
       </c>
       <c r="C54">
-        <v>4.567089795215555</v>
+        <v>4.493571007620964</v>
       </c>
       <c r="D54">
-        <v>4.649631973421897</v>
+        <v>4.592584144101862</v>
       </c>
       <c r="E54">
-        <v>4.730631216474559</v>
-      </c>
-      <c r="F54" s="2">
-        <v>47209</v>
+        <v>4.689674573387371</v>
+      </c>
+      <c r="F54">
+        <v>4.784915548240844</v>
+      </c>
+      <c r="G54">
+        <v>4.878376213301604</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="B55">
-        <v>4.484594975442796</v>
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>47270</v>
       </c>
       <c r="C55">
-        <v>4.570358187978329</v>
+        <v>4.509723178832335</v>
       </c>
       <c r="D55">
-        <v>4.654487715765562</v>
+        <v>4.608736315313234</v>
       </c>
       <c r="E55">
-        <v>4.737044636569236</v>
-      </c>
-      <c r="F55" s="2">
-        <v>47239</v>
+        <v>4.705826744598743</v>
+      </c>
+      <c r="F55">
+        <v>4.801067719452215</v>
+      </c>
+      <c r="G55">
+        <v>4.894528384512975</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56">
-        <v>4.486245194384145</v>
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>47300</v>
       </c>
       <c r="C56">
-        <v>4.573626580741101</v>
+        <v>4.572202925484229</v>
       </c>
       <c r="D56">
-        <v>4.659343458109227</v>
+        <v>4.671216061965128</v>
       </c>
       <c r="E56">
-        <v>4.743458056663913</v>
-      </c>
-      <c r="F56" s="2">
-        <v>47270</v>
+        <v>4.768306491250637</v>
+      </c>
+      <c r="F56">
+        <v>4.863547466104109</v>
+      </c>
+      <c r="G56">
+        <v>4.957008131164869</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="B57">
-        <v>4.487895413325493</v>
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>47331</v>
       </c>
       <c r="C57">
-        <v>4.576894973503875</v>
+        <v>4.588573097950166</v>
       </c>
       <c r="D57">
-        <v>4.664199200452892</v>
+        <v>4.687586234431064</v>
       </c>
       <c r="E57">
-        <v>4.749871476758591</v>
-      </c>
-      <c r="F57" s="2">
-        <v>47300</v>
+        <v>4.784676663716573</v>
+      </c>
+      <c r="F57">
+        <v>4.879917638570046</v>
+      </c>
+      <c r="G57">
+        <v>4.973378303630806</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="B58">
-        <v>4.489545632266841</v>
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>47362</v>
       </c>
       <c r="C58">
-        <v>4.580163366266649</v>
+        <v>4.55298012388381</v>
       </c>
       <c r="D58">
-        <v>4.669054942796556</v>
+        <v>4.651993260364709</v>
       </c>
       <c r="E58">
-        <v>4.756284896853268</v>
-      </c>
-      <c r="F58" s="2">
-        <v>47331</v>
+        <v>4.749083689650218</v>
+      </c>
+      <c r="F58">
+        <v>4.84432466450369</v>
+      </c>
+      <c r="G58">
+        <v>4.93778532956445</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="B59">
-        <v>4.49119585120819</v>
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>47392</v>
       </c>
       <c r="C59">
-        <v>4.583431759029422</v>
+        <v>4.58504129974513</v>
       </c>
       <c r="D59">
-        <v>4.673910685140221</v>
+        <v>4.684054436226028</v>
       </c>
       <c r="E59">
-        <v>4.762698316947946</v>
-      </c>
-      <c r="F59" s="2">
-        <v>47362</v>
+        <v>4.781144865511537</v>
+      </c>
+      <c r="F59">
+        <v>4.87638584036501</v>
+      </c>
+      <c r="G59">
+        <v>4.96984650542577</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="B60">
-        <v>4.492846070149538</v>
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>47423</v>
       </c>
       <c r="C60">
-        <v>4.586700151792195</v>
+        <v>4.503068009197655</v>
       </c>
       <c r="D60">
-        <v>4.678766427483885</v>
+        <v>4.602081145678554</v>
       </c>
       <c r="E60">
-        <v>4.769111737042623</v>
-      </c>
-      <c r="F60" s="2">
-        <v>47392</v>
+        <v>4.699171574964063</v>
+      </c>
+      <c r="F60">
+        <v>4.794412549817535</v>
+      </c>
+      <c r="G60">
+        <v>4.887873214878296</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="B61">
-        <v>4.494496289090886</v>
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>47453</v>
       </c>
       <c r="C61">
-        <v>4.589968544554969</v>
+        <v>4.397133371551336</v>
       </c>
       <c r="D61">
-        <v>4.68362216982755</v>
+        <v>4.496146508032234</v>
       </c>
       <c r="E61">
-        <v>4.775525157137301</v>
-      </c>
-      <c r="F61" s="2">
-        <v>47423</v>
+        <v>4.593236937317744</v>
+      </c>
+      <c r="F61">
+        <v>4.688477912171216</v>
+      </c>
+      <c r="G61">
+        <v>4.781938577231976</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="B62">
-        <v>4.496146508032234</v>
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>47484</v>
       </c>
       <c r="C62">
-        <v>4.593236937317743</v>
+        <v>4.394582439711202</v>
       </c>
       <c r="D62">
-        <v>4.688477912171215</v>
+        <v>4.513398203488281</v>
       </c>
       <c r="E62">
-        <v>4.781938577231978</v>
-      </c>
-      <c r="F62" s="2">
-        <v>47453</v>
+        <v>4.629906718630892</v>
+      </c>
+      <c r="F62">
+        <v>4.744195888455058</v>
+      </c>
+      <c r="G62">
+        <v>4.856348686527971</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>61</v>
-      </c>
-      <c r="B63">
-        <v>4.497796726973583</v>
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>47515</v>
       </c>
       <c r="C63">
-        <v>4.596505330080515</v>
+        <v>4.379635103483346</v>
       </c>
       <c r="D63">
-        <v>4.69333365451488</v>
+        <v>4.498450867260424</v>
       </c>
       <c r="E63">
-        <v>4.788351997326655</v>
-      </c>
-      <c r="F63" s="2">
-        <v>47484</v>
+        <v>4.614959382403035</v>
+      </c>
+      <c r="F63">
+        <v>4.729248552227202</v>
+      </c>
+      <c r="G63">
+        <v>4.841401350300115</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>62</v>
-      </c>
-      <c r="B64">
-        <v>4.499446945914931</v>
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>47543</v>
       </c>
       <c r="C64">
-        <v>4.599773722843289</v>
+        <v>4.423475692907757</v>
       </c>
       <c r="D64">
-        <v>4.698189396858544</v>
+        <v>4.542291456684835</v>
       </c>
       <c r="E64">
-        <v>4.794765417421332</v>
-      </c>
-      <c r="F64" s="2">
-        <v>47515</v>
+        <v>4.658799971827446</v>
+      </c>
+      <c r="F64">
+        <v>4.773089141651613</v>
+      </c>
+      <c r="G64">
+        <v>4.885241939724525</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>63</v>
-      </c>
-      <c r="B65">
-        <v>4.501097164856279</v>
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>47574</v>
       </c>
       <c r="C65">
-        <v>4.603042115606063</v>
+        <v>4.456325547226226</v>
       </c>
       <c r="D65">
-        <v>4.703045139202208</v>
+        <v>4.575141311003304</v>
       </c>
       <c r="E65">
-        <v>4.80117883751601</v>
-      </c>
-      <c r="F65" s="2">
-        <v>47543</v>
+        <v>4.691649826145915</v>
+      </c>
+      <c r="F65">
+        <v>4.805938995970082</v>
+      </c>
+      <c r="G65">
+        <v>4.918091794042994</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>64</v>
-      </c>
-      <c r="B66">
-        <v>4.502747383797628</v>
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>47604</v>
       </c>
       <c r="C66">
-        <v>4.606310508368836</v>
+        <v>4.493571007620964</v>
       </c>
       <c r="D66">
-        <v>4.707900881545873</v>
+        <v>4.612386771398042</v>
       </c>
       <c r="E66">
-        <v>4.807592257610687</v>
-      </c>
-      <c r="F66" s="2">
-        <v>47574</v>
+        <v>4.728895286540653</v>
+      </c>
+      <c r="F66">
+        <v>4.84318445636482</v>
+      </c>
+      <c r="G66">
+        <v>4.955337254437732</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>65</v>
-      </c>
-      <c r="B67">
-        <v>4.504397602738976</v>
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>47635</v>
       </c>
       <c r="C67">
-        <v>4.609578901131609</v>
+        <v>4.509723178832335</v>
       </c>
       <c r="D67">
-        <v>4.712756623889538</v>
+        <v>4.628538942609413</v>
       </c>
       <c r="E67">
-        <v>4.814005677705365</v>
-      </c>
-      <c r="F67" s="2">
-        <v>47604</v>
+        <v>4.745047457752024</v>
+      </c>
+      <c r="F67">
+        <v>4.859336627576191</v>
+      </c>
+      <c r="G67">
+        <v>4.971489425649104</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>66</v>
-      </c>
-      <c r="B68">
-        <v>4.506047821680324</v>
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>47665</v>
       </c>
       <c r="C68">
-        <v>4.612847293894383</v>
+        <v>4.572202925484229</v>
       </c>
       <c r="D68">
-        <v>4.717612366233203</v>
+        <v>4.691018689261307</v>
       </c>
       <c r="E68">
-        <v>4.820419097800042</v>
-      </c>
-      <c r="F68" s="2">
-        <v>47635</v>
+        <v>4.807527204403918</v>
+      </c>
+      <c r="F68">
+        <v>4.921816374228085</v>
+      </c>
+      <c r="G68">
+        <v>5.033969172300997</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>67</v>
-      </c>
-      <c r="B69">
-        <v>4.507698040621673</v>
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>47696</v>
       </c>
       <c r="C69">
-        <v>4.616115686657157</v>
+        <v>4.588573097950166</v>
       </c>
       <c r="D69">
-        <v>4.722468108576868</v>
+        <v>4.707388861727244</v>
       </c>
       <c r="E69">
-        <v>4.82683251789472</v>
-      </c>
-      <c r="F69" s="2">
-        <v>47665</v>
+        <v>4.823897376869855</v>
+      </c>
+      <c r="F69">
+        <v>4.938186546694022</v>
+      </c>
+      <c r="G69">
+        <v>5.050339344766934</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>68</v>
-      </c>
-      <c r="B70">
-        <v>4.509348259563021</v>
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>47727</v>
       </c>
       <c r="C70">
-        <v>4.619384079419929</v>
+        <v>4.55298012388381</v>
       </c>
       <c r="D70">
-        <v>4.727323850920532</v>
+        <v>4.671795887660888</v>
       </c>
       <c r="E70">
-        <v>4.833245937989396</v>
-      </c>
-      <c r="F70" s="2">
-        <v>47696</v>
+        <v>4.788304402803499</v>
+      </c>
+      <c r="F70">
+        <v>4.902593572627666</v>
+      </c>
+      <c r="G70">
+        <v>5.014746370700578</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>69</v>
-      </c>
-      <c r="B71">
-        <v>4.510998478504369</v>
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>47757</v>
       </c>
       <c r="C71">
-        <v>4.622652472182703</v>
+        <v>4.58504129974513</v>
       </c>
       <c r="D71">
-        <v>4.732179593264196</v>
+        <v>4.703857063522208</v>
       </c>
       <c r="E71">
-        <v>4.839659358084074</v>
-      </c>
-      <c r="F71" s="2">
-        <v>47727</v>
+        <v>4.820365578664819</v>
+      </c>
+      <c r="F71">
+        <v>4.934654748488986</v>
+      </c>
+      <c r="G71">
+        <v>5.046807546561898</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>70</v>
-      </c>
-      <c r="B72">
-        <v>4.512648697445718</v>
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>47788</v>
       </c>
       <c r="C72">
-        <v>4.625920864945477</v>
+        <v>4.503068009197655</v>
       </c>
       <c r="D72">
-        <v>4.737035335607861</v>
+        <v>4.621883772974734</v>
       </c>
       <c r="E72">
-        <v>4.846072778178751</v>
-      </c>
-      <c r="F72" s="2">
-        <v>47757</v>
+        <v>4.738392288117344</v>
+      </c>
+      <c r="F72">
+        <v>4.852681457941511</v>
+      </c>
+      <c r="G72">
+        <v>4.964834256014424</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>71</v>
-      </c>
-      <c r="B73">
-        <v>4.514298916387066</v>
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>47818</v>
       </c>
       <c r="C73">
-        <v>4.629189257708251</v>
+        <v>4.397133371551336</v>
       </c>
       <c r="D73">
-        <v>4.741891077951526</v>
+        <v>4.515949135328414</v>
       </c>
       <c r="E73">
-        <v>4.852486198273429</v>
-      </c>
-      <c r="F73" s="2">
-        <v>47788</v>
+        <v>4.632457650471025</v>
+      </c>
+      <c r="F73">
+        <v>4.746746820295192</v>
+      </c>
+      <c r="G73">
+        <v>4.858899618368104</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>72</v>
-      </c>
-      <c r="B74">
-        <v>4.515949135328414</v>
+        <v>73</v>
+      </c>
+      <c r="B74" s="2">
+        <v>47849</v>
       </c>
       <c r="C74">
-        <v>4.632457650471023</v>
+        <v>4.394582439711202</v>
       </c>
       <c r="D74">
-        <v>4.746746820295191</v>
+        <v>4.533200830784461</v>
       </c>
       <c r="E74">
-        <v>4.858899618368106</v>
-      </c>
-      <c r="F74" s="2">
-        <v>47818</v>
+        <v>4.669127431784173</v>
+      </c>
+      <c r="F74">
+        <v>4.802464796579034</v>
+      </c>
+      <c r="G74">
+        <v>4.933309727664099</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>73</v>
-      </c>
-      <c r="B75">
-        <v>4.517599354269763</v>
+        <v>74</v>
+      </c>
+      <c r="B75" s="2">
+        <v>47880</v>
       </c>
       <c r="C75">
-        <v>4.635726043233797</v>
+        <v>4.379635103483346</v>
       </c>
       <c r="D75">
-        <v>4.751602562638856</v>
+        <v>4.518253494556604</v>
       </c>
       <c r="E75">
-        <v>4.865313038462784</v>
-      </c>
-      <c r="F75" s="2">
-        <v>47849</v>
+        <v>4.654180095556317</v>
+      </c>
+      <c r="F75">
+        <v>4.787517460351178</v>
+      </c>
+      <c r="G75">
+        <v>4.918362391436243</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>74</v>
-      </c>
-      <c r="B76">
-        <v>4.519249573211111</v>
+        <v>75</v>
+      </c>
+      <c r="B76" s="2">
+        <v>47908</v>
       </c>
       <c r="C76">
-        <v>4.638994435996571</v>
+        <v>4.423475692907757</v>
       </c>
       <c r="D76">
-        <v>4.75645830498252</v>
+        <v>4.562094083981015</v>
       </c>
       <c r="E76">
-        <v>4.871726458557461</v>
-      </c>
-      <c r="F76" s="2">
-        <v>47880</v>
+        <v>4.698020684980728</v>
+      </c>
+      <c r="F76">
+        <v>4.831358049775589</v>
+      </c>
+      <c r="G76">
+        <v>4.962202980860654</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>75</v>
-      </c>
-      <c r="B77">
-        <v>4.520899792152459</v>
+        <v>76</v>
+      </c>
+      <c r="B77" s="2">
+        <v>47939</v>
       </c>
       <c r="C77">
-        <v>4.642262828759344</v>
+        <v>4.456325547226226</v>
       </c>
       <c r="D77">
-        <v>4.761314047326184</v>
+        <v>4.594943938299484</v>
       </c>
       <c r="E77">
-        <v>4.878139878652138</v>
-      </c>
-      <c r="F77" s="2">
-        <v>47908</v>
+        <v>4.730870539299197</v>
+      </c>
+      <c r="F77">
+        <v>4.864207904094058</v>
+      </c>
+      <c r="G77">
+        <v>4.995052835179123</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>76</v>
-      </c>
-      <c r="B78">
-        <v>4.522550011093807</v>
+        <v>77</v>
+      </c>
+      <c r="B78" s="2">
+        <v>47969</v>
       </c>
       <c r="C78">
-        <v>4.645531221522117</v>
+        <v>4.493571007620964</v>
       </c>
       <c r="D78">
-        <v>4.766169789669849</v>
+        <v>4.632189398694222</v>
       </c>
       <c r="E78">
-        <v>4.884553298746815</v>
-      </c>
-      <c r="F78" s="2">
-        <v>47939</v>
+        <v>4.768115999693935</v>
+      </c>
+      <c r="F78">
+        <v>4.901453364488796</v>
+      </c>
+      <c r="G78">
+        <v>5.03229829557386</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>77</v>
-      </c>
-      <c r="B79">
-        <v>4.524200230035156</v>
+        <v>78</v>
+      </c>
+      <c r="B79" s="2">
+        <v>48000</v>
       </c>
       <c r="C79">
-        <v>4.648799614284891</v>
+        <v>4.509723178832335</v>
       </c>
       <c r="D79">
-        <v>4.771025532013514</v>
+        <v>4.648341569905593</v>
       </c>
       <c r="E79">
-        <v>4.890966718841493</v>
-      </c>
-      <c r="F79" s="2">
-        <v>47969</v>
+        <v>4.784268170905306</v>
+      </c>
+      <c r="F79">
+        <v>4.917605535700167</v>
+      </c>
+      <c r="G79">
+        <v>5.048450466785232</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>78</v>
-      </c>
-      <c r="B80">
-        <v>4.525850448976504</v>
+        <v>79</v>
+      </c>
+      <c r="B80" s="2">
+        <v>48030</v>
       </c>
       <c r="C80">
-        <v>4.652068007047665</v>
+        <v>4.572202925484229</v>
       </c>
       <c r="D80">
-        <v>4.775881274357179</v>
+        <v>4.710821316557487</v>
       </c>
       <c r="E80">
-        <v>4.89738013893617</v>
-      </c>
-      <c r="F80" s="2">
-        <v>48000</v>
+        <v>4.8467479175572</v>
+      </c>
+      <c r="F80">
+        <v>4.980085282352061</v>
+      </c>
+      <c r="G80">
+        <v>5.110930213437126</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>79</v>
-      </c>
-      <c r="B81">
-        <v>4.527500667917852</v>
+        <v>80</v>
+      </c>
+      <c r="B81" s="2">
+        <v>48061</v>
       </c>
       <c r="C81">
-        <v>4.655336399810437</v>
+        <v>4.588573097950166</v>
       </c>
       <c r="D81">
-        <v>4.780737016700844</v>
+        <v>4.727191489023424</v>
       </c>
       <c r="E81">
-        <v>4.903793559030848</v>
-      </c>
-      <c r="F81" s="2">
-        <v>48030</v>
+        <v>4.863118090023137</v>
+      </c>
+      <c r="F81">
+        <v>4.996455454817998</v>
+      </c>
+      <c r="G81">
+        <v>5.127300385903062</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>80</v>
-      </c>
-      <c r="B82">
-        <v>4.529150886859201</v>
+        <v>81</v>
+      </c>
+      <c r="B82" s="2">
+        <v>48092</v>
       </c>
       <c r="C82">
-        <v>4.658604792573211</v>
+        <v>4.55298012388381</v>
       </c>
       <c r="D82">
-        <v>4.785592759044508</v>
+        <v>4.691598514957068</v>
       </c>
       <c r="E82">
-        <v>4.910206979125525</v>
-      </c>
-      <c r="F82" s="2">
-        <v>48061</v>
+        <v>4.827525115956781</v>
+      </c>
+      <c r="F82">
+        <v>4.960862480751642</v>
+      </c>
+      <c r="G82">
+        <v>5.091707411836706</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>81</v>
-      </c>
-      <c r="B83">
-        <v>4.530801105800549</v>
+        <v>82</v>
+      </c>
+      <c r="B83" s="2">
+        <v>48122</v>
       </c>
       <c r="C83">
-        <v>4.661873185335985</v>
+        <v>4.58504129974513</v>
       </c>
       <c r="D83">
-        <v>4.790448501388172</v>
+        <v>4.723659690818388</v>
       </c>
       <c r="E83">
-        <v>4.916620399220203</v>
-      </c>
-      <c r="F83" s="2">
-        <v>48092</v>
+        <v>4.859586291818101</v>
+      </c>
+      <c r="F83">
+        <v>4.992923656612962</v>
+      </c>
+      <c r="G83">
+        <v>5.123768587698026</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>82</v>
-      </c>
-      <c r="B84">
-        <v>4.532451324741897</v>
+        <v>83</v>
+      </c>
+      <c r="B84" s="2">
+        <v>48153</v>
       </c>
       <c r="C84">
-        <v>4.665141578098758</v>
+        <v>4.503068009197655</v>
       </c>
       <c r="D84">
-        <v>4.795304243731837</v>
+        <v>4.641686400270913</v>
       </c>
       <c r="E84">
-        <v>4.923033819314879</v>
-      </c>
-      <c r="F84" s="2">
-        <v>48122</v>
+        <v>4.777613001270626</v>
+      </c>
+      <c r="F84">
+        <v>4.910950366065487</v>
+      </c>
+      <c r="G84">
+        <v>5.041795297150552</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>83</v>
-      </c>
-      <c r="B85">
-        <v>4.534101543683246</v>
+        <v>84</v>
+      </c>
+      <c r="B85" s="2">
+        <v>48183</v>
       </c>
       <c r="C85">
-        <v>4.668409970861531</v>
+        <v>4.397133371551336</v>
       </c>
       <c r="D85">
-        <v>4.800159986075502</v>
+        <v>4.535751762624594</v>
       </c>
       <c r="E85">
-        <v>4.929447239409557</v>
-      </c>
-      <c r="F85" s="2">
-        <v>48153</v>
+        <v>4.671678363624307</v>
+      </c>
+      <c r="F85">
+        <v>4.805015728419168</v>
+      </c>
+      <c r="G85">
+        <v>4.935860659504232</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>84</v>
-      </c>
-      <c r="B86">
-        <v>4.535751762624594</v>
+        <v>85</v>
+      </c>
+      <c r="B86" s="2">
+        <v>48214</v>
       </c>
       <c r="C86">
-        <v>4.671678363624305</v>
+        <v>4.394582439711202</v>
       </c>
       <c r="D86">
-        <v>4.805015728419167</v>
+        <v>4.55300345808064</v>
       </c>
       <c r="E86">
-        <v>4.935860659504234</v>
-      </c>
-      <c r="F86" s="2">
-        <v>48183</v>
+        <v>4.708348144937455</v>
+      </c>
+      <c r="F86">
+        <v>4.86073370470301</v>
+      </c>
+      <c r="G86">
+        <v>5.010270768800227</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>85</v>
-      </c>
-      <c r="B87">
-        <v>4.537401981565942</v>
+        <v>86</v>
+      </c>
+      <c r="B87" s="2">
+        <v>48245</v>
       </c>
       <c r="C87">
-        <v>4.674946756387079</v>
+        <v>4.379635103483346</v>
       </c>
       <c r="D87">
-        <v>4.809871470762831</v>
+        <v>4.538056121852784</v>
       </c>
       <c r="E87">
-        <v>4.942274079598912</v>
-      </c>
-      <c r="F87" s="2">
-        <v>48214</v>
+        <v>4.693400808709598</v>
+      </c>
+      <c r="F87">
+        <v>4.845786368475154</v>
+      </c>
+      <c r="G87">
+        <v>4.995323432572371</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>86</v>
-      </c>
-      <c r="B88">
-        <v>4.539052200507291</v>
+        <v>87</v>
+      </c>
+      <c r="B88" s="2">
+        <v>48274</v>
       </c>
       <c r="C88">
-        <v>4.678215149149851</v>
+        <v>4.423475692907757</v>
       </c>
       <c r="D88">
-        <v>4.814727213106496</v>
+        <v>4.581896711277195</v>
       </c>
       <c r="E88">
-        <v>4.948687499693589</v>
-      </c>
-      <c r="F88" s="2">
-        <v>48245</v>
+        <v>4.737241398134009</v>
+      </c>
+      <c r="F88">
+        <v>4.889626957899565</v>
+      </c>
+      <c r="G88">
+        <v>5.039164021996782</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>87</v>
-      </c>
-      <c r="B89">
-        <v>4.540702419448639</v>
+        <v>88</v>
+      </c>
+      <c r="B89" s="2">
+        <v>48305</v>
       </c>
       <c r="C89">
-        <v>4.681483541912625</v>
+        <v>4.456325547226226</v>
       </c>
       <c r="D89">
-        <v>4.81958295545016</v>
+        <v>4.614746565595664</v>
       </c>
       <c r="E89">
-        <v>4.955100919788267</v>
-      </c>
-      <c r="F89" s="2">
-        <v>48274</v>
+        <v>4.770091252452478</v>
+      </c>
+      <c r="F89">
+        <v>4.922476812218034</v>
+      </c>
+      <c r="G89">
+        <v>5.072013876315251</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>88</v>
-      </c>
-      <c r="B90">
-        <v>4.542352638389987</v>
+        <v>89</v>
+      </c>
+      <c r="B90" s="2">
+        <v>48335</v>
       </c>
       <c r="C90">
-        <v>4.684751934675399</v>
+        <v>4.493571007620964</v>
       </c>
       <c r="D90">
-        <v>4.824438697793825</v>
+        <v>4.651992025990402</v>
       </c>
       <c r="E90">
-        <v>4.961514339882944</v>
-      </c>
-      <c r="F90" s="2">
-        <v>48305</v>
+        <v>4.807336712847216</v>
+      </c>
+      <c r="F90">
+        <v>4.959722272612772</v>
+      </c>
+      <c r="G90">
+        <v>5.109259336709989</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>89</v>
-      </c>
-      <c r="B91">
-        <v>4.544002857331336</v>
+        <v>90</v>
+      </c>
+      <c r="B91" s="2">
+        <v>48366</v>
       </c>
       <c r="C91">
-        <v>4.688020327438172</v>
+        <v>4.509723178832335</v>
       </c>
       <c r="D91">
-        <v>4.82929444013749</v>
+        <v>4.668144197201773</v>
       </c>
       <c r="E91">
-        <v>4.967927759977622</v>
-      </c>
-      <c r="F91" s="2">
-        <v>48335</v>
+        <v>4.823488884058587</v>
+      </c>
+      <c r="F91">
+        <v>4.975874443824143</v>
+      </c>
+      <c r="G91">
+        <v>5.12541150792136</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>90</v>
-      </c>
-      <c r="B92">
-        <v>4.545653076272684</v>
+        <v>91</v>
+      </c>
+      <c r="B92" s="2">
+        <v>48396</v>
       </c>
       <c r="C92">
-        <v>4.691288720200945</v>
+        <v>4.572202925484229</v>
       </c>
       <c r="D92">
-        <v>4.834150182481155</v>
+        <v>4.730623943853667</v>
       </c>
       <c r="E92">
-        <v>4.974341180072298</v>
-      </c>
-      <c r="F92" s="2">
-        <v>48366</v>
+        <v>4.885968630710481</v>
+      </c>
+      <c r="F92">
+        <v>5.038354190476037</v>
+      </c>
+      <c r="G92">
+        <v>5.187891254573254</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>91</v>
-      </c>
-      <c r="B93">
-        <v>4.547303295214032</v>
+        <v>92</v>
+      </c>
+      <c r="B93" s="2">
+        <v>48427</v>
       </c>
       <c r="C93">
-        <v>4.694557112963719</v>
+        <v>4.588573097950166</v>
       </c>
       <c r="D93">
-        <v>4.839005924824819</v>
+        <v>4.746994116319604</v>
       </c>
       <c r="E93">
-        <v>4.980754600166976</v>
-      </c>
-      <c r="F93" s="2">
-        <v>48396</v>
+        <v>4.902338803176418</v>
+      </c>
+      <c r="F93">
+        <v>5.054724362941974</v>
+      </c>
+      <c r="G93">
+        <v>5.20426142703919</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>92</v>
-      </c>
-      <c r="B94">
-        <v>4.548953514155381</v>
+        <v>93</v>
+      </c>
+      <c r="B94" s="2">
+        <v>48458</v>
       </c>
       <c r="C94">
-        <v>4.697825505726493</v>
+        <v>4.55298012388381</v>
       </c>
       <c r="D94">
-        <v>4.843861667168484</v>
+        <v>4.711401142253248</v>
       </c>
       <c r="E94">
-        <v>4.987168020261653</v>
-      </c>
-      <c r="F94" s="2">
-        <v>48427</v>
+        <v>4.866745829110062</v>
+      </c>
+      <c r="F94">
+        <v>5.019131388875618</v>
+      </c>
+      <c r="G94">
+        <v>5.168668452972835</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>93</v>
-      </c>
-      <c r="B95">
-        <v>4.550603733096729</v>
+        <v>94</v>
+      </c>
+      <c r="B95" s="2">
+        <v>48488</v>
       </c>
       <c r="C95">
-        <v>4.701093898489266</v>
+        <v>4.58504129974513</v>
       </c>
       <c r="D95">
-        <v>4.848717409512148</v>
+        <v>4.743462318114568</v>
       </c>
       <c r="E95">
-        <v>4.993581440356331</v>
-      </c>
-      <c r="F95" s="2">
-        <v>48458</v>
+        <v>4.898807004971382</v>
+      </c>
+      <c r="F95">
+        <v>5.051192564736938</v>
+      </c>
+      <c r="G95">
+        <v>5.200729628834154</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>94</v>
-      </c>
-      <c r="B96">
-        <v>4.552253952038077</v>
+        <v>95</v>
+      </c>
+      <c r="B96" s="2">
+        <v>48519</v>
       </c>
       <c r="C96">
-        <v>4.704362291252039</v>
+        <v>4.503068009197655</v>
       </c>
       <c r="D96">
-        <v>4.853573151855813</v>
+        <v>4.661489027567093</v>
       </c>
       <c r="E96">
-        <v>4.999994860451008</v>
-      </c>
-      <c r="F96" s="2">
-        <v>48488</v>
+        <v>4.816833714423908</v>
+      </c>
+      <c r="F96">
+        <v>4.969219274189463</v>
+      </c>
+      <c r="G96">
+        <v>5.11875633828668</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>95</v>
-      </c>
-      <c r="B97">
-        <v>4.553904170979425</v>
+        <v>96</v>
+      </c>
+      <c r="B97" s="2">
+        <v>48549</v>
       </c>
       <c r="C97">
-        <v>4.707630684014813</v>
+        <v>4.397133371551336</v>
       </c>
       <c r="D97">
-        <v>4.858428894199478</v>
+        <v>4.555554389920774</v>
       </c>
       <c r="E97">
-        <v>5.006408280545686</v>
-      </c>
-      <c r="F97" s="2">
-        <v>48519</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98">
-        <v>96</v>
-      </c>
-      <c r="B98">
-        <v>4.555554389920774</v>
-      </c>
-      <c r="C98">
-        <v>4.710899076777586</v>
-      </c>
-      <c r="D98">
-        <v>4.863284636543142</v>
-      </c>
-      <c r="E98">
-        <v>5.012821700640362</v>
-      </c>
-      <c r="F98" s="2">
-        <v>48549</v>
+        <v>4.710899076777588</v>
+      </c>
+      <c r="F97">
+        <v>4.863284636543144</v>
+      </c>
+      <c r="G97">
+        <v>5.012821700640361</v>
       </c>
     </row>
   </sheetData>

--- a/2025-06-15 New Run/Base de dados/PIM_Forecast_OutputFile.xlsx
+++ b/2025-06-15 New Run/Base de dados/PIM_Forecast_OutputFile.xlsx
@@ -1,25 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bteba\Documents\GitHub\GVAR_toolbox_EE\2025-06-15 New Run\Base de dados\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187E6BEF-8EAE-4DC0-BCBA-C6E0E83DEF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fcast2016" sheetId="1" r:id="rId1"/>
     <sheet name="Fcast2024" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>lPIM_0pc</t>
+  </si>
+  <si>
+    <t>lPIM_2pc</t>
+  </si>
+  <si>
+    <t>lPIM_4pc</t>
+  </si>
+  <si>
+    <t>lPIM_6pc</t>
+  </si>
+  <si>
+    <t>lPIM_8pc</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,13 +100,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -112,7 +152,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -146,6 +186,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -180,9 +221,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -355,51 +397,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.703125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_0pc</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_2pc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_4pc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_6pc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_8pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -410,19 +438,19 @@
         <v>4.334672938290411</v>
       </c>
       <c r="D2">
-        <v>4.354475565586591</v>
+        <v>4.3544755655865908</v>
       </c>
       <c r="E2">
-        <v>4.373893651443693</v>
+        <v>4.3738936514436926</v>
       </c>
       <c r="F2">
         <v>4.392941846414387</v>
       </c>
       <c r="G2">
-        <v>4.411633979426539</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>4.4116339794265391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -430,22 +458,22 @@
         <v>42767</v>
       </c>
       <c r="C3">
-        <v>4.328098292648326</v>
+        <v>4.3280982926483258</v>
       </c>
       <c r="D3">
-        <v>4.347900919944506</v>
+        <v>4.3479009199445056</v>
       </c>
       <c r="E3">
-        <v>4.367319005801607</v>
+        <v>4.3673190058016074</v>
       </c>
       <c r="F3">
-        <v>4.386367200772302</v>
+        <v>4.3863672007723018</v>
       </c>
       <c r="G3">
-        <v>4.405059333784454</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>4.4050593337844539</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -453,22 +481,22 @@
         <v>42795</v>
       </c>
       <c r="C4">
-        <v>4.426043520090656</v>
+        <v>4.4260435200906558</v>
       </c>
       <c r="D4">
-        <v>4.445846147386836</v>
+        <v>4.4458461473868356</v>
       </c>
       <c r="E4">
-        <v>4.465264233243937</v>
+        <v>4.4652642332439374</v>
       </c>
       <c r="F4">
-        <v>4.484312428214632</v>
+        <v>4.4843124282146318</v>
       </c>
       <c r="G4">
-        <v>4.503004561226784</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>4.5030045612267839</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -476,22 +504,22 @@
         <v>42826</v>
       </c>
       <c r="C5">
-        <v>4.417635062141249</v>
+        <v>4.4176350621412492</v>
       </c>
       <c r="D5">
         <v>4.437437689437429</v>
       </c>
       <c r="E5">
-        <v>4.456855775294531</v>
+        <v>4.4568557752945308</v>
       </c>
       <c r="F5">
-        <v>4.475903970265225</v>
+        <v>4.4759039702652252</v>
       </c>
       <c r="G5">
-        <v>4.494596103277377</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>4.4945961032773774</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -499,22 +527,22 @@
         <v>42856</v>
       </c>
       <c r="C6">
-        <v>4.456670177669648</v>
+        <v>4.4566701776696478</v>
       </c>
       <c r="D6">
-        <v>4.476472804965828</v>
+        <v>4.4764728049658276</v>
       </c>
       <c r="E6">
-        <v>4.495890890822929</v>
+        <v>4.4958908908229294</v>
       </c>
       <c r="F6">
-        <v>4.514939085793624</v>
+        <v>4.5149390857936238</v>
       </c>
       <c r="G6">
-        <v>4.533631218805776</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>4.5336312188057759</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -522,22 +550,22 @@
         <v>42887</v>
       </c>
       <c r="C7">
-        <v>4.470495282661489</v>
+        <v>4.4704952826614894</v>
       </c>
       <c r="D7">
-        <v>4.490297909957669</v>
+        <v>4.4902979099576692</v>
       </c>
       <c r="E7">
         <v>4.509715995814771</v>
       </c>
       <c r="F7">
-        <v>4.528764190785465</v>
+        <v>4.5287641907854654</v>
       </c>
       <c r="G7">
-        <v>4.547456323797618</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>4.5474563237976184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A8">
         <v>7</v>
       </c>
@@ -545,22 +573,22 @@
         <v>42917</v>
       </c>
       <c r="C8">
-        <v>4.49423862528081</v>
+        <v>4.4942386252808104</v>
       </c>
       <c r="D8">
-        <v>4.514041252576989</v>
+        <v>4.5140412525769893</v>
       </c>
       <c r="E8">
-        <v>4.533459338434091</v>
+        <v>4.5334593384340911</v>
       </c>
       <c r="F8">
-        <v>4.552507533404786</v>
+        <v>4.5525075334047864</v>
       </c>
       <c r="G8">
-        <v>4.571199666416938</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>4.5711996664169376</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -568,22 +596,22 @@
         <v>42948</v>
       </c>
       <c r="C9">
-        <v>4.530446639792155</v>
+        <v>4.5304466397921548</v>
       </c>
       <c r="D9">
-        <v>4.550249267088335</v>
+        <v>4.5502492670883354</v>
       </c>
       <c r="E9">
-        <v>4.569667352945436</v>
+        <v>4.5696673529454364</v>
       </c>
       <c r="F9">
-        <v>4.588715547916131</v>
+        <v>4.5887155479161308</v>
       </c>
       <c r="G9">
-        <v>4.607407680928283</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>4.6074076809282829</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -594,19 +622,19 @@
         <v>4.499809670330265</v>
       </c>
       <c r="D10">
-        <v>4.519612297626445</v>
+        <v>4.5196122976264448</v>
       </c>
       <c r="E10">
-        <v>4.539030383483547</v>
+        <v>4.5390303834835466</v>
       </c>
       <c r="F10">
         <v>4.558078578454241</v>
       </c>
       <c r="G10">
-        <v>4.576770711466393</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>4.5767707114663931</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A11">
         <v>10</v>
       </c>
@@ -614,22 +642,22 @@
         <v>43009</v>
       </c>
       <c r="C11">
-        <v>4.502029427068578</v>
+        <v>4.5020294270685781</v>
       </c>
       <c r="D11">
-        <v>4.521832054364758</v>
+        <v>4.5218320543647579</v>
       </c>
       <c r="E11">
-        <v>4.54125014022186</v>
+        <v>4.5412501402218597</v>
       </c>
       <c r="F11">
-        <v>4.560298335192554</v>
+        <v>4.5602983351925541</v>
       </c>
       <c r="G11">
-        <v>4.578990468204706</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>4.5789904682047062</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>11</v>
       </c>
@@ -637,22 +665,22 @@
         <v>43040</v>
       </c>
       <c r="C12">
-        <v>4.460144413937834</v>
+        <v>4.4601444139378339</v>
       </c>
       <c r="D12">
-        <v>4.479947041234014</v>
+        <v>4.4799470412340137</v>
       </c>
       <c r="E12">
-        <v>4.499365127091115</v>
+        <v>4.4993651270911146</v>
       </c>
       <c r="F12">
-        <v>4.51841332206181</v>
+        <v>4.5184133220618099</v>
       </c>
       <c r="G12">
         <v>4.537105455073962</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A13">
         <v>12</v>
       </c>
@@ -660,22 +688,22 @@
         <v>43070</v>
       </c>
       <c r="C13">
-        <v>4.34639945703073</v>
+        <v>4.3463994570307296</v>
       </c>
       <c r="D13">
-        <v>4.36620208432691</v>
+        <v>4.3662020843269103</v>
       </c>
       <c r="E13">
-        <v>4.385620170184012</v>
+        <v>4.3856201701840121</v>
       </c>
       <c r="F13">
-        <v>4.404668365154706</v>
+        <v>4.4046683651547056</v>
       </c>
       <c r="G13">
-        <v>4.423360498166859</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>4.4233604981668586</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A14">
         <v>13</v>
       </c>
@@ -686,19 +714,19 @@
         <v>4.334672938290411</v>
       </c>
       <c r="D14">
-        <v>4.374278192882771</v>
+        <v>4.3742781928827714</v>
       </c>
       <c r="E14">
-        <v>4.413114364596974</v>
+        <v>4.4131143645969741</v>
       </c>
       <c r="F14">
         <v>4.451210754538363</v>
       </c>
       <c r="G14">
-        <v>4.488595020562667</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>4.4885950205626672</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A15">
         <v>14</v>
       </c>
@@ -706,22 +734,22 @@
         <v>43132</v>
       </c>
       <c r="C15">
-        <v>4.328098292648326</v>
+        <v>4.3280982926483258</v>
       </c>
       <c r="D15">
-        <v>4.367703547240685</v>
+        <v>4.3677035472406853</v>
       </c>
       <c r="E15">
-        <v>4.406539718954889</v>
+        <v>4.4065397189548889</v>
       </c>
       <c r="F15">
-        <v>4.444636108896278</v>
+        <v>4.4446361088962778</v>
       </c>
       <c r="G15">
         <v>4.482020374920582</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A16">
         <v>15</v>
       </c>
@@ -729,22 +757,22 @@
         <v>43160</v>
       </c>
       <c r="C16">
-        <v>4.426043520090656</v>
+        <v>4.4260435200906558</v>
       </c>
       <c r="D16">
-        <v>4.465648774683015</v>
+        <v>4.4656487746830154</v>
       </c>
       <c r="E16">
         <v>4.504484946397219</v>
       </c>
       <c r="F16">
-        <v>4.542581336338608</v>
+        <v>4.5425813363386078</v>
       </c>
       <c r="G16">
-        <v>4.579965602362912</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>4.5799656023629121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A17">
         <v>16</v>
       </c>
@@ -752,22 +780,22 @@
         <v>43191</v>
       </c>
       <c r="C17">
-        <v>4.417635062141249</v>
+        <v>4.4176350621412492</v>
       </c>
       <c r="D17">
-        <v>4.457240316733609</v>
+        <v>4.4572403167336088</v>
       </c>
       <c r="E17">
-        <v>4.496076488447812</v>
+        <v>4.4960764884478124</v>
       </c>
       <c r="F17">
-        <v>4.534172878389201</v>
+        <v>4.5341728783892012</v>
       </c>
       <c r="G17">
-        <v>4.571557144413505</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>4.5715571444135046</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A18">
         <v>17</v>
       </c>
@@ -775,22 +803,22 @@
         <v>43221</v>
       </c>
       <c r="C18">
-        <v>4.456670177669648</v>
+        <v>4.4566701776696478</v>
       </c>
       <c r="D18">
-        <v>4.496275432262007</v>
+        <v>4.4962754322620073</v>
       </c>
       <c r="E18">
-        <v>4.535111603976211</v>
+        <v>4.5351116039762109</v>
       </c>
       <c r="F18">
-        <v>4.5732079939176</v>
+        <v>4.5732079939175998</v>
       </c>
       <c r="G18">
         <v>4.610592259941904</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A19">
         <v>18</v>
       </c>
@@ -798,22 +826,22 @@
         <v>43252</v>
       </c>
       <c r="C19">
-        <v>4.470495282661489</v>
+        <v>4.4704952826614894</v>
       </c>
       <c r="D19">
         <v>4.510100537253849</v>
       </c>
       <c r="E19">
-        <v>4.548936708968053</v>
+        <v>4.5489367089680526</v>
       </c>
       <c r="F19">
-        <v>4.587033098909441</v>
+        <v>4.5870330989094414</v>
       </c>
       <c r="G19">
-        <v>4.624417364933746</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>4.6244173649337457</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A20">
         <v>19</v>
       </c>
@@ -821,22 +849,22 @@
         <v>43282</v>
       </c>
       <c r="C20">
-        <v>4.49423862528081</v>
+        <v>4.4942386252808104</v>
       </c>
       <c r="D20">
-        <v>4.533843879873169</v>
+        <v>4.5338438798731691</v>
       </c>
       <c r="E20">
-        <v>4.572680051587373</v>
+        <v>4.5726800515873727</v>
       </c>
       <c r="F20">
-        <v>4.610776441528762</v>
+        <v>4.6107764415287624</v>
       </c>
       <c r="G20">
-        <v>4.648160707553066</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>4.6481607075530658</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A21">
         <v>20</v>
       </c>
@@ -844,22 +872,22 @@
         <v>43313</v>
       </c>
       <c r="C21">
-        <v>4.530446639792155</v>
+        <v>4.5304466397921548</v>
       </c>
       <c r="D21">
-        <v>4.570051894384514</v>
+        <v>4.5700518943845143</v>
       </c>
       <c r="E21">
-        <v>4.608888066098718</v>
+        <v>4.6088880660987179</v>
       </c>
       <c r="F21">
-        <v>4.646984456040107</v>
+        <v>4.6469844560401068</v>
       </c>
       <c r="G21">
         <v>4.684368722064411</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A22">
         <v>21</v>
       </c>
@@ -870,19 +898,19 @@
         <v>4.499809670330265</v>
       </c>
       <c r="D22">
-        <v>4.539414924922625</v>
+        <v>4.5394149249226254</v>
       </c>
       <c r="E22">
-        <v>4.578251096636828</v>
+        <v>4.5782510966368282</v>
       </c>
       <c r="F22">
         <v>4.616347486578217</v>
       </c>
       <c r="G22">
-        <v>4.653731752602521</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>4.6537317526025213</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A23">
         <v>22</v>
       </c>
@@ -890,22 +918,22 @@
         <v>43374</v>
       </c>
       <c r="C23">
-        <v>4.502029427068578</v>
+        <v>4.5020294270685781</v>
       </c>
       <c r="D23">
-        <v>4.541634681660938</v>
+        <v>4.5416346816609376</v>
       </c>
       <c r="E23">
-        <v>4.580470853375141</v>
+        <v>4.5804708533751413</v>
       </c>
       <c r="F23">
-        <v>4.61856724331653</v>
+        <v>4.6185672433165301</v>
       </c>
       <c r="G23">
-        <v>4.655951509340834</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>4.6559515093408343</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A24">
         <v>23</v>
       </c>
@@ -913,22 +941,22 @@
         <v>43405</v>
       </c>
       <c r="C24">
-        <v>4.460144413937834</v>
+        <v>4.4601444139378339</v>
       </c>
       <c r="D24">
-        <v>4.499749668530193</v>
+        <v>4.4997496685301934</v>
       </c>
       <c r="E24">
         <v>4.538585840244397</v>
       </c>
       <c r="F24">
-        <v>4.576682230185786</v>
+        <v>4.5766822301857859</v>
       </c>
       <c r="G24">
-        <v>4.61406649621009</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>4.6140664962100901</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A25">
         <v>24</v>
       </c>
@@ -936,22 +964,22 @@
         <v>43435</v>
       </c>
       <c r="C25">
-        <v>4.34639945703073</v>
+        <v>4.3463994570307296</v>
       </c>
       <c r="D25">
         <v>4.38600471162309</v>
       </c>
       <c r="E25">
-        <v>4.424840883337294</v>
+        <v>4.4248408833372936</v>
       </c>
       <c r="F25">
-        <v>4.462937273278683</v>
+        <v>4.4629372732786834</v>
       </c>
       <c r="G25">
-        <v>4.500321539302987</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>4.5003215393029867</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A26">
         <v>25</v>
       </c>
@@ -962,19 +990,19 @@
         <v>4.334672938290411</v>
       </c>
       <c r="D26">
-        <v>4.39408082017895</v>
+        <v>4.3940808201789503</v>
       </c>
       <c r="E26">
-        <v>4.452335077750256</v>
+        <v>4.4523350777502557</v>
       </c>
       <c r="F26">
         <v>4.509479662662339</v>
       </c>
       <c r="G26">
-        <v>4.565556061698795</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>4.5655560616987954</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A27">
         <v>26</v>
       </c>
@@ -982,22 +1010,22 @@
         <v>43497</v>
       </c>
       <c r="C27">
-        <v>4.328098292648326</v>
+        <v>4.3280982926483258</v>
       </c>
       <c r="D27">
-        <v>4.387506174536865</v>
+        <v>4.3875061745368651</v>
       </c>
       <c r="E27">
-        <v>4.445760432108171</v>
+        <v>4.4457604321081714</v>
       </c>
       <c r="F27">
-        <v>4.502905017020254</v>
+        <v>4.5029050170202538</v>
       </c>
       <c r="G27">
-        <v>4.55898141605671</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>4.5589814160567101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1005,22 +1033,22 @@
         <v>43525</v>
       </c>
       <c r="C28">
-        <v>4.426043520090656</v>
+        <v>4.4260435200906558</v>
       </c>
       <c r="D28">
-        <v>4.485451401979195</v>
+        <v>4.4854514019791951</v>
       </c>
       <c r="E28">
-        <v>4.543705659550501</v>
+        <v>4.5437056595505014</v>
       </c>
       <c r="F28">
-        <v>4.600850244462584</v>
+        <v>4.6008502444625838</v>
       </c>
       <c r="G28">
-        <v>4.65692664349904</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>4.6569266434990402</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1028,22 +1056,22 @@
         <v>43556</v>
       </c>
       <c r="C29">
-        <v>4.417635062141249</v>
+        <v>4.4176350621412492</v>
       </c>
       <c r="D29">
-        <v>4.477042944029789</v>
+        <v>4.4770429440297894</v>
       </c>
       <c r="E29">
         <v>4.535297201601094</v>
       </c>
       <c r="F29">
-        <v>4.592441786513177</v>
+        <v>4.5924417865131772</v>
       </c>
       <c r="G29">
-        <v>4.648518185549634</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>4.6485181855496336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1051,22 +1079,22 @@
         <v>43586</v>
       </c>
       <c r="C30">
-        <v>4.456670177669648</v>
+        <v>4.4566701776696478</v>
       </c>
       <c r="D30">
-        <v>4.516078059558187</v>
+        <v>4.5160780595581871</v>
       </c>
       <c r="E30">
-        <v>4.574332317129493</v>
+        <v>4.5743323171294934</v>
       </c>
       <c r="F30">
-        <v>4.631476902041576</v>
+        <v>4.6314769020415758</v>
       </c>
       <c r="G30">
-        <v>4.687553301078032</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>4.6875533010780321</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1074,22 +1102,22 @@
         <v>43617</v>
       </c>
       <c r="C31">
-        <v>4.470495282661489</v>
+        <v>4.4704952826614894</v>
       </c>
       <c r="D31">
-        <v>4.529903164550029</v>
+        <v>4.5299031645500287</v>
       </c>
       <c r="E31">
-        <v>4.588157422121334</v>
+        <v>4.5881574221213342</v>
       </c>
       <c r="F31">
-        <v>4.645302007033417</v>
+        <v>4.6453020070334166</v>
       </c>
       <c r="G31">
-        <v>4.701378406069874</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>4.7013784060698738</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1097,22 +1125,22 @@
         <v>43647</v>
       </c>
       <c r="C32">
-        <v>4.49423862528081</v>
+        <v>4.4942386252808104</v>
       </c>
       <c r="D32">
-        <v>4.553646507169349</v>
+        <v>4.5536465071693488</v>
       </c>
       <c r="E32">
-        <v>4.611900764740654</v>
+        <v>4.6119007647406542</v>
       </c>
       <c r="F32">
-        <v>4.669045349652738</v>
+        <v>4.6690453496527384</v>
       </c>
       <c r="G32">
-        <v>4.725121748689194</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>4.7251217486891939</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1120,22 +1148,22 @@
         <v>43678</v>
       </c>
       <c r="C33">
-        <v>4.530446639792155</v>
+        <v>4.5304466397921548</v>
       </c>
       <c r="D33">
-        <v>4.589854521680694</v>
+        <v>4.5898545216806941</v>
       </c>
       <c r="E33">
-        <v>4.648108779252</v>
+        <v>4.6481087792520004</v>
       </c>
       <c r="F33">
-        <v>4.705253364164083</v>
+        <v>4.7052533641640828</v>
       </c>
       <c r="G33">
-        <v>4.761329763200539</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>4.7613297632005391</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1146,19 +1174,19 @@
         <v>4.499809670330265</v>
       </c>
       <c r="D34">
-        <v>4.559217552218804</v>
+        <v>4.5592175522188043</v>
       </c>
       <c r="E34">
-        <v>4.61747180979011</v>
+        <v>4.6174718097901097</v>
       </c>
       <c r="F34">
         <v>4.674616394702193</v>
       </c>
       <c r="G34">
-        <v>4.730692793738649</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>4.7306927937386494</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1166,22 +1194,22 @@
         <v>43739</v>
       </c>
       <c r="C35">
-        <v>4.502029427068578</v>
+        <v>4.5020294270685781</v>
       </c>
       <c r="D35">
-        <v>4.561437308957117</v>
+        <v>4.5614373089571174</v>
       </c>
       <c r="E35">
-        <v>4.619691566528423</v>
+        <v>4.6196915665284228</v>
       </c>
       <c r="F35">
-        <v>4.676836151440506</v>
+        <v>4.6768361514405061</v>
       </c>
       <c r="G35">
-        <v>4.732912550476962</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>4.7329125504769616</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1189,22 +1217,22 @@
         <v>43770</v>
       </c>
       <c r="C36">
-        <v>4.460144413937834</v>
+        <v>4.4601444139378339</v>
       </c>
       <c r="D36">
-        <v>4.519552295826373</v>
+        <v>4.5195522958263732</v>
       </c>
       <c r="E36">
-        <v>4.577806553397679</v>
+        <v>4.5778065533976786</v>
       </c>
       <c r="F36">
-        <v>4.634951138309762</v>
+        <v>4.6349511383097619</v>
       </c>
       <c r="G36">
-        <v>4.691027537346218</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>4.6910275373462182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1212,22 +1240,22 @@
         <v>43800</v>
       </c>
       <c r="C37">
-        <v>4.34639945703073</v>
+        <v>4.3463994570307296</v>
       </c>
       <c r="D37">
-        <v>4.40580733891927</v>
+        <v>4.4058073389192698</v>
       </c>
       <c r="E37">
-        <v>4.464061596490575</v>
+        <v>4.4640615964905752</v>
       </c>
       <c r="F37">
-        <v>4.521206181402659</v>
+        <v>4.5212061814026594</v>
       </c>
       <c r="G37">
-        <v>4.577282580439115</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>4.5772825804391148</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1238,19 +1266,19 @@
         <v>4.334672938290411</v>
       </c>
       <c r="D38">
-        <v>4.41388344747513</v>
+        <v>4.4138834474751301</v>
       </c>
       <c r="E38">
-        <v>4.491555790903537</v>
+        <v>4.4915557909035373</v>
       </c>
       <c r="F38">
         <v>4.567748570786315</v>
       </c>
       <c r="G38">
-        <v>4.642517102834923</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>4.6425171028349226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1258,22 +1286,22 @@
         <v>43862</v>
       </c>
       <c r="C39">
-        <v>4.328098292648326</v>
+        <v>4.3280982926483258</v>
       </c>
       <c r="D39">
-        <v>4.407308801833045</v>
+        <v>4.4073088018330449</v>
       </c>
       <c r="E39">
-        <v>4.484981145261452</v>
+        <v>4.4849811452614521</v>
       </c>
       <c r="F39">
-        <v>4.56117392514423</v>
+        <v>4.5611739251442298</v>
       </c>
       <c r="G39">
-        <v>4.635942457192838</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>4.6359424571928383</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1281,22 +1309,22 @@
         <v>43891</v>
       </c>
       <c r="C40">
-        <v>4.426043520090656</v>
+        <v>4.4260435200906558</v>
       </c>
       <c r="D40">
-        <v>4.505254029275375</v>
+        <v>4.5052540292753749</v>
       </c>
       <c r="E40">
-        <v>4.582926372703782</v>
+        <v>4.5829263727037821</v>
       </c>
       <c r="F40">
-        <v>4.65911915258656</v>
+        <v>4.6591191525865598</v>
       </c>
       <c r="G40">
-        <v>4.733887684635168</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>4.7338876846351683</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1304,22 +1332,22 @@
         <v>43922</v>
       </c>
       <c r="C41">
-        <v>4.417635062141249</v>
+        <v>4.4176350621412492</v>
       </c>
       <c r="D41">
-        <v>4.496845571325968</v>
+        <v>4.4968455713259683</v>
       </c>
       <c r="E41">
-        <v>4.574517914754376</v>
+        <v>4.5745179147543764</v>
       </c>
       <c r="F41">
-        <v>4.650710694637153</v>
+        <v>4.6507106946371533</v>
       </c>
       <c r="G41">
-        <v>4.725479226685762</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>4.7254792266857617</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1327,22 +1355,22 @@
         <v>43952</v>
       </c>
       <c r="C42">
-        <v>4.456670177669648</v>
+        <v>4.4566701776696478</v>
       </c>
       <c r="D42">
-        <v>4.535880686854367</v>
+        <v>4.5358806868543669</v>
       </c>
       <c r="E42">
-        <v>4.613553030282774</v>
+        <v>4.6135530302827741</v>
       </c>
       <c r="F42">
-        <v>4.689745810165552</v>
+        <v>4.6897458101655518</v>
       </c>
       <c r="G42">
-        <v>4.76451434221416</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>4.7645143422141603</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1350,22 +1378,22 @@
         <v>43983</v>
       </c>
       <c r="C43">
-        <v>4.470495282661489</v>
+        <v>4.4704952826614894</v>
       </c>
       <c r="D43">
-        <v>4.549705791846208</v>
+        <v>4.5497057918462076</v>
       </c>
       <c r="E43">
-        <v>4.627378135274616</v>
+        <v>4.6273781352746157</v>
       </c>
       <c r="F43">
-        <v>4.703570915157393</v>
+        <v>4.7035709151573926</v>
       </c>
       <c r="G43">
-        <v>4.778339447206002</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>4.7783394472060019</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1373,22 +1401,22 @@
         <v>44013</v>
       </c>
       <c r="C44">
-        <v>4.49423862528081</v>
+        <v>4.4942386252808104</v>
       </c>
       <c r="D44">
-        <v>4.573449134465529</v>
+        <v>4.5734491344655286</v>
       </c>
       <c r="E44">
-        <v>4.651121477893936</v>
+        <v>4.6511214778939358</v>
       </c>
       <c r="F44">
-        <v>4.727314257776714</v>
+        <v>4.7273142577767144</v>
       </c>
       <c r="G44">
         <v>4.802082789825322</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1396,22 +1424,22 @@
         <v>44044</v>
       </c>
       <c r="C45">
-        <v>4.530446639792155</v>
+        <v>4.5304466397921548</v>
       </c>
       <c r="D45">
-        <v>4.609657148976874</v>
+        <v>4.6096571489768738</v>
       </c>
       <c r="E45">
-        <v>4.687329492405281</v>
+        <v>4.6873294924052811</v>
       </c>
       <c r="F45">
-        <v>4.763522272288059</v>
+        <v>4.7635222722880588</v>
       </c>
       <c r="G45">
-        <v>4.838290804336667</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>4.8382908043366673</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1422,19 +1450,19 @@
         <v>4.499809670330265</v>
       </c>
       <c r="D46">
-        <v>4.579020179514984</v>
+        <v>4.5790201795149841</v>
       </c>
       <c r="E46">
-        <v>4.656692522943391</v>
+        <v>4.6566925229433913</v>
       </c>
       <c r="F46">
         <v>4.732885302826169</v>
       </c>
       <c r="G46">
-        <v>4.807653834874777</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>4.8076538348747766</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1442,22 +1470,22 @@
         <v>44105</v>
       </c>
       <c r="C47">
-        <v>4.502029427068578</v>
+        <v>4.5020294270685781</v>
       </c>
       <c r="D47">
-        <v>4.581239936253297</v>
+        <v>4.5812399362532972</v>
       </c>
       <c r="E47">
-        <v>4.658912279681704</v>
+        <v>4.6589122796817044</v>
       </c>
       <c r="F47">
-        <v>4.735105059564482</v>
+        <v>4.7351050595644821</v>
       </c>
       <c r="G47">
-        <v>4.809873591613091</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>4.8098735916130906</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1465,22 +1493,22 @@
         <v>44136</v>
       </c>
       <c r="C48">
-        <v>4.460144413937834</v>
+        <v>4.4601444139378339</v>
       </c>
       <c r="D48">
         <v>4.539354923122553</v>
       </c>
       <c r="E48">
-        <v>4.61702726655096</v>
+        <v>4.6170272665509602</v>
       </c>
       <c r="F48">
-        <v>4.693220046433738</v>
+        <v>4.6932200464337379</v>
       </c>
       <c r="G48">
-        <v>4.767988578482346</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>4.7679885784823464</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1488,22 +1516,22 @@
         <v>44166</v>
       </c>
       <c r="C49">
-        <v>4.34639945703073</v>
+        <v>4.3463994570307296</v>
       </c>
       <c r="D49">
-        <v>4.42560996621545</v>
+        <v>4.4256099662154504</v>
       </c>
       <c r="E49">
-        <v>4.503282309643857</v>
+        <v>4.5032823096438568</v>
       </c>
       <c r="F49">
-        <v>4.579475089526635</v>
+        <v>4.5794750895266354</v>
       </c>
       <c r="G49">
         <v>4.654243621575243</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1514,19 +1542,19 @@
         <v>4.334672938290411</v>
       </c>
       <c r="D50">
-        <v>4.43368607477131</v>
+        <v>4.4336860747713098</v>
       </c>
       <c r="E50">
-        <v>4.530776504056819</v>
+        <v>4.5307765040568189</v>
       </c>
       <c r="F50">
         <v>4.626017478910291</v>
       </c>
       <c r="G50">
-        <v>4.719478143971052</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>4.7194781439710516</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1534,22 +1562,22 @@
         <v>44228</v>
       </c>
       <c r="C51">
-        <v>4.328098292648326</v>
+        <v>4.3280982926483258</v>
       </c>
       <c r="D51">
-        <v>4.427111429129225</v>
+        <v>4.4271114291292246</v>
       </c>
       <c r="E51">
-        <v>4.524201858414734</v>
+        <v>4.5242018584147337</v>
       </c>
       <c r="F51">
-        <v>4.619442833268206</v>
+        <v>4.6194428332682058</v>
       </c>
       <c r="G51">
-        <v>4.712903498328966</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>4.7129034983289664</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1557,22 +1585,22 @@
         <v>44256</v>
       </c>
       <c r="C52">
-        <v>4.426043520090656</v>
+        <v>4.4260435200906558</v>
       </c>
       <c r="D52">
-        <v>4.525056656571555</v>
+        <v>4.5250566565715546</v>
       </c>
       <c r="E52">
-        <v>4.622147085857064</v>
+        <v>4.6221470858570637</v>
       </c>
       <c r="F52">
-        <v>4.717388060710536</v>
+        <v>4.7173880607105358</v>
       </c>
       <c r="G52">
-        <v>4.810848725771296</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>4.8108487257712964</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1580,22 +1608,22 @@
         <v>44287</v>
       </c>
       <c r="C53">
-        <v>4.417635062141249</v>
+        <v>4.4176350621412492</v>
       </c>
       <c r="D53">
-        <v>4.516648198622148</v>
+        <v>4.5166481986221481</v>
       </c>
       <c r="E53">
-        <v>4.613738627907657</v>
+        <v>4.6137386279076571</v>
       </c>
       <c r="F53">
-        <v>4.708979602761129</v>
+        <v>4.7089796027611293</v>
       </c>
       <c r="G53">
-        <v>4.80244026782189</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>4.8024402678218898</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1603,22 +1631,22 @@
         <v>44317</v>
       </c>
       <c r="C54">
-        <v>4.456670177669648</v>
+        <v>4.4566701776696478</v>
       </c>
       <c r="D54">
-        <v>4.555683314150547</v>
+        <v>4.5556833141505466</v>
       </c>
       <c r="E54">
-        <v>4.652773743436056</v>
+        <v>4.6527737434360557</v>
       </c>
       <c r="F54">
-        <v>4.748014718289528</v>
+        <v>4.7480147182895278</v>
       </c>
       <c r="G54">
-        <v>4.841475383350288</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>4.8414753833502884</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1626,22 +1654,22 @@
         <v>44348</v>
       </c>
       <c r="C55">
-        <v>4.470495282661489</v>
+        <v>4.4704952826614894</v>
       </c>
       <c r="D55">
-        <v>4.569508419142388</v>
+        <v>4.5695084191423883</v>
       </c>
       <c r="E55">
-        <v>4.666598848427897</v>
+        <v>4.6665988484278973</v>
       </c>
       <c r="F55">
-        <v>4.761839823281369</v>
+        <v>4.7618398232813686</v>
       </c>
       <c r="G55">
         <v>4.85530048834213</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1649,22 +1677,22 @@
         <v>44378</v>
       </c>
       <c r="C56">
-        <v>4.49423862528081</v>
+        <v>4.4942386252808104</v>
       </c>
       <c r="D56">
-        <v>4.593251761761708</v>
+        <v>4.5932517617617084</v>
       </c>
       <c r="E56">
-        <v>4.690342191047217</v>
+        <v>4.6903421910472174</v>
       </c>
       <c r="F56">
-        <v>4.78558316590069</v>
+        <v>4.7855831659006904</v>
       </c>
       <c r="G56">
-        <v>4.87904383096145</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>4.8790438309614501</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1672,22 +1700,22 @@
         <v>44409</v>
       </c>
       <c r="C57">
-        <v>4.530446639792155</v>
+        <v>4.5304466397921548</v>
       </c>
       <c r="D57">
-        <v>4.629459776273054</v>
+        <v>4.6294597762730536</v>
       </c>
       <c r="E57">
-        <v>4.726550205558563</v>
+        <v>4.7265502055585626</v>
       </c>
       <c r="F57">
-        <v>4.821791180412035</v>
+        <v>4.8217911804120348</v>
       </c>
       <c r="G57">
-        <v>4.915251845472795</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>4.9152518454727954</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1698,19 +1726,19 @@
         <v>4.499809670330265</v>
       </c>
       <c r="D58">
-        <v>4.598822806811164</v>
+        <v>4.5988228068111638</v>
       </c>
       <c r="E58">
-        <v>4.695913236096673</v>
+        <v>4.6959132360966729</v>
       </c>
       <c r="F58">
         <v>4.791154210950145</v>
       </c>
       <c r="G58">
-        <v>4.884614876010906</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>4.8846148760109056</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1718,22 +1746,22 @@
         <v>44470</v>
       </c>
       <c r="C59">
-        <v>4.502029427068578</v>
+        <v>4.5020294270685781</v>
       </c>
       <c r="D59">
-        <v>4.601042563549477</v>
+        <v>4.6010425635494769</v>
       </c>
       <c r="E59">
         <v>4.698132992834986</v>
       </c>
       <c r="F59">
-        <v>4.793373967688458</v>
+        <v>4.7933739676884581</v>
       </c>
       <c r="G59">
-        <v>4.886834632749219</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>4.8868346327492187</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1741,22 +1769,22 @@
         <v>44501</v>
       </c>
       <c r="C60">
-        <v>4.460144413937834</v>
+        <v>4.4601444139378339</v>
       </c>
       <c r="D60">
-        <v>4.559157550418733</v>
+        <v>4.5591575504187327</v>
       </c>
       <c r="E60">
-        <v>4.656247979704242</v>
+        <v>4.6562479797042418</v>
       </c>
       <c r="F60">
-        <v>4.751488954557714</v>
+        <v>4.7514889545577139</v>
       </c>
       <c r="G60">
-        <v>4.844949619618474</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>4.8449496196184736</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1764,22 +1792,22 @@
         <v>44531</v>
       </c>
       <c r="C61">
-        <v>4.34639945703073</v>
+        <v>4.3463994570307296</v>
       </c>
       <c r="D61">
-        <v>4.445412593511629</v>
+        <v>4.4454125935116293</v>
       </c>
       <c r="E61">
-        <v>4.542503022797138</v>
+        <v>4.5425030227971384</v>
       </c>
       <c r="F61">
-        <v>4.637743997650611</v>
+        <v>4.6377439976506114</v>
       </c>
       <c r="G61">
-        <v>4.731204662711371</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>4.7312046627113711</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1790,19 +1818,19 @@
         <v>4.334672938290411</v>
       </c>
       <c r="D62">
-        <v>4.45348870206749</v>
+        <v>4.4534887020674896</v>
       </c>
       <c r="E62">
-        <v>4.5699972172101</v>
+        <v>4.5699972172101004</v>
       </c>
       <c r="F62">
         <v>4.684286387034267</v>
       </c>
       <c r="G62">
-        <v>4.79643918510718</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>4.7964391851071797</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1810,22 +1838,22 @@
         <v>44593</v>
       </c>
       <c r="C63">
-        <v>4.328098292648326</v>
+        <v>4.3280982926483258</v>
       </c>
       <c r="D63">
-        <v>4.446914056425404</v>
+        <v>4.4469140564254044</v>
       </c>
       <c r="E63">
-        <v>4.563422571568015</v>
+        <v>4.5634225715680152</v>
       </c>
       <c r="F63">
-        <v>4.677711741392182</v>
+        <v>4.6777117413921818</v>
       </c>
       <c r="G63">
-        <v>4.789864539465094</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>4.7898645394650936</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1833,22 +1861,22 @@
         <v>44621</v>
       </c>
       <c r="C64">
-        <v>4.426043520090656</v>
+        <v>4.4260435200906558</v>
       </c>
       <c r="D64">
-        <v>4.544859283867734</v>
+        <v>4.5448592838677344</v>
       </c>
       <c r="E64">
-        <v>4.661367799010345</v>
+        <v>4.6613677990103453</v>
       </c>
       <c r="F64">
-        <v>4.775656968834512</v>
+        <v>4.7756569688345119</v>
       </c>
       <c r="G64">
-        <v>4.887809766907425</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>4.8878097669074254</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1856,22 +1884,22 @@
         <v>44652</v>
       </c>
       <c r="C65">
-        <v>4.417635062141249</v>
+        <v>4.4176350621412492</v>
       </c>
       <c r="D65">
-        <v>4.536450825918328</v>
+        <v>4.5364508259183278</v>
       </c>
       <c r="E65">
-        <v>4.652959341060939</v>
+        <v>4.6529593410609387</v>
       </c>
       <c r="F65">
-        <v>4.767248510885105</v>
+        <v>4.7672485108851053</v>
       </c>
       <c r="G65">
-        <v>4.879401308958018</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>4.8794013089580179</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1879,22 +1907,22 @@
         <v>44682</v>
       </c>
       <c r="C66">
-        <v>4.456670177669648</v>
+        <v>4.4566701776696478</v>
       </c>
       <c r="D66">
-        <v>4.575485941446726</v>
+        <v>4.5754859414467264</v>
       </c>
       <c r="E66">
-        <v>4.691994456589337</v>
+        <v>4.6919944565893372</v>
       </c>
       <c r="F66">
-        <v>4.806283626413504</v>
+        <v>4.8062836264135038</v>
       </c>
       <c r="G66">
-        <v>4.918436424486416</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>4.9184364244864156</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1902,22 +1930,22 @@
         <v>44713</v>
       </c>
       <c r="C67">
-        <v>4.470495282661489</v>
+        <v>4.4704952826614894</v>
       </c>
       <c r="D67">
         <v>4.589311046438568</v>
       </c>
       <c r="E67">
-        <v>4.705819561581179</v>
+        <v>4.7058195615811789</v>
       </c>
       <c r="F67">
-        <v>4.820108731405345</v>
+        <v>4.8201087314053446</v>
       </c>
       <c r="G67">
-        <v>4.932261529478258</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>4.9322615294782581</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1925,22 +1953,22 @@
         <v>44743</v>
       </c>
       <c r="C68">
-        <v>4.49423862528081</v>
+        <v>4.4942386252808104</v>
       </c>
       <c r="D68">
-        <v>4.613054389057888</v>
+        <v>4.6130543890578881</v>
       </c>
       <c r="E68">
         <v>4.729562904200499</v>
       </c>
       <c r="F68">
-        <v>4.843852074024666</v>
+        <v>4.8438520740246664</v>
       </c>
       <c r="G68">
-        <v>4.956004872097578</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>4.9560048720975782</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1948,22 +1976,22 @@
         <v>44774</v>
       </c>
       <c r="C69">
-        <v>4.530446639792155</v>
+        <v>4.5304466397921548</v>
       </c>
       <c r="D69">
-        <v>4.649262403569233</v>
+        <v>4.6492624035692334</v>
       </c>
       <c r="E69">
-        <v>4.765770918711844</v>
+        <v>4.7657709187118442</v>
       </c>
       <c r="F69">
-        <v>4.880060088536011</v>
+        <v>4.8800600885360108</v>
       </c>
       <c r="G69">
-        <v>4.992212886608923</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>4.9922128866089226</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1974,19 +2002,19 @@
         <v>4.499809670330265</v>
       </c>
       <c r="D70">
-        <v>4.618625434107344</v>
+        <v>4.6186254341073436</v>
       </c>
       <c r="E70">
-        <v>4.735133949249954</v>
+        <v>4.7351339492499536</v>
       </c>
       <c r="F70">
         <v>4.849423119074121</v>
       </c>
       <c r="G70">
-        <v>4.961575917147034</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>4.9615759171470337</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1994,22 +2022,22 @@
         <v>44835</v>
       </c>
       <c r="C71">
-        <v>4.502029427068578</v>
+        <v>4.5020294270685781</v>
       </c>
       <c r="D71">
-        <v>4.620845190845657</v>
+        <v>4.6208451908456567</v>
       </c>
       <c r="E71">
-        <v>4.737353705988268</v>
+        <v>4.7373537059882684</v>
       </c>
       <c r="F71">
-        <v>4.851642875812434</v>
+        <v>4.8516428758124341</v>
       </c>
       <c r="G71">
-        <v>4.963795673885347</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>4.9637956738853468</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2017,22 +2045,22 @@
         <v>44866</v>
       </c>
       <c r="C72">
-        <v>4.460144413937834</v>
+        <v>4.4601444139378339</v>
       </c>
       <c r="D72">
-        <v>4.578960177714912</v>
+        <v>4.5789601777149116</v>
       </c>
       <c r="E72">
-        <v>4.695468692857523</v>
+        <v>4.6954686928575233</v>
       </c>
       <c r="F72">
-        <v>4.80975786268169</v>
+        <v>4.8097578626816899</v>
       </c>
       <c r="G72">
-        <v>4.921910660754603</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>4.9219106607546026</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2040,22 +2068,22 @@
         <v>44896</v>
       </c>
       <c r="C73">
-        <v>4.34639945703073</v>
+        <v>4.3463994570307296</v>
       </c>
       <c r="D73">
-        <v>4.465215220807809</v>
+        <v>4.4652152208078091</v>
       </c>
       <c r="E73">
-        <v>4.58172373595042</v>
+        <v>4.5817237359504199</v>
       </c>
       <c r="F73">
-        <v>4.696012905774587</v>
+        <v>4.6960129057745874</v>
       </c>
       <c r="G73">
-        <v>4.808165703847499</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>4.8081657038474992</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2066,7 +2094,7 @@
         <v>4.334672938290411</v>
       </c>
       <c r="D74">
-        <v>4.473291329363669</v>
+        <v>4.4732913293636694</v>
       </c>
       <c r="E74">
         <v>4.609217930363382</v>
@@ -2075,10 +2103,10 @@
         <v>4.742555295158243</v>
       </c>
       <c r="G74">
-        <v>4.873400226243308</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>4.8734002262433078</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2086,22 +2114,22 @@
         <v>44958</v>
       </c>
       <c r="C75">
-        <v>4.328098292648326</v>
+        <v>4.3280982926483258</v>
       </c>
       <c r="D75">
-        <v>4.466716683721584</v>
+        <v>4.4667166837215841</v>
       </c>
       <c r="E75">
-        <v>4.602643284721297</v>
+        <v>4.6026432847212968</v>
       </c>
       <c r="F75">
-        <v>4.735980649516158</v>
+        <v>4.7359806495161578</v>
       </c>
       <c r="G75">
-        <v>4.866825580601223</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>4.8668255806012226</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2109,22 +2137,22 @@
         <v>44986</v>
       </c>
       <c r="C76">
-        <v>4.426043520090656</v>
+        <v>4.4260435200906558</v>
       </c>
       <c r="D76">
-        <v>4.564661911163914</v>
+        <v>4.5646619111639142</v>
       </c>
       <c r="E76">
-        <v>4.700588512163627</v>
+        <v>4.7005885121636268</v>
       </c>
       <c r="F76">
-        <v>4.833925876958488</v>
+        <v>4.8339258769584879</v>
       </c>
       <c r="G76">
-        <v>4.964770808043553</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>4.9647708080435526</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2132,22 +2160,22 @@
         <v>45017</v>
       </c>
       <c r="C77">
-        <v>4.417635062141249</v>
+        <v>4.4176350621412492</v>
       </c>
       <c r="D77">
-        <v>4.556253453214508</v>
+        <v>4.5562534532145076</v>
       </c>
       <c r="E77">
-        <v>4.69218005421422</v>
+        <v>4.6921800542142202</v>
       </c>
       <c r="F77">
-        <v>4.825517419009081</v>
+        <v>4.8255174190090813</v>
       </c>
       <c r="G77">
-        <v>4.956362350094146</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>4.9563623500941461</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2155,22 +2183,22 @@
         <v>45047</v>
       </c>
       <c r="C78">
-        <v>4.456670177669648</v>
+        <v>4.4566701776696478</v>
       </c>
       <c r="D78">
-        <v>4.595288568742906</v>
+        <v>4.5952885687429061</v>
       </c>
       <c r="E78">
-        <v>4.731215169742619</v>
+        <v>4.7312151697426188</v>
       </c>
       <c r="F78">
-        <v>4.86455253453748</v>
+        <v>4.8645525345374798</v>
       </c>
       <c r="G78">
-        <v>4.995397465622545</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>4.9953974656225446</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2178,22 +2206,22 @@
         <v>45078</v>
       </c>
       <c r="C79">
-        <v>4.470495282661489</v>
+        <v>4.4704952826614894</v>
       </c>
       <c r="D79">
-        <v>4.609113673734748</v>
+        <v>4.6091136737347478</v>
       </c>
       <c r="E79">
-        <v>4.74504027473446</v>
+        <v>4.7450402747344604</v>
       </c>
       <c r="F79">
-        <v>4.878377639529321</v>
+        <v>4.8783776395293206</v>
       </c>
       <c r="G79">
-        <v>5.009222570614386</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>5.0092225706143862</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2201,22 +2229,22 @@
         <v>45108</v>
       </c>
       <c r="C80">
-        <v>4.49423862528081</v>
+        <v>4.4942386252808104</v>
       </c>
       <c r="D80">
-        <v>4.632857016354068</v>
+        <v>4.6328570163540679</v>
       </c>
       <c r="E80">
-        <v>4.768783617353781</v>
+        <v>4.7687836173537814</v>
       </c>
       <c r="F80">
-        <v>4.902120982148642</v>
+        <v>4.9021209821486416</v>
       </c>
       <c r="G80">
-        <v>5.032965913233706</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>5.0329659132337063</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2224,22 +2252,22 @@
         <v>45139</v>
       </c>
       <c r="C81">
-        <v>4.530446639792155</v>
+        <v>4.5304466397921548</v>
       </c>
       <c r="D81">
-        <v>4.669065030865413</v>
+        <v>4.6690650308654131</v>
       </c>
       <c r="E81">
-        <v>4.804991631865126</v>
+        <v>4.8049916318651258</v>
       </c>
       <c r="F81">
-        <v>4.938328996659987</v>
+        <v>4.9383289966599868</v>
       </c>
       <c r="G81">
-        <v>5.069173927745052</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>5.0691739277450516</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2250,19 +2278,19 @@
         <v>4.499809670330265</v>
       </c>
       <c r="D82">
-        <v>4.638428061403523</v>
+        <v>4.6384280614035234</v>
       </c>
       <c r="E82">
         <v>4.774354662403236</v>
       </c>
       <c r="F82">
-        <v>4.907692027198097</v>
+        <v>4.9076920271980971</v>
       </c>
       <c r="G82">
-        <v>5.038536958283162</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>5.0385369582831618</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2270,22 +2298,22 @@
         <v>45200</v>
       </c>
       <c r="C83">
-        <v>4.502029427068578</v>
+        <v>4.5020294270685781</v>
       </c>
       <c r="D83">
-        <v>4.640647818141836</v>
+        <v>4.6406478181418356</v>
       </c>
       <c r="E83">
-        <v>4.776574419141549</v>
+        <v>4.7765744191415491</v>
       </c>
       <c r="F83">
-        <v>4.90991178393641</v>
+        <v>4.9099117839364101</v>
       </c>
       <c r="G83">
-        <v>5.040756715021475</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>5.0407567150214749</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2293,22 +2321,22 @@
         <v>45231</v>
       </c>
       <c r="C84">
-        <v>4.460144413937834</v>
+        <v>4.4601444139378339</v>
       </c>
       <c r="D84">
-        <v>4.598762805011092</v>
+        <v>4.5987628050110922</v>
       </c>
       <c r="E84">
-        <v>4.734689406010805</v>
+        <v>4.7346894060108049</v>
       </c>
       <c r="F84">
-        <v>4.868026770805666</v>
+        <v>4.8680267708056659</v>
       </c>
       <c r="G84">
-        <v>4.998871701890731</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>4.9988717018907307</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2316,22 +2344,22 @@
         <v>45261</v>
       </c>
       <c r="C85">
-        <v>4.34639945703073</v>
+        <v>4.3463994570307296</v>
       </c>
       <c r="D85">
-        <v>4.485017848103989</v>
+        <v>4.4850178481039888</v>
       </c>
       <c r="E85">
-        <v>4.620944449103702</v>
+        <v>4.6209444491037024</v>
       </c>
       <c r="F85">
-        <v>4.754281813898563</v>
+        <v>4.7542818138985634</v>
       </c>
       <c r="G85">
-        <v>4.885126744983627</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>4.8851267449836273</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2342,19 +2370,19 @@
         <v>4.334672938290411</v>
       </c>
       <c r="D86">
-        <v>4.493093956659849</v>
+        <v>4.4930939566598491</v>
       </c>
       <c r="E86">
-        <v>4.648438643516664</v>
+        <v>4.6484386435166636</v>
       </c>
       <c r="F86">
         <v>4.800824203282219</v>
       </c>
       <c r="G86">
-        <v>4.950361267379436</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>4.9503612673794359</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2362,22 +2390,22 @@
         <v>45323</v>
       </c>
       <c r="C87">
-        <v>4.328098292648326</v>
+        <v>4.3280982926483258</v>
       </c>
       <c r="D87">
-        <v>4.486519311017764</v>
+        <v>4.4865193110177639</v>
       </c>
       <c r="E87">
-        <v>4.641863997874578</v>
+        <v>4.6418639978745784</v>
       </c>
       <c r="F87">
-        <v>4.794249557640134</v>
+        <v>4.7942495576401338</v>
       </c>
       <c r="G87">
-        <v>4.943786621737351</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>4.9437866217373507</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2385,22 +2413,22 @@
         <v>45352</v>
       </c>
       <c r="C88">
-        <v>4.426043520090656</v>
+        <v>4.4260435200906558</v>
       </c>
       <c r="D88">
-        <v>4.584464538460094</v>
+        <v>4.5844645384600939</v>
       </c>
       <c r="E88">
-        <v>4.739809225316908</v>
+        <v>4.7398092253169084</v>
       </c>
       <c r="F88">
-        <v>4.892194785082464</v>
+        <v>4.8921947850824639</v>
       </c>
       <c r="G88">
-        <v>5.041731849179681</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>5.0417318491796808</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2408,22 +2436,22 @@
         <v>45383</v>
       </c>
       <c r="C89">
-        <v>4.417635062141249</v>
+        <v>4.4176350621412492</v>
       </c>
       <c r="D89">
-        <v>4.576056080510687</v>
+        <v>4.5760560805106874</v>
       </c>
       <c r="E89">
-        <v>4.731400767367502</v>
+        <v>4.7314007673675018</v>
       </c>
       <c r="F89">
-        <v>4.883786327133057</v>
+        <v>4.8837863271330573</v>
       </c>
       <c r="G89">
-        <v>5.033323391230274</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>5.0333233912302742</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2431,22 +2459,22 @@
         <v>45413</v>
       </c>
       <c r="C90">
-        <v>4.456670177669648</v>
+        <v>4.4566701776696478</v>
       </c>
       <c r="D90">
-        <v>4.615091196039086</v>
+        <v>4.6150911960390859</v>
       </c>
       <c r="E90">
-        <v>4.7704358828959</v>
+        <v>4.7704358828959004</v>
       </c>
       <c r="F90">
-        <v>4.922821442661456</v>
+        <v>4.9228214426614558</v>
       </c>
       <c r="G90">
-        <v>5.072358506758673</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>5.0723585067586727</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2454,22 +2482,22 @@
         <v>45444</v>
       </c>
       <c r="C91">
-        <v>4.470495282661489</v>
+        <v>4.4704952826614894</v>
       </c>
       <c r="D91">
-        <v>4.628916301030928</v>
+        <v>4.6289163010309284</v>
       </c>
       <c r="E91">
         <v>4.784260987887742</v>
       </c>
       <c r="F91">
-        <v>4.936646547653297</v>
+        <v>4.9366465476532966</v>
       </c>
       <c r="G91">
-        <v>5.086183611750514</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>5.0861836117505144</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2477,22 +2505,22 @@
         <v>45474</v>
       </c>
       <c r="C92">
-        <v>4.49423862528081</v>
+        <v>4.4942386252808104</v>
       </c>
       <c r="D92">
-        <v>4.652659643650248</v>
+        <v>4.6526596436502476</v>
       </c>
       <c r="E92">
-        <v>4.808004330507062</v>
+        <v>4.8080043305070621</v>
       </c>
       <c r="F92">
-        <v>4.960389890272618</v>
+        <v>4.9603898902726176</v>
       </c>
       <c r="G92">
-        <v>5.109926954369834</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>5.1099269543698336</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2500,22 +2528,22 @@
         <v>45505</v>
       </c>
       <c r="C93">
-        <v>4.530446639792155</v>
+        <v>4.5304466397921548</v>
       </c>
       <c r="D93">
-        <v>4.688867658161593</v>
+        <v>4.6888676581615929</v>
       </c>
       <c r="E93">
-        <v>4.844212345018407</v>
+        <v>4.8442123450184074</v>
       </c>
       <c r="F93">
-        <v>4.996597904783963</v>
+        <v>4.9965979047839628</v>
       </c>
       <c r="G93">
-        <v>5.14613496888118</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>5.1461349688811797</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2526,19 +2554,19 @@
         <v>4.499809670330265</v>
       </c>
       <c r="D94">
-        <v>4.658230688699703</v>
+        <v>4.6582306886997031</v>
       </c>
       <c r="E94">
-        <v>4.813575375556518</v>
+        <v>4.8135753755565176</v>
       </c>
       <c r="F94">
-        <v>4.965960935322073</v>
+        <v>4.9659609353220731</v>
       </c>
       <c r="G94">
         <v>5.11549799941929</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2546,22 +2574,22 @@
         <v>45566</v>
       </c>
       <c r="C95">
-        <v>4.502029427068578</v>
+        <v>4.5020294270685781</v>
       </c>
       <c r="D95">
-        <v>4.660450445438016</v>
+        <v>4.6604504454380162</v>
       </c>
       <c r="E95">
-        <v>4.815795132294831</v>
+        <v>4.8157951322948307</v>
       </c>
       <c r="F95">
-        <v>4.968180692060386</v>
+        <v>4.9681806920603861</v>
       </c>
       <c r="G95">
         <v>5.117717756157603</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2569,22 +2597,22 @@
         <v>45597</v>
       </c>
       <c r="C96">
-        <v>4.460144413937834</v>
+        <v>4.4601444139378339</v>
       </c>
       <c r="D96">
         <v>4.618565432307272</v>
       </c>
       <c r="E96">
-        <v>4.773910119164086</v>
+        <v>4.7739101191640856</v>
       </c>
       <c r="F96">
-        <v>4.926295678929642</v>
+        <v>4.9262956789296419</v>
       </c>
       <c r="G96">
-        <v>5.075832743026859</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>5.0758327430268588</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2592,19 +2620,19 @@
         <v>45627</v>
       </c>
       <c r="C97">
-        <v>4.34639945703073</v>
+        <v>4.3463994570307296</v>
       </c>
       <c r="D97">
-        <v>4.504820475400169</v>
+        <v>4.5048204754001686</v>
       </c>
       <c r="E97">
-        <v>4.660165162256983</v>
+        <v>4.6601651622569831</v>
       </c>
       <c r="F97">
-        <v>4.812550722022539</v>
+        <v>4.8125507220225394</v>
       </c>
       <c r="G97">
-        <v>4.962087786119755</v>
+        <v>4.9620877861197554</v>
       </c>
     </row>
   </sheetData>
@@ -2613,51 +2641,37 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.703125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_0pc</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_2pc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_4pc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_6pc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>lPIM_8pc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2665,22 +2679,22 @@
         <v>45658</v>
       </c>
       <c r="C2">
-        <v>4.394582439711202</v>
+        <v>4.3945824397112023</v>
       </c>
       <c r="D2">
-        <v>4.414385067007382</v>
+        <v>4.4143850670073821</v>
       </c>
       <c r="E2">
-        <v>4.433803152864484</v>
+        <v>4.4338031528644839</v>
       </c>
       <c r="F2">
-        <v>4.452851347835178</v>
+        <v>4.4528513478351783</v>
       </c>
       <c r="G2">
-        <v>4.47154348084733</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>4.4715434808473304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2688,22 +2702,22 @@
         <v>45689</v>
       </c>
       <c r="C3">
-        <v>4.379635103483346</v>
+        <v>4.3796351034833458</v>
       </c>
       <c r="D3">
-        <v>4.399437730779526</v>
+        <v>4.3994377307795256</v>
       </c>
       <c r="E3">
-        <v>4.418855816636627</v>
+        <v>4.4188558166366274</v>
       </c>
       <c r="F3">
-        <v>4.437904011607322</v>
+        <v>4.4379040116073218</v>
       </c>
       <c r="G3">
         <v>4.456596144619474</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2711,22 +2725,22 @@
         <v>45717</v>
       </c>
       <c r="C4">
-        <v>4.423475692907757</v>
+        <v>4.4234756929077568</v>
       </c>
       <c r="D4">
-        <v>4.443278320203937</v>
+        <v>4.4432783202039374</v>
       </c>
       <c r="E4">
-        <v>4.462696406061038</v>
+        <v>4.4626964060610383</v>
       </c>
       <c r="F4">
-        <v>4.481744601031733</v>
+        <v>4.4817446010317328</v>
       </c>
       <c r="G4">
-        <v>4.500436734043885</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>4.5004367340438849</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2734,22 +2748,22 @@
         <v>45748</v>
       </c>
       <c r="C5">
-        <v>4.456325547226226</v>
+        <v>4.4563255472262258</v>
       </c>
       <c r="D5">
-        <v>4.476128174522406</v>
+        <v>4.4761281745224064</v>
       </c>
       <c r="E5">
-        <v>4.495546260379507</v>
+        <v>4.4955462603795073</v>
       </c>
       <c r="F5">
-        <v>4.514594455350202</v>
+        <v>4.5145944553502018</v>
       </c>
       <c r="G5">
-        <v>4.533286588362354</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>4.5332865883623539</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2757,22 +2771,22 @@
         <v>45778</v>
       </c>
       <c r="C6">
-        <v>4.493571007620964</v>
+        <v>4.4935710076209636</v>
       </c>
       <c r="D6">
-        <v>4.513373634917143</v>
+        <v>4.5133736349171434</v>
       </c>
       <c r="E6">
-        <v>4.532791720774245</v>
+        <v>4.5327917207742452</v>
       </c>
       <c r="F6">
-        <v>4.55183991574494</v>
+        <v>4.5518399157449396</v>
       </c>
       <c r="G6">
-        <v>4.570532048757092</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>4.5705320487570917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2780,22 +2794,22 @@
         <v>45809</v>
       </c>
       <c r="C7">
-        <v>4.509723178832335</v>
+        <v>4.5097231788323349</v>
       </c>
       <c r="D7">
-        <v>4.529525806128515</v>
+        <v>4.5295258061285146</v>
       </c>
       <c r="E7">
-        <v>4.548943891985616</v>
+        <v>4.5489438919856164</v>
       </c>
       <c r="F7">
-        <v>4.567992086956311</v>
+        <v>4.5679920869563109</v>
       </c>
       <c r="G7">
         <v>4.586684219968463</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2803,22 +2817,22 @@
         <v>45839</v>
       </c>
       <c r="C8">
-        <v>4.572202925484229</v>
+        <v>4.5722029254842287</v>
       </c>
       <c r="D8">
-        <v>4.592005552780408</v>
+        <v>4.5920055527804076</v>
       </c>
       <c r="E8">
-        <v>4.61142363863751</v>
+        <v>4.6114236386375103</v>
       </c>
       <c r="F8">
-        <v>4.630471833608205</v>
+        <v>4.6304718336082047</v>
       </c>
       <c r="G8">
-        <v>4.649163966620357</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>4.6491639666203568</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2826,22 +2840,22 @@
         <v>45870</v>
       </c>
       <c r="C9">
-        <v>4.588573097950166</v>
+        <v>4.5885730979501664</v>
       </c>
       <c r="D9">
-        <v>4.608375725246345</v>
+        <v>4.6083757252463453</v>
       </c>
       <c r="E9">
-        <v>4.627793811103447</v>
+        <v>4.6277938111034471</v>
       </c>
       <c r="F9">
-        <v>4.646842006074142</v>
+        <v>4.6468420060741424</v>
       </c>
       <c r="G9">
-        <v>4.665534139086294</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>4.6655341390862937</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2849,22 +2863,22 @@
         <v>45901</v>
       </c>
       <c r="C10">
-        <v>4.55298012388381</v>
+        <v>4.5529801238838097</v>
       </c>
       <c r="D10">
-        <v>4.572782751179989</v>
+        <v>4.5727827511799886</v>
       </c>
       <c r="E10">
-        <v>4.592200837037091</v>
+        <v>4.5922008370370913</v>
       </c>
       <c r="F10">
-        <v>4.611249032007786</v>
+        <v>4.6112490320077857</v>
       </c>
       <c r="G10">
-        <v>4.629941165019938</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>4.6299411650199378</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2872,22 +2886,22 @@
         <v>45931</v>
       </c>
       <c r="C11">
-        <v>4.58504129974513</v>
+        <v>4.5850412997451304</v>
       </c>
       <c r="D11">
-        <v>4.604843927041309</v>
+        <v>4.6048439270413093</v>
       </c>
       <c r="E11">
-        <v>4.624262012898411</v>
+        <v>4.6242620128984111</v>
       </c>
       <c r="F11">
-        <v>4.643310207869106</v>
+        <v>4.6433102078691064</v>
       </c>
       <c r="G11">
-        <v>4.662002340881258</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>4.6620023408812576</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2895,22 +2909,22 @@
         <v>45962</v>
       </c>
       <c r="C12">
-        <v>4.503068009197655</v>
+        <v>4.5030680091976549</v>
       </c>
       <c r="D12">
-        <v>4.522870636493835</v>
+        <v>4.5228706364938347</v>
       </c>
       <c r="E12">
-        <v>4.542288722350937</v>
+        <v>4.5422887223509374</v>
       </c>
       <c r="F12">
-        <v>4.561336917321631</v>
+        <v>4.5613369173216309</v>
       </c>
       <c r="G12">
         <v>4.580029050333783</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2918,22 +2932,22 @@
         <v>45992</v>
       </c>
       <c r="C13">
-        <v>4.397133371551336</v>
+        <v>4.3971333715513357</v>
       </c>
       <c r="D13">
-        <v>4.416935998847515</v>
+        <v>4.4169359988475154</v>
       </c>
       <c r="E13">
-        <v>4.436354084704617</v>
+        <v>4.4363540847046172</v>
       </c>
       <c r="F13">
-        <v>4.455402279675312</v>
+        <v>4.4554022796753117</v>
       </c>
       <c r="G13">
-        <v>4.474094412687464</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>4.4740944126874638</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2941,22 +2955,22 @@
         <v>46023</v>
       </c>
       <c r="C14">
-        <v>4.394582439711202</v>
+        <v>4.3945824397112023</v>
       </c>
       <c r="D14">
-        <v>4.434187694303562</v>
+        <v>4.4341876943035619</v>
       </c>
       <c r="E14">
-        <v>4.473023866017765</v>
+        <v>4.4730238660177646</v>
       </c>
       <c r="F14">
-        <v>4.511120255959154</v>
+        <v>4.5111202559591543</v>
       </c>
       <c r="G14">
-        <v>4.548504521983459</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>4.5485045219834586</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2964,22 +2978,22 @@
         <v>46054</v>
       </c>
       <c r="C15">
-        <v>4.379635103483346</v>
+        <v>4.3796351034833458</v>
       </c>
       <c r="D15">
-        <v>4.419240358075705</v>
+        <v>4.4192403580757054</v>
       </c>
       <c r="E15">
         <v>4.458076529789909</v>
       </c>
       <c r="F15">
-        <v>4.496172919731298</v>
+        <v>4.4961729197312978</v>
       </c>
       <c r="G15">
-        <v>4.533557185755602</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>4.5335571857556021</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2987,22 +3001,22 @@
         <v>46082</v>
       </c>
       <c r="C16">
-        <v>4.423475692907757</v>
+        <v>4.4234756929077568</v>
       </c>
       <c r="D16">
-        <v>4.463080947500116</v>
+        <v>4.4630809475001163</v>
       </c>
       <c r="E16">
-        <v>4.50191711921432</v>
+        <v>4.5019171192143199</v>
       </c>
       <c r="F16">
-        <v>4.540013509155709</v>
+        <v>4.5400135091557088</v>
       </c>
       <c r="G16">
         <v>4.577397775180013</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3010,22 +3024,22 @@
         <v>46113</v>
       </c>
       <c r="C17">
-        <v>4.456325547226226</v>
+        <v>4.4563255472262258</v>
       </c>
       <c r="D17">
-        <v>4.495930801818585</v>
+        <v>4.4959308018185853</v>
       </c>
       <c r="E17">
-        <v>4.534766973532789</v>
+        <v>4.5347669735327889</v>
       </c>
       <c r="F17">
-        <v>4.572863363474178</v>
+        <v>4.5728633634741778</v>
       </c>
       <c r="G17">
         <v>4.610247629498482</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3033,22 +3047,22 @@
         <v>46143</v>
       </c>
       <c r="C18">
-        <v>4.493571007620964</v>
+        <v>4.4935710076209636</v>
       </c>
       <c r="D18">
-        <v>4.533176262213323</v>
+        <v>4.5331762622133231</v>
       </c>
       <c r="E18">
-        <v>4.572012433927527</v>
+        <v>4.5720124339275268</v>
       </c>
       <c r="F18">
-        <v>4.610108823868916</v>
+        <v>4.6101088238689156</v>
       </c>
       <c r="G18">
-        <v>4.64749308989322</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>4.6474930898932199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3056,22 +3070,22 @@
         <v>46174</v>
       </c>
       <c r="C19">
-        <v>4.509723178832335</v>
+        <v>4.5097231788323349</v>
       </c>
       <c r="D19">
-        <v>4.549328433424694</v>
+        <v>4.5493284334246944</v>
       </c>
       <c r="E19">
         <v>4.588164605138898</v>
       </c>
       <c r="F19">
-        <v>4.626260995080287</v>
+        <v>4.6262609950802869</v>
       </c>
       <c r="G19">
-        <v>4.663645261104591</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>4.6636452611045911</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3079,22 +3093,22 @@
         <v>46204</v>
       </c>
       <c r="C20">
-        <v>4.572202925484229</v>
+        <v>4.5722029254842287</v>
       </c>
       <c r="D20">
-        <v>4.611808180076588</v>
+        <v>4.6118081800765882</v>
       </c>
       <c r="E20">
-        <v>4.650644351790792</v>
+        <v>4.6506443517907918</v>
       </c>
       <c r="F20">
-        <v>4.688740741732181</v>
+        <v>4.6887407417321807</v>
       </c>
       <c r="G20">
-        <v>4.726125007756485</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>4.7261250077564849</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3102,22 +3116,22 @@
         <v>46235</v>
       </c>
       <c r="C21">
-        <v>4.588573097950166</v>
+        <v>4.5885730979501664</v>
       </c>
       <c r="D21">
-        <v>4.628178352542525</v>
+        <v>4.6281783525425251</v>
       </c>
       <c r="E21">
-        <v>4.667014524256729</v>
+        <v>4.6670145242567287</v>
       </c>
       <c r="F21">
-        <v>4.705110914198118</v>
+        <v>4.7051109141981184</v>
       </c>
       <c r="G21">
-        <v>4.742495180222422</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>4.7424951802224218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3125,22 +3139,22 @@
         <v>46266</v>
       </c>
       <c r="C22">
-        <v>4.55298012388381</v>
+        <v>4.5529801238838097</v>
       </c>
       <c r="D22">
-        <v>4.592585378476169</v>
+        <v>4.5925853784761692</v>
       </c>
       <c r="E22">
-        <v>4.631421550190373</v>
+        <v>4.6314215501903728</v>
       </c>
       <c r="F22">
-        <v>4.669517940131762</v>
+        <v>4.6695179401317617</v>
       </c>
       <c r="G22">
-        <v>4.706902206156066</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>4.7069022061560659</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3148,22 +3162,22 @@
         <v>46296</v>
       </c>
       <c r="C23">
-        <v>4.58504129974513</v>
+        <v>4.5850412997451304</v>
       </c>
       <c r="D23">
-        <v>4.624646554337489</v>
+        <v>4.6246465543374891</v>
       </c>
       <c r="E23">
-        <v>4.663482726051693</v>
+        <v>4.6634827260516927</v>
       </c>
       <c r="F23">
-        <v>4.701579115993082</v>
+        <v>4.7015791159930824</v>
       </c>
       <c r="G23">
-        <v>4.738963382017386</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>4.7389633820173858</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3171,22 +3185,22 @@
         <v>46327</v>
       </c>
       <c r="C24">
-        <v>4.503068009197655</v>
+        <v>4.5030680091976549</v>
       </c>
       <c r="D24">
-        <v>4.542673263790014</v>
+        <v>4.5426732637900136</v>
       </c>
       <c r="E24">
-        <v>4.581509435504218</v>
+        <v>4.5815094355042181</v>
       </c>
       <c r="F24">
-        <v>4.619605825445607</v>
+        <v>4.6196058254456069</v>
       </c>
       <c r="G24">
-        <v>4.656990091469911</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>4.6569900914699112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3194,22 +3208,22 @@
         <v>46357</v>
       </c>
       <c r="C25">
-        <v>4.397133371551336</v>
+        <v>4.3971333715513357</v>
       </c>
       <c r="D25">
-        <v>4.436738626143695</v>
+        <v>4.4367386261436952</v>
       </c>
       <c r="E25">
-        <v>4.475574797857899</v>
+        <v>4.4755747978578988</v>
       </c>
       <c r="F25">
-        <v>4.513671187799288</v>
+        <v>4.5136711877992877</v>
       </c>
       <c r="G25">
-        <v>4.551055453823592</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>4.5510554538235919</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3217,22 +3231,22 @@
         <v>46388</v>
       </c>
       <c r="C26">
-        <v>4.394582439711202</v>
+        <v>4.3945824397112023</v>
       </c>
       <c r="D26">
-        <v>4.453990321599742</v>
+        <v>4.4539903215997416</v>
       </c>
       <c r="E26">
         <v>4.512244579171047</v>
       </c>
       <c r="F26">
-        <v>4.56938916408313</v>
+        <v>4.5693891640831303</v>
       </c>
       <c r="G26">
-        <v>4.625465563119587</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>4.6254655631195867</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3240,22 +3254,22 @@
         <v>46419</v>
       </c>
       <c r="C27">
-        <v>4.379635103483346</v>
+        <v>4.3796351034833458</v>
       </c>
       <c r="D27">
-        <v>4.439042985371885</v>
+        <v>4.4390429853718851</v>
       </c>
       <c r="E27">
-        <v>4.497297242943191</v>
+        <v>4.4972972429431914</v>
       </c>
       <c r="F27">
-        <v>4.554441827855274</v>
+        <v>4.5544418278552738</v>
       </c>
       <c r="G27">
-        <v>4.61051822689173</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>4.6105182268917302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3263,22 +3277,22 @@
         <v>46447</v>
       </c>
       <c r="C28">
-        <v>4.423475692907757</v>
+        <v>4.4234756929077568</v>
       </c>
       <c r="D28">
-        <v>4.482883574796296</v>
+        <v>4.4828835747962961</v>
       </c>
       <c r="E28">
-        <v>4.541137832367601</v>
+        <v>4.5411378323676006</v>
       </c>
       <c r="F28">
-        <v>4.598282417279685</v>
+        <v>4.5982824172796848</v>
       </c>
       <c r="G28">
-        <v>4.654358816316141</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>4.6543588163161411</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3286,22 +3300,22 @@
         <v>46478</v>
       </c>
       <c r="C29">
-        <v>4.456325547226226</v>
+        <v>4.4563255472262258</v>
       </c>
       <c r="D29">
-        <v>4.515733429114765</v>
+        <v>4.5157334291147651</v>
       </c>
       <c r="E29">
-        <v>4.57398768668607</v>
+        <v>4.5739876866860696</v>
       </c>
       <c r="F29">
-        <v>4.631132271598154</v>
+        <v>4.6311322715981538</v>
       </c>
       <c r="G29">
-        <v>4.68720867063461</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>4.6872086706346101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3309,22 +3323,22 @@
         <v>46508</v>
       </c>
       <c r="C30">
-        <v>4.493571007620964</v>
+        <v>4.4935710076209636</v>
       </c>
       <c r="D30">
-        <v>4.552978889509503</v>
+        <v>4.5529788895095029</v>
       </c>
       <c r="E30">
-        <v>4.611233147080808</v>
+        <v>4.6112331470808083</v>
       </c>
       <c r="F30">
-        <v>4.668377731992892</v>
+        <v>4.6683777319928916</v>
       </c>
       <c r="G30">
         <v>4.724454131029348</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3332,22 +3346,22 @@
         <v>46539</v>
       </c>
       <c r="C31">
-        <v>4.509723178832335</v>
+        <v>4.5097231788323349</v>
       </c>
       <c r="D31">
-        <v>4.569131060720874</v>
+        <v>4.5691310607208742</v>
       </c>
       <c r="E31">
-        <v>4.62738531829218</v>
+        <v>4.6273853182921796</v>
       </c>
       <c r="F31">
-        <v>4.684529903204263</v>
+        <v>4.6845299032042629</v>
       </c>
       <c r="G31">
-        <v>4.740606302240719</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>4.7406063022407192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3355,22 +3369,22 @@
         <v>46569</v>
       </c>
       <c r="C32">
-        <v>4.572202925484229</v>
+        <v>4.5722029254842287</v>
       </c>
       <c r="D32">
         <v>4.631610807372768</v>
       </c>
       <c r="E32">
-        <v>4.689865064944073</v>
+        <v>4.6898650649440734</v>
       </c>
       <c r="F32">
-        <v>4.747009649856157</v>
+        <v>4.7470096498561567</v>
       </c>
       <c r="G32">
         <v>4.803086048892613</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3378,22 +3392,22 @@
         <v>46600</v>
       </c>
       <c r="C33">
-        <v>4.588573097950166</v>
+        <v>4.5885730979501664</v>
       </c>
       <c r="D33">
-        <v>4.647980979838705</v>
+        <v>4.6479809798387048</v>
       </c>
       <c r="E33">
-        <v>4.70623523741001</v>
+        <v>4.7062352374100103</v>
       </c>
       <c r="F33">
-        <v>4.763379822322094</v>
+        <v>4.7633798223220936</v>
       </c>
       <c r="G33">
-        <v>4.81945622135855</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>4.8194562213585499</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3401,22 +3415,22 @@
         <v>46631</v>
       </c>
       <c r="C34">
-        <v>4.55298012388381</v>
+        <v>4.5529801238838097</v>
       </c>
       <c r="D34">
         <v>4.612388005772349</v>
       </c>
       <c r="E34">
-        <v>4.670642263343654</v>
+        <v>4.6706422633436544</v>
       </c>
       <c r="F34">
-        <v>4.727786848255738</v>
+        <v>4.7277868482557377</v>
       </c>
       <c r="G34">
         <v>4.783863247292194</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3424,22 +3438,22 @@
         <v>46661</v>
       </c>
       <c r="C35">
-        <v>4.58504129974513</v>
+        <v>4.5850412997451304</v>
       </c>
       <c r="D35">
-        <v>4.644449181633669</v>
+        <v>4.6444491816336688</v>
       </c>
       <c r="E35">
-        <v>4.702703439204974</v>
+        <v>4.7027034392049742</v>
       </c>
       <c r="F35">
-        <v>4.759848024117058</v>
+        <v>4.7598480241170584</v>
       </c>
       <c r="G35">
-        <v>4.815924423153514</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>4.8159244231535139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3447,22 +3461,22 @@
         <v>46692</v>
       </c>
       <c r="C36">
-        <v>4.503068009197655</v>
+        <v>4.5030680091976549</v>
       </c>
       <c r="D36">
-        <v>4.562475891086194</v>
+        <v>4.5624758910861942</v>
       </c>
       <c r="E36">
-        <v>4.6207301486575</v>
+        <v>4.6207301486574996</v>
       </c>
       <c r="F36">
-        <v>4.677874733569583</v>
+        <v>4.6778747335695829</v>
       </c>
       <c r="G36">
-        <v>4.733951132606039</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>4.7339511326060393</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3470,22 +3484,22 @@
         <v>46722</v>
       </c>
       <c r="C37">
-        <v>4.397133371551336</v>
+        <v>4.3971333715513357</v>
       </c>
       <c r="D37">
         <v>4.456541253439875</v>
       </c>
       <c r="E37">
-        <v>4.51479551101118</v>
+        <v>4.5147955110111804</v>
       </c>
       <c r="F37">
-        <v>4.571940095923264</v>
+        <v>4.5719400959232637</v>
       </c>
       <c r="G37">
         <v>4.62801649495972</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3493,22 +3507,22 @@
         <v>46753</v>
       </c>
       <c r="C38">
-        <v>4.394582439711202</v>
+        <v>4.3945824397112023</v>
       </c>
       <c r="D38">
-        <v>4.473792948895921</v>
+        <v>4.4737929488959214</v>
       </c>
       <c r="E38">
-        <v>4.551465292324329</v>
+        <v>4.5514652923243286</v>
       </c>
       <c r="F38">
-        <v>4.627658072207106</v>
+        <v>4.6276580722071063</v>
       </c>
       <c r="G38">
-        <v>4.702426604255715</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>4.7024266042557148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3516,22 +3530,22 @@
         <v>46784</v>
       </c>
       <c r="C39">
-        <v>4.379635103483346</v>
+        <v>4.3796351034833458</v>
       </c>
       <c r="D39">
-        <v>4.458845612668065</v>
+        <v>4.4588456126680649</v>
       </c>
       <c r="E39">
-        <v>4.536517956096472</v>
+        <v>4.5365179560964721</v>
       </c>
       <c r="F39">
-        <v>4.61271073597925</v>
+        <v>4.6127107359792499</v>
       </c>
       <c r="G39">
-        <v>4.687479268027858</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>4.6874792680278583</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3539,22 +3553,22 @@
         <v>46813</v>
       </c>
       <c r="C40">
-        <v>4.423475692907757</v>
+        <v>4.4234756929077568</v>
       </c>
       <c r="D40">
-        <v>4.502686202092476</v>
+        <v>4.5026862020924758</v>
       </c>
       <c r="E40">
-        <v>4.580358545520883</v>
+        <v>4.5803585455208831</v>
       </c>
       <c r="F40">
-        <v>4.656551325403661</v>
+        <v>4.6565513254036608</v>
       </c>
       <c r="G40">
-        <v>4.731319857452269</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>4.7313198574522692</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3562,22 +3576,22 @@
         <v>46844</v>
       </c>
       <c r="C41">
-        <v>4.456325547226226</v>
+        <v>4.4563255472262258</v>
       </c>
       <c r="D41">
-        <v>4.535536056410945</v>
+        <v>4.5355360564109448</v>
       </c>
       <c r="E41">
         <v>4.613208399839352</v>
       </c>
       <c r="F41">
-        <v>4.68940117972213</v>
+        <v>4.6894011797221298</v>
       </c>
       <c r="G41">
-        <v>4.764169711770738</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>4.7641697117707382</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3585,22 +3599,22 @@
         <v>46874</v>
       </c>
       <c r="C42">
-        <v>4.493571007620964</v>
+        <v>4.4935710076209636</v>
       </c>
       <c r="D42">
-        <v>4.572781516805683</v>
+        <v>4.5727815168056827</v>
       </c>
       <c r="E42">
-        <v>4.65045386023409</v>
+        <v>4.6504538602340899</v>
       </c>
       <c r="F42">
-        <v>4.726646640116868</v>
+        <v>4.7266466401168676</v>
       </c>
       <c r="G42">
-        <v>4.801415172165476</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>4.8014151721654761</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3608,22 +3622,22 @@
         <v>46905</v>
       </c>
       <c r="C43">
-        <v>4.509723178832335</v>
+        <v>4.5097231788323349</v>
       </c>
       <c r="D43">
-        <v>4.588933688017054</v>
+        <v>4.5889336880170539</v>
       </c>
       <c r="E43">
-        <v>4.666606031445461</v>
+        <v>4.6666060314454612</v>
       </c>
       <c r="F43">
-        <v>4.742798811328239</v>
+        <v>4.7427988113282389</v>
       </c>
       <c r="G43">
-        <v>4.817567343376847</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>4.8175673433768473</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3631,22 +3645,22 @@
         <v>46935</v>
       </c>
       <c r="C44">
-        <v>4.572202925484229</v>
+        <v>4.5722029254842287</v>
       </c>
       <c r="D44">
-        <v>4.651413434668948</v>
+        <v>4.6514134346689477</v>
       </c>
       <c r="E44">
         <v>4.729085778097355</v>
       </c>
       <c r="F44">
-        <v>4.805278557980133</v>
+        <v>4.8052785579801327</v>
       </c>
       <c r="G44">
-        <v>4.880047090028741</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>4.8800470900287412</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3654,22 +3668,22 @@
         <v>46966</v>
       </c>
       <c r="C45">
-        <v>4.588573097950166</v>
+        <v>4.5885730979501664</v>
       </c>
       <c r="D45">
-        <v>4.667783607134885</v>
+        <v>4.6677836071348846</v>
       </c>
       <c r="E45">
-        <v>4.745455950563292</v>
+        <v>4.7454559505632918</v>
       </c>
       <c r="F45">
-        <v>4.82164873044607</v>
+        <v>4.8216487304460696</v>
       </c>
       <c r="G45">
         <v>4.896417262494678</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3677,22 +3691,22 @@
         <v>46997</v>
       </c>
       <c r="C46">
-        <v>4.55298012388381</v>
+        <v>4.5529801238838097</v>
       </c>
       <c r="D46">
-        <v>4.632190633068529</v>
+        <v>4.6321906330685287</v>
       </c>
       <c r="E46">
         <v>4.709862976496936</v>
       </c>
       <c r="F46">
-        <v>4.786055756379714</v>
+        <v>4.7860557563797137</v>
       </c>
       <c r="G46">
-        <v>4.860824288428322</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>4.8608242884283221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3700,22 +3714,22 @@
         <v>47027</v>
       </c>
       <c r="C47">
-        <v>4.58504129974513</v>
+        <v>4.5850412997451304</v>
       </c>
       <c r="D47">
-        <v>4.664251808929849</v>
+        <v>4.6642518089298486</v>
       </c>
       <c r="E47">
-        <v>4.741924152358256</v>
+        <v>4.7419241523582558</v>
       </c>
       <c r="F47">
-        <v>4.818116932241034</v>
+        <v>4.8181169322410344</v>
       </c>
       <c r="G47">
         <v>4.892885464289642</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3723,22 +3737,22 @@
         <v>47058</v>
       </c>
       <c r="C48">
-        <v>4.503068009197655</v>
+        <v>4.5030680091976549</v>
       </c>
       <c r="D48">
         <v>4.582278518382374</v>
       </c>
       <c r="E48">
-        <v>4.659950861810781</v>
+        <v>4.6599508618107812</v>
       </c>
       <c r="F48">
-        <v>4.736143641693559</v>
+        <v>4.7361436416935589</v>
       </c>
       <c r="G48">
-        <v>4.810912173742167</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>4.8109121737421674</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3746,22 +3760,22 @@
         <v>47088</v>
       </c>
       <c r="C49">
-        <v>4.397133371551336</v>
+        <v>4.3971333715513357</v>
       </c>
       <c r="D49">
-        <v>4.476343880736055</v>
+        <v>4.4763438807360547</v>
       </c>
       <c r="E49">
-        <v>4.554016224164462</v>
+        <v>4.5540162241644619</v>
       </c>
       <c r="F49">
-        <v>4.63020900404724</v>
+        <v>4.6302090040472397</v>
       </c>
       <c r="G49">
-        <v>4.704977536095848</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>4.7049775360958481</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3769,22 +3783,22 @@
         <v>47119</v>
       </c>
       <c r="C50">
-        <v>4.394582439711202</v>
+        <v>4.3945824397112023</v>
       </c>
       <c r="D50">
-        <v>4.493595576192101</v>
+        <v>4.4935955761921011</v>
       </c>
       <c r="E50">
-        <v>4.59068600547761</v>
+        <v>4.5906860054776102</v>
       </c>
       <c r="F50">
-        <v>4.685926980331082</v>
+        <v>4.6859269803310823</v>
       </c>
       <c r="G50">
-        <v>4.779387645391843</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>4.7793876453918429</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3792,22 +3806,22 @@
         <v>47150</v>
       </c>
       <c r="C51">
-        <v>4.379635103483346</v>
+        <v>4.3796351034833458</v>
       </c>
       <c r="D51">
-        <v>4.478648239964245</v>
+        <v>4.4786482399642447</v>
       </c>
       <c r="E51">
-        <v>4.575738669249754</v>
+        <v>4.5757386692497537</v>
       </c>
       <c r="F51">
-        <v>4.670979644103226</v>
+        <v>4.6709796441032259</v>
       </c>
       <c r="G51">
-        <v>4.764440309163986</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>4.7644403091639864</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3815,22 +3829,22 @@
         <v>47178</v>
       </c>
       <c r="C52">
-        <v>4.423475692907757</v>
+        <v>4.4234756929077568</v>
       </c>
       <c r="D52">
-        <v>4.522488829388656</v>
+        <v>4.5224888293886556</v>
       </c>
       <c r="E52">
-        <v>4.619579258674165</v>
+        <v>4.6195792586741646</v>
       </c>
       <c r="F52">
-        <v>4.714820233527637</v>
+        <v>4.7148202335276368</v>
       </c>
       <c r="G52">
-        <v>4.808280898588397</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>4.8082808985883974</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3838,22 +3852,22 @@
         <v>47209</v>
       </c>
       <c r="C53">
-        <v>4.456325547226226</v>
+        <v>4.4563255472262258</v>
       </c>
       <c r="D53">
-        <v>4.555338683707125</v>
+        <v>4.5553386837071246</v>
       </c>
       <c r="E53">
-        <v>4.652429112992634</v>
+        <v>4.6524291129926336</v>
       </c>
       <c r="F53">
-        <v>4.747670087846106</v>
+        <v>4.7476700878461058</v>
       </c>
       <c r="G53">
-        <v>4.841130752906866</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>4.8411307529068663</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3861,22 +3875,22 @@
         <v>47239</v>
       </c>
       <c r="C54">
-        <v>4.493571007620964</v>
+        <v>4.4935710076209636</v>
       </c>
       <c r="D54">
-        <v>4.592584144101862</v>
+        <v>4.5925841441018624</v>
       </c>
       <c r="E54">
-        <v>4.689674573387371</v>
+        <v>4.6896745733873706</v>
       </c>
       <c r="F54">
-        <v>4.784915548240844</v>
+        <v>4.7849155482408436</v>
       </c>
       <c r="G54">
-        <v>4.878376213301604</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>4.8783762133016042</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3884,22 +3898,22 @@
         <v>47270</v>
       </c>
       <c r="C55">
-        <v>4.509723178832335</v>
+        <v>4.5097231788323349</v>
       </c>
       <c r="D55">
-        <v>4.608736315313234</v>
+        <v>4.6087363153132337</v>
       </c>
       <c r="E55">
-        <v>4.705826744598743</v>
+        <v>4.7058267445987427</v>
       </c>
       <c r="F55">
-        <v>4.801067719452215</v>
+        <v>4.8010677194522149</v>
       </c>
       <c r="G55">
-        <v>4.894528384512975</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>4.8945283845129746</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3907,22 +3921,22 @@
         <v>47300</v>
       </c>
       <c r="C56">
-        <v>4.572202925484229</v>
+        <v>4.5722029254842287</v>
       </c>
       <c r="D56">
-        <v>4.671216061965128</v>
+        <v>4.6712160619651284</v>
       </c>
       <c r="E56">
-        <v>4.768306491250637</v>
+        <v>4.7683064912506374</v>
       </c>
       <c r="F56">
-        <v>4.863547466104109</v>
+        <v>4.8635474661041087</v>
       </c>
       <c r="G56">
-        <v>4.957008131164869</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>4.9570081311648693</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3930,22 +3944,22 @@
         <v>47331</v>
       </c>
       <c r="C57">
-        <v>4.588573097950166</v>
+        <v>4.5885730979501664</v>
       </c>
       <c r="D57">
-        <v>4.687586234431064</v>
+        <v>4.6875862344310644</v>
       </c>
       <c r="E57">
-        <v>4.784676663716573</v>
+        <v>4.7846766637165734</v>
       </c>
       <c r="F57">
-        <v>4.879917638570046</v>
+        <v>4.8799176385700456</v>
       </c>
       <c r="G57">
-        <v>4.973378303630806</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>4.9733783036308061</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3953,22 +3967,22 @@
         <v>47362</v>
       </c>
       <c r="C58">
-        <v>4.55298012388381</v>
+        <v>4.5529801238838097</v>
       </c>
       <c r="D58">
-        <v>4.651993260364709</v>
+        <v>4.6519932603647094</v>
       </c>
       <c r="E58">
-        <v>4.749083689650218</v>
+        <v>4.7490836896502184</v>
       </c>
       <c r="F58">
-        <v>4.84432466450369</v>
+        <v>4.8443246645036897</v>
       </c>
       <c r="G58">
-        <v>4.93778532956445</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>4.9377853295644503</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3976,22 +3990,22 @@
         <v>47392</v>
       </c>
       <c r="C59">
-        <v>4.58504129974513</v>
+        <v>4.5850412997451304</v>
       </c>
       <c r="D59">
-        <v>4.684054436226028</v>
+        <v>4.6840544362260284</v>
       </c>
       <c r="E59">
-        <v>4.781144865511537</v>
+        <v>4.7811448655115374</v>
       </c>
       <c r="F59">
-        <v>4.87638584036501</v>
+        <v>4.8763858403650104</v>
       </c>
       <c r="G59">
-        <v>4.96984650542577</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>4.9698465054257701</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3999,22 +4013,22 @@
         <v>47423</v>
       </c>
       <c r="C60">
-        <v>4.503068009197655</v>
+        <v>4.5030680091976549</v>
       </c>
       <c r="D60">
-        <v>4.602081145678554</v>
+        <v>4.6020811456785538</v>
       </c>
       <c r="E60">
-        <v>4.699171574964063</v>
+        <v>4.6991715749640628</v>
       </c>
       <c r="F60">
         <v>4.794412549817535</v>
       </c>
       <c r="G60">
-        <v>4.887873214878296</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>4.8878732148782964</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4022,22 +4036,22 @@
         <v>47453</v>
       </c>
       <c r="C61">
-        <v>4.397133371551336</v>
+        <v>4.3971333715513357</v>
       </c>
       <c r="D61">
-        <v>4.496146508032234</v>
+        <v>4.4961465080322336</v>
       </c>
       <c r="E61">
-        <v>4.593236937317744</v>
+        <v>4.5932369373177444</v>
       </c>
       <c r="F61">
-        <v>4.688477912171216</v>
+        <v>4.6884779121712157</v>
       </c>
       <c r="G61">
-        <v>4.781938577231976</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>4.7819385772319762</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4045,22 +4059,22 @@
         <v>47484</v>
       </c>
       <c r="C62">
-        <v>4.394582439711202</v>
+        <v>4.3945824397112023</v>
       </c>
       <c r="D62">
-        <v>4.513398203488281</v>
+        <v>4.5133982034882809</v>
       </c>
       <c r="E62">
-        <v>4.629906718630892</v>
+        <v>4.6299067186308918</v>
       </c>
       <c r="F62">
-        <v>4.744195888455058</v>
+        <v>4.7441958884550584</v>
       </c>
       <c r="G62">
         <v>4.856348686527971</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4068,22 +4082,22 @@
         <v>47515</v>
       </c>
       <c r="C63">
-        <v>4.379635103483346</v>
+        <v>4.3796351034833458</v>
       </c>
       <c r="D63">
-        <v>4.498450867260424</v>
+        <v>4.4984508672604244</v>
       </c>
       <c r="E63">
-        <v>4.614959382403035</v>
+        <v>4.6149593824030353</v>
       </c>
       <c r="F63">
-        <v>4.729248552227202</v>
+        <v>4.7292485522272019</v>
       </c>
       <c r="G63">
-        <v>4.841401350300115</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>4.8414013503001154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4091,22 +4105,22 @@
         <v>47543</v>
       </c>
       <c r="C64">
-        <v>4.423475692907757</v>
+        <v>4.4234756929077568</v>
       </c>
       <c r="D64">
-        <v>4.542291456684835</v>
+        <v>4.5422914566848354</v>
       </c>
       <c r="E64">
-        <v>4.658799971827446</v>
+        <v>4.6587999718274462</v>
       </c>
       <c r="F64">
-        <v>4.773089141651613</v>
+        <v>4.7730891416516128</v>
       </c>
       <c r="G64">
-        <v>4.885241939724525</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>4.8852419397245246</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4114,22 +4128,22 @@
         <v>47574</v>
       </c>
       <c r="C65">
-        <v>4.456325547226226</v>
+        <v>4.4563255472262258</v>
       </c>
       <c r="D65">
-        <v>4.575141311003304</v>
+        <v>4.5751413110033043</v>
       </c>
       <c r="E65">
-        <v>4.691649826145915</v>
+        <v>4.6916498261459152</v>
       </c>
       <c r="F65">
-        <v>4.805938995970082</v>
+        <v>4.8059389959700818</v>
       </c>
       <c r="G65">
-        <v>4.918091794042994</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>4.9180917940429936</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4137,22 +4151,22 @@
         <v>47604</v>
       </c>
       <c r="C66">
-        <v>4.493571007620964</v>
+        <v>4.4935710076209636</v>
       </c>
       <c r="D66">
-        <v>4.612386771398042</v>
+        <v>4.6123867713980422</v>
       </c>
       <c r="E66">
-        <v>4.728895286540653</v>
+        <v>4.7288952865406531</v>
       </c>
       <c r="F66">
-        <v>4.84318445636482</v>
+        <v>4.8431844563648196</v>
       </c>
       <c r="G66">
-        <v>4.955337254437732</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>4.9553372544377323</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4160,22 +4174,22 @@
         <v>47635</v>
       </c>
       <c r="C67">
-        <v>4.509723178832335</v>
+        <v>4.5097231788323349</v>
       </c>
       <c r="D67">
-        <v>4.628538942609413</v>
+        <v>4.6285389426094126</v>
       </c>
       <c r="E67">
-        <v>4.745047457752024</v>
+        <v>4.7450474577520243</v>
       </c>
       <c r="F67">
-        <v>4.859336627576191</v>
+        <v>4.8593366275761909</v>
       </c>
       <c r="G67">
-        <v>4.971489425649104</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>4.9714894256491036</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4183,22 +4197,22 @@
         <v>47665</v>
       </c>
       <c r="C68">
-        <v>4.572202925484229</v>
+        <v>4.5722029254842287</v>
       </c>
       <c r="D68">
-        <v>4.691018689261307</v>
+        <v>4.6910186892613073</v>
       </c>
       <c r="E68">
-        <v>4.807527204403918</v>
+        <v>4.8075272044039181</v>
       </c>
       <c r="F68">
-        <v>4.921816374228085</v>
+        <v>4.9218163742280847</v>
       </c>
       <c r="G68">
-        <v>5.033969172300997</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>5.0339691723009974</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4206,22 +4220,22 @@
         <v>47696</v>
       </c>
       <c r="C69">
-        <v>4.588573097950166</v>
+        <v>4.5885730979501664</v>
       </c>
       <c r="D69">
-        <v>4.707388861727244</v>
+        <v>4.7073888617272441</v>
       </c>
       <c r="E69">
         <v>4.823897376869855</v>
       </c>
       <c r="F69">
-        <v>4.938186546694022</v>
+        <v>4.9381865466940216</v>
       </c>
       <c r="G69">
-        <v>5.050339344766934</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>5.0503393447669342</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4229,22 +4243,22 @@
         <v>47727</v>
       </c>
       <c r="C70">
-        <v>4.55298012388381</v>
+        <v>4.5529801238838097</v>
       </c>
       <c r="D70">
-        <v>4.671795887660888</v>
+        <v>4.6717958876608883</v>
       </c>
       <c r="E70">
-        <v>4.788304402803499</v>
+        <v>4.7883044028034991</v>
       </c>
       <c r="F70">
-        <v>4.902593572627666</v>
+        <v>4.9025935726276657</v>
       </c>
       <c r="G70">
-        <v>5.014746370700578</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>5.0147463707005784</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4252,22 +4266,22 @@
         <v>47757</v>
       </c>
       <c r="C71">
-        <v>4.58504129974513</v>
+        <v>4.5850412997451304</v>
       </c>
       <c r="D71">
-        <v>4.703857063522208</v>
+        <v>4.7038570635222081</v>
       </c>
       <c r="E71">
         <v>4.820365578664819</v>
       </c>
       <c r="F71">
-        <v>4.934654748488986</v>
+        <v>4.9346547484889864</v>
       </c>
       <c r="G71">
-        <v>5.046807546561898</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>5.0468075465618982</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4275,22 +4289,22 @@
         <v>47788</v>
       </c>
       <c r="C72">
-        <v>4.503068009197655</v>
+        <v>4.5030680091976549</v>
       </c>
       <c r="D72">
-        <v>4.621883772974734</v>
+        <v>4.6218837729747344</v>
       </c>
       <c r="E72">
-        <v>4.738392288117344</v>
+        <v>4.7383922881173444</v>
       </c>
       <c r="F72">
         <v>4.852681457941511</v>
       </c>
       <c r="G72">
-        <v>4.964834256014424</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>4.9648342560144236</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4298,22 +4312,22 @@
         <v>47818</v>
       </c>
       <c r="C73">
-        <v>4.397133371551336</v>
+        <v>4.3971333715513357</v>
       </c>
       <c r="D73">
-        <v>4.515949135328414</v>
+        <v>4.5159491353284142</v>
       </c>
       <c r="E73">
-        <v>4.632457650471025</v>
+        <v>4.6324576504710251</v>
       </c>
       <c r="F73">
-        <v>4.746746820295192</v>
+        <v>4.7467468202951917</v>
       </c>
       <c r="G73">
-        <v>4.858899618368104</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>4.8588996183681044</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4321,22 +4335,22 @@
         <v>47849</v>
       </c>
       <c r="C74">
-        <v>4.394582439711202</v>
+        <v>4.3945824397112023</v>
       </c>
       <c r="D74">
-        <v>4.533200830784461</v>
+        <v>4.5332008307844607</v>
       </c>
       <c r="E74">
-        <v>4.669127431784173</v>
+        <v>4.6691274317841733</v>
       </c>
       <c r="F74">
-        <v>4.802464796579034</v>
+        <v>4.8024647965790344</v>
       </c>
       <c r="G74">
-        <v>4.933309727664099</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>4.9333097276640991</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4344,22 +4358,22 @@
         <v>47880</v>
       </c>
       <c r="C75">
-        <v>4.379635103483346</v>
+        <v>4.3796351034833458</v>
       </c>
       <c r="D75">
-        <v>4.518253494556604</v>
+        <v>4.5182534945566042</v>
       </c>
       <c r="E75">
-        <v>4.654180095556317</v>
+        <v>4.6541800955563168</v>
       </c>
       <c r="F75">
-        <v>4.787517460351178</v>
+        <v>4.7875174603511779</v>
       </c>
       <c r="G75">
-        <v>4.918362391436243</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>4.9183623914362427</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4367,22 +4381,22 @@
         <v>47908</v>
       </c>
       <c r="C76">
-        <v>4.423475692907757</v>
+        <v>4.4234756929077568</v>
       </c>
       <c r="D76">
-        <v>4.562094083981015</v>
+        <v>4.5620940839810151</v>
       </c>
       <c r="E76">
-        <v>4.698020684980728</v>
+        <v>4.6980206849807278</v>
       </c>
       <c r="F76">
-        <v>4.831358049775589</v>
+        <v>4.8313580497755888</v>
       </c>
       <c r="G76">
-        <v>4.962202980860654</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>4.9622029808606536</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4390,22 +4404,22 @@
         <v>47939</v>
       </c>
       <c r="C77">
-        <v>4.456325547226226</v>
+        <v>4.4563255472262258</v>
       </c>
       <c r="D77">
-        <v>4.594943938299484</v>
+        <v>4.5949439382994841</v>
       </c>
       <c r="E77">
-        <v>4.730870539299197</v>
+        <v>4.7308705392991968</v>
       </c>
       <c r="F77">
-        <v>4.864207904094058</v>
+        <v>4.8642079040940578</v>
       </c>
       <c r="G77">
-        <v>4.995052835179123</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>4.9950528351791226</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4413,22 +4427,22 @@
         <v>47969</v>
       </c>
       <c r="C78">
-        <v>4.493571007620964</v>
+        <v>4.4935710076209636</v>
       </c>
       <c r="D78">
         <v>4.632189398694222</v>
       </c>
       <c r="E78">
-        <v>4.768115999693935</v>
+        <v>4.7681159996939346</v>
       </c>
       <c r="F78">
-        <v>4.901453364488796</v>
+        <v>4.9014533644887956</v>
       </c>
       <c r="G78">
-        <v>5.03229829557386</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>5.0322982955738604</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4436,22 +4450,22 @@
         <v>48000</v>
       </c>
       <c r="C79">
-        <v>4.509723178832335</v>
+        <v>4.5097231788323349</v>
       </c>
       <c r="D79">
-        <v>4.648341569905593</v>
+        <v>4.6483415699055932</v>
       </c>
       <c r="E79">
-        <v>4.784268170905306</v>
+        <v>4.7842681709053059</v>
       </c>
       <c r="F79">
-        <v>4.917605535700167</v>
+        <v>4.9176055357001669</v>
       </c>
       <c r="G79">
-        <v>5.048450466785232</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>5.0484504667852317</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4459,22 +4473,22 @@
         <v>48030</v>
       </c>
       <c r="C80">
-        <v>4.572202925484229</v>
+        <v>4.5722029254842287</v>
       </c>
       <c r="D80">
         <v>4.710821316557487</v>
       </c>
       <c r="E80">
-        <v>4.8467479175572</v>
+        <v>4.8467479175571997</v>
       </c>
       <c r="F80">
-        <v>4.980085282352061</v>
+        <v>4.9800852823520607</v>
       </c>
       <c r="G80">
-        <v>5.110930213437126</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>5.1109302134371264</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4482,22 +4496,22 @@
         <v>48061</v>
       </c>
       <c r="C81">
-        <v>4.588573097950166</v>
+        <v>4.5885730979501664</v>
       </c>
       <c r="D81">
-        <v>4.727191489023424</v>
+        <v>4.7271914890234239</v>
       </c>
       <c r="E81">
-        <v>4.863118090023137</v>
+        <v>4.8631180900231374</v>
       </c>
       <c r="F81">
-        <v>4.996455454817998</v>
+        <v>4.9964554548179976</v>
       </c>
       <c r="G81">
-        <v>5.127300385903062</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>5.1273003859030624</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4505,22 +4519,22 @@
         <v>48092</v>
       </c>
       <c r="C82">
-        <v>4.55298012388381</v>
+        <v>4.5529801238838097</v>
       </c>
       <c r="D82">
         <v>4.691598514957068</v>
       </c>
       <c r="E82">
-        <v>4.827525115956781</v>
+        <v>4.8275251159567807</v>
       </c>
       <c r="F82">
-        <v>4.960862480751642</v>
+        <v>4.9608624807516417</v>
       </c>
       <c r="G82">
-        <v>5.091707411836706</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>5.0917074118367056</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4528,22 +4542,22 @@
         <v>48122</v>
       </c>
       <c r="C83">
-        <v>4.58504129974513</v>
+        <v>4.5850412997451304</v>
       </c>
       <c r="D83">
-        <v>4.723659690818388</v>
+        <v>4.7236596908183879</v>
       </c>
       <c r="E83">
-        <v>4.859586291818101</v>
+        <v>4.8595862918181014</v>
       </c>
       <c r="F83">
-        <v>4.992923656612962</v>
+        <v>4.9929236566129616</v>
       </c>
       <c r="G83">
-        <v>5.123768587698026</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>5.1237685876980263</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4551,22 +4565,22 @@
         <v>48153</v>
       </c>
       <c r="C84">
-        <v>4.503068009197655</v>
+        <v>4.5030680091976549</v>
       </c>
       <c r="D84">
-        <v>4.641686400270913</v>
+        <v>4.6416864002709133</v>
       </c>
       <c r="E84">
-        <v>4.777613001270626</v>
+        <v>4.7776130012706259</v>
       </c>
       <c r="F84">
         <v>4.910950366065487</v>
       </c>
       <c r="G84">
-        <v>5.041795297150552</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>5.0417952971505517</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4574,22 +4588,22 @@
         <v>48183</v>
       </c>
       <c r="C85">
-        <v>4.397133371551336</v>
+        <v>4.3971333715513357</v>
       </c>
       <c r="D85">
         <v>4.535751762624594</v>
       </c>
       <c r="E85">
-        <v>4.671678363624307</v>
+        <v>4.6716783636243067</v>
       </c>
       <c r="F85">
-        <v>4.805015728419168</v>
+        <v>4.8050157284191677</v>
       </c>
       <c r="G85">
-        <v>4.935860659504232</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>4.9358606595042316</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4597,22 +4611,22 @@
         <v>48214</v>
       </c>
       <c r="C86">
-        <v>4.394582439711202</v>
+        <v>4.3945824397112023</v>
       </c>
       <c r="D86">
-        <v>4.55300345808064</v>
+        <v>4.5530034580806404</v>
       </c>
       <c r="E86">
-        <v>4.708348144937455</v>
+        <v>4.7083481449374549</v>
       </c>
       <c r="F86">
-        <v>4.86073370470301</v>
+        <v>4.8607337047030104</v>
       </c>
       <c r="G86">
-        <v>5.010270768800227</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>5.0102707688002273</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4620,22 +4634,22 @@
         <v>48245</v>
       </c>
       <c r="C87">
-        <v>4.379635103483346</v>
+        <v>4.3796351034833458</v>
       </c>
       <c r="D87">
         <v>4.538056121852784</v>
       </c>
       <c r="E87">
-        <v>4.693400808709598</v>
+        <v>4.6934008087095984</v>
       </c>
       <c r="F87">
-        <v>4.845786368475154</v>
+        <v>4.8457863684751539</v>
       </c>
       <c r="G87">
-        <v>4.995323432572371</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>4.9953234325723708</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4643,22 +4657,22 @@
         <v>48274</v>
       </c>
       <c r="C88">
-        <v>4.423475692907757</v>
+        <v>4.4234756929077568</v>
       </c>
       <c r="D88">
-        <v>4.581896711277195</v>
+        <v>4.5818967112771949</v>
       </c>
       <c r="E88">
-        <v>4.737241398134009</v>
+        <v>4.7372413981340094</v>
       </c>
       <c r="F88">
-        <v>4.889626957899565</v>
+        <v>4.8896269578995648</v>
       </c>
       <c r="G88">
-        <v>5.039164021996782</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>5.0391640219967817</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4666,22 +4680,22 @@
         <v>48305</v>
       </c>
       <c r="C89">
-        <v>4.456325547226226</v>
+        <v>4.4563255472262258</v>
       </c>
       <c r="D89">
-        <v>4.614746565595664</v>
+        <v>4.6147465655956639</v>
       </c>
       <c r="E89">
-        <v>4.770091252452478</v>
+        <v>4.7700912524524783</v>
       </c>
       <c r="F89">
-        <v>4.922476812218034</v>
+        <v>4.9224768122180338</v>
       </c>
       <c r="G89">
-        <v>5.072013876315251</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>5.0720138763152507</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4689,22 +4703,22 @@
         <v>48335</v>
       </c>
       <c r="C90">
-        <v>4.493571007620964</v>
+        <v>4.4935710076209636</v>
       </c>
       <c r="D90">
-        <v>4.651992025990402</v>
+        <v>4.6519920259904017</v>
       </c>
       <c r="E90">
-        <v>4.807336712847216</v>
+        <v>4.8073367128472162</v>
       </c>
       <c r="F90">
-        <v>4.959722272612772</v>
+        <v>4.9597222726127717</v>
       </c>
       <c r="G90">
-        <v>5.109259336709989</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>5.1092593367099894</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4712,22 +4726,22 @@
         <v>48366</v>
       </c>
       <c r="C91">
-        <v>4.509723178832335</v>
+        <v>4.5097231788323349</v>
       </c>
       <c r="D91">
         <v>4.668144197201773</v>
       </c>
       <c r="E91">
-        <v>4.823488884058587</v>
+        <v>4.8234888840585866</v>
       </c>
       <c r="F91">
-        <v>4.975874443824143</v>
+        <v>4.9758744438241429</v>
       </c>
       <c r="G91">
-        <v>5.12541150792136</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>5.1254115079213598</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4735,22 +4749,22 @@
         <v>48396</v>
       </c>
       <c r="C92">
-        <v>4.572202925484229</v>
+        <v>4.5722029254842287</v>
       </c>
       <c r="D92">
-        <v>4.730623943853667</v>
+        <v>4.7306239438536668</v>
       </c>
       <c r="E92">
-        <v>4.885968630710481</v>
+        <v>4.8859686307104813</v>
       </c>
       <c r="F92">
-        <v>5.038354190476037</v>
+        <v>5.0383541904760367</v>
       </c>
       <c r="G92">
-        <v>5.187891254573254</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>5.1878912545732536</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4758,22 +4772,22 @@
         <v>48427</v>
       </c>
       <c r="C93">
-        <v>4.588573097950166</v>
+        <v>4.5885730979501664</v>
       </c>
       <c r="D93">
-        <v>4.746994116319604</v>
+        <v>4.7469941163196037</v>
       </c>
       <c r="E93">
-        <v>4.902338803176418</v>
+        <v>4.9023388031764181</v>
       </c>
       <c r="F93">
-        <v>5.054724362941974</v>
+        <v>5.0547243629419736</v>
       </c>
       <c r="G93">
-        <v>5.20426142703919</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>5.2042614270391896</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4781,22 +4795,22 @@
         <v>48458</v>
       </c>
       <c r="C94">
-        <v>4.55298012388381</v>
+        <v>4.5529801238838097</v>
       </c>
       <c r="D94">
-        <v>4.711401142253248</v>
+        <v>4.7114011422532478</v>
       </c>
       <c r="E94">
-        <v>4.866745829110062</v>
+        <v>4.8667458291100623</v>
       </c>
       <c r="F94">
-        <v>5.019131388875618</v>
+        <v>5.0191313888756177</v>
       </c>
       <c r="G94">
-        <v>5.168668452972835</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>5.1686684529728346</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4804,22 +4818,22 @@
         <v>48488</v>
       </c>
       <c r="C95">
-        <v>4.58504129974513</v>
+        <v>4.5850412997451304</v>
       </c>
       <c r="D95">
-        <v>4.743462318114568</v>
+        <v>4.7434623181145676</v>
       </c>
       <c r="E95">
-        <v>4.898807004971382</v>
+        <v>4.8988070049713821</v>
       </c>
       <c r="F95">
-        <v>5.051192564736938</v>
+        <v>5.0511925647369376</v>
       </c>
       <c r="G95">
-        <v>5.200729628834154</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>5.2007296288341536</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4827,22 +4841,22 @@
         <v>48519</v>
       </c>
       <c r="C96">
-        <v>4.503068009197655</v>
+        <v>4.5030680091976549</v>
       </c>
       <c r="D96">
         <v>4.661489027567093</v>
       </c>
       <c r="E96">
-        <v>4.816833714423908</v>
+        <v>4.8168337144239084</v>
       </c>
       <c r="F96">
         <v>4.969219274189463</v>
       </c>
       <c r="G96">
-        <v>5.11875633828668</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>5.1187563382866799</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4850,19 +4864,19 @@
         <v>48549</v>
       </c>
       <c r="C97">
-        <v>4.397133371551336</v>
+        <v>4.3971333715513357</v>
       </c>
       <c r="D97">
-        <v>4.555554389920774</v>
+        <v>4.5555543899207738</v>
       </c>
       <c r="E97">
-        <v>4.710899076777588</v>
+        <v>4.7108990767775882</v>
       </c>
       <c r="F97">
-        <v>4.863284636543144</v>
+        <v>4.8632846365431437</v>
       </c>
       <c r="G97">
-        <v>5.012821700640361</v>
+        <v>5.0128217006403606</v>
       </c>
     </row>
   </sheetData>
